--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45106</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>46132</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46101</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45841</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46170</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46220</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45469</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>46094</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>46125</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>46185</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>46126</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>45812</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46125</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>46125</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3823,7 +3823,7 @@
         <v>46139</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>46036</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4040,7 +4040,7 @@
         <v>46044</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46114</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46132</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45274</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45280</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>45022</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4813,7 +4813,7 @@
         <v>45754</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45448</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>46070</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45469</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>46139</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>46104</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>46085</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5586,7 +5586,7 @@
         <v>46077</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5696,7 +5696,7 @@
         <v>44496</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>45247</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5916,7 +5916,7 @@
         <v>45582</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6026,7 +6026,7 @@
         <v>45972</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>46009</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6241,7 +6241,7 @@
         <v>46038</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>46053</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         <v>46056</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>46077</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>46097</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>46100</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6884,7 +6884,7 @@
         <v>46101</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6998,7 +6998,7 @@
         <v>46125</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>46091</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7221,7 +7221,7 @@
         <v>46076</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>44953</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>45519</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46283</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         <v>46282</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>46282</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44460</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44795</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44460</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44479</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44529</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8724,7 +8724,7 @@
         <v>44532</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8797,7 +8797,7 @@
         <v>44817</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8948,7 +8948,7 @@
         <v>44509</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>44460</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9094,7 +9094,7 @@
         <v>44858</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9172,7 +9172,7 @@
         <v>44492</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44711</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44795</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44858</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44462</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44802</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44881</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9698,7 +9698,7 @@
         <v>44705</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44872</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>44532</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>44643</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>44663</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>44460</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>44460</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44480</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10297,7 +10297,7 @@
         <v>44889</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>45180</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10443,7 +10443,7 @@
         <v>44804</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>45156</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>45611</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>44890</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45548</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10823,7 +10823,7 @@
         <v>44879</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>45211</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10974,7 +10974,7 @@
         <v>45252</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11047,7 +11047,7 @@
         <v>45167</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45534</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>45617</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11276,7 +11276,7 @@
         <v>45645</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11354,7 +11354,7 @@
         <v>45341</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11427,7 +11427,7 @@
         <v>44950</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45772</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11573,7 +11573,7 @@
         <v>45254</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11646,7 +11646,7 @@
         <v>45434</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>44797</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44986</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>45132</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11943,7 +11943,7 @@
         <v>45611</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12021,7 +12021,7 @@
         <v>44950</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12094,7 +12094,7 @@
         <v>45618</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12167,7 +12167,7 @@
         <v>45432</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>45443</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>45169</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>44887</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>45757</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>45488</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>45581</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>45041</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>45048</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12839,7 +12839,7 @@
         <v>45510</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12912,7 +12912,7 @@
         <v>45111</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12985,7 +12985,7 @@
         <v>45223</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>46029</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>45870</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13209,7 +13209,7 @@
         <v>45799</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13287,7 +13287,7 @@
         <v>45184</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>46050</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>45490</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>45656</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>45139</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>46137</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13745,7 +13745,7 @@
         <v>46137</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13823,7 +13823,7 @@
         <v>45705</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13896,7 +13896,7 @@
         <v>46043</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13969,7 +13969,7 @@
         <v>45803</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>45800</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>46052</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14193,7 +14193,7 @@
         <v>46052</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>45181</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44915</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45821</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45608</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14568,7 +14568,7 @@
         <v>45608</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>44700</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14724,7 +14724,7 @@
         <v>45889</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14797,7 +14797,7 @@
         <v>45888</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>45888</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15026,7 +15026,7 @@
         <v>45889</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45891</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15177,7 +15177,7 @@
         <v>46036</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15250,7 +15250,7 @@
         <v>45744</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>45204</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15401,7 +15401,7 @@
         <v>45884</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15474,7 +15474,7 @@
         <v>46021</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15547,7 +15547,7 @@
         <v>46139</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15625,7 +15625,7 @@
         <v>45334</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45894</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15771,7 +15771,7 @@
         <v>46107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>45645</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15927,7 +15927,7 @@
         <v>45478</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16005,7 +16005,7 @@
         <v>45441</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>46136</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>46136</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16224,7 +16224,7 @@
         <v>45254</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45896</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16370,7 +16370,7 @@
         <v>46064</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16448,7 +16448,7 @@
         <v>46138</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16526,7 +16526,7 @@
         <v>46042</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16604,7 +16604,7 @@
         <v>46065</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16682,7 +16682,7 @@
         <v>45450</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>45366</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>45712</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16906,7 +16906,7 @@
         <v>45903</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16979,7 +16979,7 @@
         <v>45903</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17052,7 +17052,7 @@
         <v>45903</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17130,7 +17130,7 @@
         <v>46034</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>45840</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17286,7 +17286,7 @@
         <v>46052</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17364,7 +17364,7 @@
         <v>45817</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17442,7 +17442,7 @@
         <v>45905</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17515,7 +17515,7 @@
         <v>46140</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>46106</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>45835</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17739,7 +17739,7 @@
         <v>45488</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17812,7 +17812,7 @@
         <v>46066</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>46064</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17958,7 +17958,7 @@
         <v>46035</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
         <v>44712</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
         <v>46071</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18177,7 +18177,7 @@
         <v>45301</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18250,7 +18250,7 @@
         <v>46048</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
         <v>46140</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18401,7 +18401,7 @@
         <v>46140</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>45111</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18552,7 +18552,7 @@
         <v>45111</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>46027</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>45911</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18776,7 +18776,7 @@
         <v>45777</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18854,7 +18854,7 @@
         <v>46056</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18932,7 +18932,7 @@
         <v>46042</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
         <v>46063</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19078,7 +19078,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19151,7 +19151,7 @@
         <v>46140</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45237</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45911</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19380,7 +19380,7 @@
         <v>46141</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19458,7 +19458,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19536,7 +19536,7 @@
         <v>46071</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>45488</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19687,7 +19687,7 @@
         <v>46098</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19760,7 +19760,7 @@
         <v>45526</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>46140</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19916,7 +19916,7 @@
         <v>46079</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>46125</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
         <v>46091</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20145,7 +20145,7 @@
         <v>45747</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>46029</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>46063</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20369,7 +20369,7 @@
         <v>46043</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20442,7 +20442,7 @@
         <v>45488</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20515,7 +20515,7 @@
         <v>46037</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20588,7 +20588,7 @@
         <v>46073</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>46056</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>46052</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>46034</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
         <v>46077</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45925</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>45644</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45602</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>45027</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>45602</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>45602</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>46140</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>46063</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21582,7 +21582,7 @@
         <v>45608</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45162</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>44522</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21816,7 +21816,7 @@
         <v>45700</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21889,7 +21889,7 @@
         <v>45846</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21967,7 +21967,7 @@
         <v>45554</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45216</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22123,7 +22123,7 @@
         <v>45554</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>44816</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45590</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45929</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45929</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>44501</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45617</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22659,7 +22659,7 @@
         <v>44845</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22737,7 +22737,7 @@
         <v>44525</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22815,7 +22815,7 @@
         <v>45582</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>45107</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>46142</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>45930</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45342</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23195,7 +23195,7 @@
         <v>46104</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45994</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45932</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>44970</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>46146</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23575,7 +23575,7 @@
         <v>46127</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>46122</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23731,7 +23731,7 @@
         <v>45754</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>45330</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23882,7 +23882,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45937</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45937</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>46125</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>46147</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>46147</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24335,7 +24335,7 @@
         <v>45937</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45937</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24486,7 +24486,7 @@
         <v>45937</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>46107</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45106</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>46148</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24793,7 +24793,7 @@
         <v>46148</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24871,7 +24871,7 @@
         <v>45834</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>46134</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25022,7 +25022,7 @@
         <v>46149</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>46148</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>46148</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>46148</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>46100</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>46119</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>46066</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45674</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>46153</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25699,7 +25699,7 @@
         <v>46071</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25777,7 +25777,7 @@
         <v>46128</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25855,7 +25855,7 @@
         <v>45258</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45953</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26001,7 +26001,7 @@
         <v>45952</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45953</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45957</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45954</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46153</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26381,7 +26381,7 @@
         <v>45954</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45291</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>46071</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45624</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45959</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45551</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>46065</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45966</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45967</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45967</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27131,7 +27131,7 @@
         <v>45986</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>46043</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45926</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45972</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>45973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45973</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45972</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>46155</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45973</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>45973</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27939,7 +27939,7 @@
         <v>45972</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28012,7 +28012,7 @@
         <v>45649</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45973</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45973</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45975</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>46154</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28601,7 +28601,7 @@
         <v>45978</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28674,7 +28674,7 @@
         <v>45978</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>46155</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28820,7 +28820,7 @@
         <v>46093</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28893,7 +28893,7 @@
         <v>46119</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28966,7 +28966,7 @@
         <v>46056</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45909</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29112,7 +29112,7 @@
         <v>45978</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29185,7 +29185,7 @@
         <v>45978</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29258,7 +29258,7 @@
         <v>45600</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29331,7 +29331,7 @@
         <v>46155</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29404,7 +29404,7 @@
         <v>46104</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29482,7 +29482,7 @@
         <v>46088</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29560,7 +29560,7 @@
         <v>46044</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29633,7 +29633,7 @@
         <v>46049</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29706,7 +29706,7 @@
         <v>45985</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>46093</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29852,7 +29852,7 @@
         <v>46093</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29930,7 +29930,7 @@
         <v>45985</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30003,7 +30003,7 @@
         <v>45994</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30076,7 +30076,7 @@
         <v>45986</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30154,7 +30154,7 @@
         <v>45994</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>46156</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>46122</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30373,7 +30373,7 @@
         <v>46100</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45455</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>46161</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30592,7 +30592,7 @@
         <v>45986</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30665,7 +30665,7 @@
         <v>46161</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30743,7 +30743,7 @@
         <v>46099</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30816,7 +30816,7 @@
         <v>45988</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30894,7 +30894,7 @@
         <v>46160</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30967,7 +30967,7 @@
         <v>44883</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31045,7 +31045,7 @@
         <v>46161</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31118,7 +31118,7 @@
         <v>46163</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>45554</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45716</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>45995</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45620</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31498,7 +31498,7 @@
         <v>45203</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31571,7 +31571,7 @@
         <v>45995</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31649,7 +31649,7 @@
         <v>45994</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31727,7 +31727,7 @@
         <v>45996</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>46000</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>46164</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31956,7 +31956,7 @@
         <v>45398</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>45134</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32107,7 +32107,7 @@
         <v>45134</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32185,7 +32185,7 @@
         <v>45646</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>46006</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>45989</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32409,7 +32409,7 @@
         <v>46164</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>46009</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32565,7 +32565,7 @@
         <v>44839</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32643,7 +32643,7 @@
         <v>46009</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>46044</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32789,7 +32789,7 @@
         <v>46013</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>46013</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32945,7 +32945,7 @@
         <v>46010</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33018,7 +33018,7 @@
         <v>46169</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33091,7 +33091,7 @@
         <v>46169</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33169,7 +33169,7 @@
         <v>44496</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>46169</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>46168</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>46009</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33481,7 +33481,7 @@
         <v>46014</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33554,7 +33554,7 @@
         <v>46169</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>46168</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33710,7 +33710,7 @@
         <v>45699</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33788,7 +33788,7 @@
         <v>46169</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33861,7 +33861,7 @@
         <v>46168</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>46170</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34012,7 +34012,7 @@
         <v>46021</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>46170</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34163,7 +34163,7 @@
         <v>46170</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34241,7 +34241,7 @@
         <v>45184</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34319,7 +34319,7 @@
         <v>46170</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34397,7 +34397,7 @@
         <v>46027</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>46027</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34543,7 +34543,7 @@
         <v>46027</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>46027</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>46027</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34762,7 +34762,7 @@
         <v>46024</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34835,7 +34835,7 @@
         <v>46027</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34908,7 +34908,7 @@
         <v>46029</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34981,7 +34981,7 @@
         <v>46170</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35059,7 +35059,7 @@
         <v>46028</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35132,7 +35132,7 @@
         <v>46028</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35205,7 +35205,7 @@
         <v>46029</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35278,7 +35278,7 @@
         <v>46024</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35351,7 +35351,7 @@
         <v>46029</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>46029</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>46170</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46031</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35648,7 +35648,7 @@
         <v>46031</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35721,7 +35721,7 @@
         <v>46170</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>46034</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>46034</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>46033</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>46035</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>46035</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>46085</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45511</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>46035</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>44820</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>46037</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>45152</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>46023</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36685,7 +36685,7 @@
         <v>46036</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36758,7 +36758,7 @@
         <v>46036</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36831,7 +36831,7 @@
         <v>46036</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>46036</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>46174</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>44643</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37123,7 +37123,7 @@
         <v>44893</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>46036</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37269,7 +37269,7 @@
         <v>45107</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37347,7 +37347,7 @@
         <v>46036</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37420,7 +37420,7 @@
         <v>46041</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37493,7 +37493,7 @@
         <v>45243</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37566,7 +37566,7 @@
         <v>46036</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
         <v>45967</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>46174</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37785,7 +37785,7 @@
         <v>46041</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37858,7 +37858,7 @@
         <v>46038</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37931,7 +37931,7 @@
         <v>46038</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38004,7 +38004,7 @@
         <v>45671</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38082,7 +38082,7 @@
         <v>46043</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>46043</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38228,7 +38228,7 @@
         <v>45210</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38301,7 +38301,7 @@
         <v>46174</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46044</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>46044</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>46045</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38598,7 +38598,7 @@
         <v>46036</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38671,7 +38671,7 @@
         <v>46044</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>46045</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>46171</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>46036</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>46049</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39036,7 +39036,7 @@
         <v>46038</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39109,7 +39109,7 @@
         <v>46049</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39182,7 +39182,7 @@
         <v>46048</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39255,7 +39255,7 @@
         <v>46048</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39328,7 +39328,7 @@
         <v>46050</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>45593</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39479,7 +39479,7 @@
         <v>46175</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39557,7 +39557,7 @@
         <v>46175</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39635,7 +39635,7 @@
         <v>46051</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39713,7 +39713,7 @@
         <v>46050</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>46051</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39864,7 +39864,7 @@
         <v>46052</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39937,7 +39937,7 @@
         <v>46053</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40010,7 +40010,7 @@
         <v>46052</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40083,7 +40083,7 @@
         <v>46052</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40156,7 +40156,7 @@
         <v>45603</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40229,7 +40229,7 @@
         <v>46055</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40307,7 +40307,7 @@
         <v>45678</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40380,7 +40380,7 @@
         <v>46052</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40453,7 +40453,7 @@
         <v>46056</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40531,7 +40531,7 @@
         <v>46056</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40604,7 +40604,7 @@
         <v>46057</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40682,7 +40682,7 @@
         <v>45156</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40760,7 +40760,7 @@
         <v>46056</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40833,7 +40833,7 @@
         <v>46056</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>46056</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>46056</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>46056</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41125,7 +41125,7 @@
         <v>46056</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41198,7 +41198,7 @@
         <v>45674</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41271,7 +41271,7 @@
         <v>46059</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41344,7 +41344,7 @@
         <v>46177</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>46177</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41500,7 +41500,7 @@
         <v>46062</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41573,7 +41573,7 @@
         <v>46062</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41646,7 +41646,7 @@
         <v>46062</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>46062</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>46065</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>46064</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41948,7 +41948,7 @@
         <v>46064</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>46065</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42094,7 +42094,7 @@
         <v>46064</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>46156</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>46069</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>46071</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>46071</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>46071</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>46071</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>46071</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46071</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42776,7 +42776,7 @@
         <v>46071</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>46071</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42922,7 +42922,7 @@
         <v>46181</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42995,7 +42995,7 @@
         <v>45527</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43073,7 +43073,7 @@
         <v>46056</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>46031</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>46072</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43297,7 +43297,7 @@
         <v>46072</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43370,7 +43370,7 @@
         <v>46072</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43448,7 +43448,7 @@
         <v>46072</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43526,7 +43526,7 @@
         <v>46073</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43599,7 +43599,7 @@
         <v>46077</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43677,7 +43677,7 @@
         <v>46078</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>46077</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43833,7 +43833,7 @@
         <v>46077</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43911,7 +43911,7 @@
         <v>46077</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43989,7 +43989,7 @@
         <v>46077</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>46031</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44140,7 +44140,7 @@
         <v>44781</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44213,7 +44213,7 @@
         <v>46076</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44291,7 +44291,7 @@
         <v>46077</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>46077</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44442,7 +44442,7 @@
         <v>46079</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45261</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44588,7 +44588,7 @@
         <v>46080</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44661,7 +44661,7 @@
         <v>46080</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>46080</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44807,7 +44807,7 @@
         <v>46079</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44880,7 +44880,7 @@
         <v>46126</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44953,7 +44953,7 @@
         <v>46083</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45026,7 +45026,7 @@
         <v>46083</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>46083</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>46085</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>46185</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45328,7 +45328,7 @@
         <v>46185</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45401,7 +45401,7 @@
         <v>46188</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>46087</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>46188</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>46185</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45703,7 +45703,7 @@
         <v>46185</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45776,7 +45776,7 @@
         <v>46185</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45849,7 +45849,7 @@
         <v>46190</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45922,7 +45922,7 @@
         <v>46089</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46000,7 +46000,7 @@
         <v>46092</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46073,7 +46073,7 @@
         <v>46091</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46146,7 +46146,7 @@
         <v>45981</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46224,7 +46224,7 @@
         <v>46093</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46297,7 +46297,7 @@
         <v>46076</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46375,7 +46375,7 @@
         <v>46094</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>46190</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>46190</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46599,7 +46599,7 @@
         <v>46190</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46677,7 +46677,7 @@
         <v>45615</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46750,7 +46750,7 @@
         <v>46094</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46823,7 +46823,7 @@
         <v>46093</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46896,7 +46896,7 @@
         <v>46094</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -46969,7 +46969,7 @@
         <v>46189</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47042,7 +47042,7 @@
         <v>46189</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47115,7 +47115,7 @@
         <v>46189</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>46093</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47271,7 +47271,7 @@
         <v>46189</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47344,7 +47344,7 @@
         <v>46189</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47422,7 +47422,7 @@
         <v>46098</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47500,7 +47500,7 @@
         <v>46098</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47578,7 +47578,7 @@
         <v>46098</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47651,7 +47651,7 @@
         <v>46092</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47724,7 +47724,7 @@
         <v>46191</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47802,7 +47802,7 @@
         <v>46098</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47880,7 +47880,7 @@
         <v>46097</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>46098</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>46099</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48104,7 +48104,7 @@
         <v>46055</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48182,7 +48182,7 @@
         <v>46196</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48260,7 +48260,7 @@
         <v>46196</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>46196</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48416,7 +48416,7 @@
         <v>46195</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48494,7 +48494,7 @@
         <v>46098</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48572,7 +48572,7 @@
         <v>46098</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48650,7 +48650,7 @@
         <v>46100</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48723,7 +48723,7 @@
         <v>46100</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48796,7 +48796,7 @@
         <v>46099</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48874,7 +48874,7 @@
         <v>46104</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48952,7 +48952,7 @@
         <v>46104</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49025,7 +49025,7 @@
         <v>46104</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49103,7 +49103,7 @@
         <v>46104</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49181,7 +49181,7 @@
         <v>46101</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49259,7 +49259,7 @@
         <v>46104</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>46104</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49410,7 +49410,7 @@
         <v>46104</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49488,7 +49488,7 @@
         <v>46101</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>46104</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49644,7 +49644,7 @@
         <v>46106</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49722,7 +49722,7 @@
         <v>45758</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49795,7 +49795,7 @@
         <v>46106</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49868,7 +49868,7 @@
         <v>45534</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49941,7 +49941,7 @@
         <v>45334</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>46106</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>46198</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>46099</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>46099</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>46105</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>46198</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50472,7 +50472,7 @@
         <v>45609</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50550,7 +50550,7 @@
         <v>46198</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>46106</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>46106</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50779,7 +50779,7 @@
         <v>45022</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50852,7 +50852,7 @@
         <v>45139</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>46108</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>46108</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>46111</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>46112</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51232,7 +51232,7 @@
         <v>46112</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51310,7 +51310,7 @@
         <v>46199</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51388,7 +51388,7 @@
         <v>46112</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51466,7 +51466,7 @@
         <v>46111</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>45237</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51612,7 +51612,7 @@
         <v>45698</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>46114</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>46114</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>45727</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>46114</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -51987,7 +51987,7 @@
         <v>46114</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>46094</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52138,7 +52138,7 @@
         <v>46076</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52216,7 +52216,7 @@
         <v>46076</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52294,7 +52294,7 @@
         <v>46077</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52372,7 +52372,7 @@
         <v>46119</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52445,7 +52445,7 @@
         <v>46076</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>46119</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>46118</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>46076</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>46121</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>46121</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52898,7 +52898,7 @@
         <v>46121</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -52971,7 +52971,7 @@
         <v>45497</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53044,7 +53044,7 @@
         <v>46049</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53117,7 +53117,7 @@
         <v>46125</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53195,7 +53195,7 @@
         <v>46199</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>46126</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>46126</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>46098</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>46127</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>46105</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>46127</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>46112</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>46128</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>46112</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>44838</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>46128</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>46106</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54184,7 +54184,7 @@
         <v>46127</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54257,7 +54257,7 @@
         <v>46045</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54330,7 +54330,7 @@
         <v>46245</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54408,7 +54408,7 @@
         <v>45156</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54486,7 +54486,7 @@
         <v>46183</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54564,7 +54564,7 @@
         <v>46104</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54637,7 +54637,7 @@
         <v>46204</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54715,7 +54715,7 @@
         <v>46132</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54793,7 +54793,7 @@
         <v>46133</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
         <v>46132</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54949,7 +54949,7 @@
         <v>46133</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55027,7 +55027,7 @@
         <v>46203</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55105,7 +55105,7 @@
         <v>46132</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55178,7 +55178,7 @@
         <v>46132</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55256,7 +55256,7 @@
         <v>46132</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55329,7 +55329,7 @@
         <v>45134</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>46203</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55485,7 +55485,7 @@
         <v>46133</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55558,7 +55558,7 @@
         <v>46132</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55636,7 +55636,7 @@
         <v>45134</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55714,7 +55714,7 @@
         <v>46132</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55792,7 +55792,7 @@
         <v>46132</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55870,7 +55870,7 @@
         <v>45596</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55943,7 +55943,7 @@
         <v>46134</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56016,7 +56016,7 @@
         <v>46134</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56089,7 +56089,7 @@
         <v>46114</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>46119</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>46133</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>46134</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56391,7 +56391,7 @@
         <v>45240</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56469,7 +56469,7 @@
         <v>46121</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56542,7 +56542,7 @@
         <v>45609</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56620,7 +56620,7 @@
         <v>45139</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56693,7 +56693,7 @@
         <v>46043</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56766,7 +56766,7 @@
         <v>46064</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56839,7 +56839,7 @@
         <v>46137</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56917,7 +56917,7 @@
         <v>45800</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56995,7 +56995,7 @@
         <v>46049</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57073,7 +57073,7 @@
         <v>46106</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57151,7 +57151,7 @@
         <v>45946</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57229,7 +57229,7 @@
         <v>44663</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57307,7 +57307,7 @@
         <v>45544</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57380,7 +57380,7 @@
         <v>45925</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57458,7 +57458,7 @@
         <v>46048</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57536,7 +57536,7 @@
         <v>46055</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57614,7 +57614,7 @@
         <v>46203</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57687,7 +57687,7 @@
         <v>46205</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57760,7 +57760,7 @@
         <v>45481</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57833,7 +57833,7 @@
         <v>45623</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57911,7 +57911,7 @@
         <v>46206</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57984,7 +57984,7 @@
         <v>46205</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58057,7 +58057,7 @@
         <v>44725</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58130,7 +58130,7 @@
         <v>46205</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58203,7 +58203,7 @@
         <v>45281</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58276,7 +58276,7 @@
         <v>44950</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58349,7 +58349,7 @@
         <v>45068</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58427,7 +58427,7 @@
         <v>45771</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58505,7 +58505,7 @@
         <v>45068</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58583,7 +58583,7 @@
         <v>45534</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58656,7 +58656,7 @@
         <v>46254</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45230</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58812,7 +58812,7 @@
         <v>45156</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58890,7 +58890,7 @@
         <v>45070</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58963,7 +58963,7 @@
         <v>45628</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59036,7 +59036,7 @@
         <v>45771</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59114,7 +59114,7 @@
         <v>45484</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59187,7 +59187,7 @@
         <v>45280</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59260,7 +59260,7 @@
         <v>46216</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59338,7 +59338,7 @@
         <v>46258</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59416,7 +59416,7 @@
         <v>45239</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59489,7 +59489,7 @@
         <v>46052</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59562,7 +59562,7 @@
         <v>46213</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59635,7 +59635,7 @@
         <v>45600</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59708,7 +59708,7 @@
         <v>45744</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59786,7 +59786,7 @@
         <v>46260</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59864,7 +59864,7 @@
         <v>45072</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59937,7 +59937,7 @@
         <v>46218</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60015,7 +60015,7 @@
         <v>46071</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60093,7 +60093,7 @@
         <v>46220</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60171,7 +60171,7 @@
         <v>46098</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60249,7 +60249,7 @@
         <v>45982</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60327,7 +60327,7 @@
         <v>45448</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60405,7 +60405,7 @@
         <v>46267</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60483,7 +60483,7 @@
         <v>45666</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>46223</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60629,7 +60629,7 @@
         <v>46223</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60702,7 +60702,7 @@
         <v>45265</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60775,7 +60775,7 @@
         <v>46224</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60853,7 +60853,7 @@
         <v>46223</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60931,7 +60931,7 @@
         <v>45134</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61009,7 +61009,7 @@
         <v>46224</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>46268</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61165,7 +61165,7 @@
         <v>46269</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61243,7 +61243,7 @@
         <v>46269</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61321,7 +61321,7 @@
         <v>44950</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61394,7 +61394,7 @@
         <v>46268</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61472,7 +61472,7 @@
         <v>45776</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61545,7 +61545,7 @@
         <v>46230</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61623,7 +61623,7 @@
         <v>45455</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61696,7 +61696,7 @@
         <v>46232</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61774,7 +61774,7 @@
         <v>46275</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61852,7 +61852,7 @@
         <v>46274</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61925,7 +61925,7 @@
         <v>45608</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61998,7 +61998,7 @@
         <v>45544</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62071,7 +62071,7 @@
         <v>46275</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62149,7 +62149,7 @@
         <v>46140</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62222,7 +62222,7 @@
         <v>45258</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62295,7 +62295,7 @@
         <v>46279</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62373,7 +62373,7 @@
         <v>46140</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62446,7 +62446,7 @@
         <v>45786</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62524,7 +62524,7 @@
         <v>45786</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45478</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62680,7 +62680,7 @@
         <v>45617</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62758,7 +62758,7 @@
         <v>44746</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62831,7 +62831,7 @@
         <v>45776</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62909,7 +62909,7 @@
         <v>45790</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62982,7 +62982,7 @@
         <v>45621</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63055,7 +63055,7 @@
         <v>45468</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63128,7 +63128,7 @@
         <v>45593</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63201,7 +63201,7 @@
         <v>45754</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63274,7 +63274,7 @@
         <v>44659</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63347,7 +63347,7 @@
         <v>45282</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63420,7 +63420,7 @@
         <v>45434</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63493,7 +63493,7 @@
         <v>46283</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63566,7 +63566,7 @@
         <v>46283</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63644,7 +63644,7 @@
         <v>45596</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63717,7 +63717,7 @@
         <v>45747</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63795,7 +63795,7 @@
         <v>45803</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63868,7 +63868,7 @@
         <v>45800</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63946,7 +63946,7 @@
         <v>45800</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64024,7 +64024,7 @@
         <v>45800</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64102,7 +64102,7 @@
         <v>45800</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64180,7 +64180,7 @@
         <v>45800</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64258,7 +64258,7 @@
         <v>45800</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64336,7 +64336,7 @@
         <v>45805</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64409,7 +64409,7 @@
         <v>45817</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64487,7 +64487,7 @@
         <v>45817</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64560,7 +64560,7 @@
         <v>45817</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64638,7 +64638,7 @@
         <v>45819</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64716,7 +64716,7 @@
         <v>45819</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64794,7 +64794,7 @@
         <v>45821</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64872,7 +64872,7 @@
         <v>45824</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64950,7 +64950,7 @@
         <v>45827</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65028,7 +65028,7 @@
         <v>45827</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65101,7 +65101,7 @@
         <v>45827</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65179,7 +65179,7 @@
         <v>45827</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65257,7 +65257,7 @@
         <v>45838</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45840</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65403,7 +65403,7 @@
         <v>45840</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45109</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65554,7 +65554,7 @@
         <v>45719</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65627,7 +65627,7 @@
         <v>45073</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65700,7 +65700,7 @@
         <v>45851</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65778,7 +65778,7 @@
         <v>45719</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65856,7 +65856,7 @@
         <v>45551</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65929,7 +65929,7 @@
         <v>45586</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66002,7 +66002,7 @@
         <v>45323</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>45638</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
@@ -66158,7 +66158,7 @@
         <v>45315</v>
       </c>
       <c r="E840" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -66236,7 +66236,7 @@
         <v>45699</v>
       </c>
       <c r="E841" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -66314,7 +66314,7 @@
         <v>44904</v>
       </c>
       <c r="E842" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
@@ -66392,7 +66392,7 @@
         <v>46058</v>
       </c>
       <c r="E843" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
@@ -66465,7 +66465,7 @@
         <v>46089</v>
       </c>
       <c r="E844" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
@@ -66543,7 +66543,7 @@
         <v>46148</v>
       </c>
       <c r="E845" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -66616,7 +66616,7 @@
         <v>46148</v>
       </c>
       <c r="E846" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -66689,7 +66689,7 @@
         <v>46048</v>
       </c>
       <c r="E847" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46101</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46170</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46220</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45469</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>46126</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46094</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>46185</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>46125</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>46114</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>46132</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46125</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45274</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46038</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45280</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>46053</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46056</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46077</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45582</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>46097</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>46100</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46101</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>46125</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>46091</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>46076</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45972</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45448</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45469</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>46009</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>46104</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>46085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>46077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45022</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45754</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46282</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>46282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>46283</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44953</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45519</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44479</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44532</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44492</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44795</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44858</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44802</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44881</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44643</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44663</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45184</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45334</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45203</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45527</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45330</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44893</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44838</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45434</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45450</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>45443</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45334</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45455</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45366</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>45481</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45490</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45282</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45884</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45478</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>46021</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>46024</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>46027</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>46027</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>46027</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>46027</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>46027</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>46027</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>46029</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45434</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45134</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>45342</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>46028</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>46029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44659</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45468</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>45754</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45534</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45239</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45747</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>46028</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>46029</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>46029</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>46024</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46031</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>46034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45799</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45888</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>46033</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>46031</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>46036</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>46036</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>46035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>45888</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>46036</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>46035</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>46036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>46036</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>46035</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>46036</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45488</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46038</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45800</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45889</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>46038</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45744</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>46037</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45800</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45800</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45184</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>46041</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45891</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>46036</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45800</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45800</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45800</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45894</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>46041</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>46044</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44879</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>46044</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45618</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>44889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>46043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46043</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>46038</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>46036</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>46048</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>46036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>46044</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>46045</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>46045</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>46049</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>46050</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>46049</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>46050</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45835</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45905</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>46052</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>46052</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46052</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>46051</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>46056</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46056</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>46053</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45777</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45280</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>46056</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>46056</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>46056</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>46056</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>46055</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45911</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>46056</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46056</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45911</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>46057</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>46062</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>46059</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>46062</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45554</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>46062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>46062</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46064</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46064</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>46064</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>46065</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>46065</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45803</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46069</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46056</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>46071</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44950</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>46071</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45925</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>46071</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>46071</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>46071</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>46072</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>46072</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46072</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>46072</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>46071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>46071</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>46031</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>46071</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>46076</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46077</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>46077</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>46077</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46073</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46077</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>46077</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45846</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45107</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>46031</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>46077</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45930</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>46078</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>46079</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>44845</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45590</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45617</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44501</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45554</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>46079</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45497</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44525</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>46080</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45582</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45929</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45929</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45602</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>45602</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45602</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44816</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45027</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45608</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45554</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45644</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45216</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44522</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>46080</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46083</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>46083</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>46083</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>46080</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>45805</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>45932</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>46126</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>46085</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>46087</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46089</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>46091</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45937</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45937</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45937</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45937</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46093</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46093</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45937</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45937</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>46093</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>46097</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44950</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>46094</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>46094</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45834</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>46092</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46098</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>46098</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46099</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>46098</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>46098</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46098</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>46098</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>46099</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>46100</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>46100</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45398</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>46101</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>46101</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>45448</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46104</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>46105</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>46104</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46104</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>46104</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>46104</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46104</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>46104</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>46099</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45952</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>46106</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46106</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>46099</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>46106</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45954</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>46106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>46106</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45953</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>46111</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45954</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>46108</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>45953</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>46108</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45281</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>46111</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>46112</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>46112</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>46112</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45291</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46114</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>46114</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46114</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46094</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>46114</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46119</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>46119</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>46118</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45959</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>46121</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>46076</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46076</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46077</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46076</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46121</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46121</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46049</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46076</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45106</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46125</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45609</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46106</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46126</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>46105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46126</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46127</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46127</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45967</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45967</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45972</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>45611</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45674</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45972</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45972</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>45973</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45973</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45973</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45973</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45973</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45973</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>46127</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46098</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46132</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45973</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45817</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>46132</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45978</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46132</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45978</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>46132</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45978</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>46128</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45978</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>46112</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>46112</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>46132</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>46128</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45978</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45978</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45978</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45975</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>46132</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>46132</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45666</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46134</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>46134</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45510</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>46134</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>46133</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46133</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46133</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>46133</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46136</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45511</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45986</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45070</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45646</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45986</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45985</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45985</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45645</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45656</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45988</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45727</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46136</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45817</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>46121</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45699</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>46119</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>46114</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45712</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45994</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45817</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45484</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46140</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45996</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>46071</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45840</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45995</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45995</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>46048</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>46042</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>46064</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>46000</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>46140</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45534</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46137</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>46137</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>46140</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45111</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>46139</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>46036</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45819</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>46006</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45821</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45946</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45989</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45819</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>46043</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46043</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45488</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>46063</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>46042</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>46049</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>46063</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45698</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>46009</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>46138</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>46052</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>46048</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45526</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>46009</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>46098</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>46079</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>46013</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>46014</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>46010</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>46055</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>46013</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>46107</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>45817</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45803</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>46050</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>46021</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46140</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41414,7 +41414,7 @@
         <v>46056</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>46052</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45870</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45800</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45111</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45824</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>46052</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45800</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45821</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>46140</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>46140</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>46137</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45022</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45925</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>44890</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>46034</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>46064</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44663</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>46065</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>46052</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42929,7 +42929,7 @@
         <v>44915</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>46029</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>46043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>44883</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>46034</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>46035</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>46091</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44712</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>46066</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46106</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46077</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>45111</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45827</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>46063</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45134</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>46029</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45994</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>46064</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46037</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>46141</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>46125</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>46056</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>46027</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45827</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45534</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45827</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>45827</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>46071</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>46073</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>46142</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>46146</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>46104</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>46122</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>46127</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>46125</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>46148</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>46148</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>46134</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>46147</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>46119</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46147</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>46148</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>46148</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46100</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45754</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>46149</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>46153</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>46128</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>46093</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>46093</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>46119</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>46093</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>46088</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46071</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>46071</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45909</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45986</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46043</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46104</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>46154</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>46065</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>46066</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46049</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>46056</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45994</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>46155</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46156</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45838</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45994</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>46044</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45926</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46155</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45758</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>46155</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
         <v>46100</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>46160</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
         <v>46122</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>46161</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>46161</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>45840</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>45840</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45716</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>46161</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45109</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46163</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45719</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45073</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>46164</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>46164</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>46168</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45851</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>46168</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>46044</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>46168</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>46169</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>46169</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>46169</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>46169</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50391,7 +50391,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50464,7 +50464,7 @@
         <v>46085</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>46023</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>46170</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>46170</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50766,7 +50766,7 @@
         <v>45967</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>46170</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46170</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>46170</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>46170</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>45156</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>46171</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46170</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>46175</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>46175</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>46174</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>46174</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>46174</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45603</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46177</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>46177</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51979,7 +51979,7 @@
         <v>46181</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45593</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>45041</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>46156</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45611</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52359,7 +52359,7 @@
         <v>46185</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>46185</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>46185</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>46185</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>46185</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>46189</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>46189</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>46189</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>46076</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53026,7 +53026,7 @@
         <v>45615</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>46188</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>46189</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>46189</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>45981</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>46188</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>46055</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>46190</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>46190</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>46190</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>46190</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>46191</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>44970</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45649</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>46195</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>46196</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>46196</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>46196</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45072</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54468,7 +54468,7 @@
         <v>46198</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54541,7 +54541,7 @@
         <v>45719</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>45620</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>46045</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>46183</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54843,7 +54843,7 @@
         <v>46199</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54921,7 +54921,7 @@
         <v>46198</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>45596</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>45341</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>46199</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55223,7 +55223,7 @@
         <v>45600</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55296,7 +55296,7 @@
         <v>46198</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>46203</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>46203</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45586</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>46203</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>45551</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55744,7 +55744,7 @@
         <v>46205</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55817,7 +55817,7 @@
         <v>46205</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>46204</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>46205</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>45617</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>46104</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56192,7 +56192,7 @@
         <v>45181</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56265,7 +56265,7 @@
         <v>45624</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         <v>45180</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
         <v>45645</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>46206</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56567,7 +56567,7 @@
         <v>46254</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>45152</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>45432</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45441</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56864,7 +56864,7 @@
         <v>46258</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45671</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45757</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>46213</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>45705</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         <v>46052</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>46260</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46216</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>44643</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>45156</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>45243</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>45254</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>46218</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57848,7 +57848,7 @@
         <v>44804</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57921,7 +57921,7 @@
         <v>44725</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57994,7 +57994,7 @@
         <v>44781</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58067,7 +58067,7 @@
         <v>45204</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58140,7 +58140,7 @@
         <v>45134</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>44700</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45265</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58369,7 +58369,7 @@
         <v>46220</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58447,7 +58447,7 @@
         <v>45744</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>45982</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>46098</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58681,7 +58681,7 @@
         <v>46223</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>44797</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>46071</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>46223</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58983,7 +58983,7 @@
         <v>46223</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>46224</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45772</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>46224</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59285,7 +59285,7 @@
         <v>45237</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
         <v>46267</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>46268</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>45254</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>46268</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59665,7 +59665,7 @@
         <v>45230</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59743,7 +59743,7 @@
         <v>46269</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59821,7 +59821,7 @@
         <v>46269</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59899,7 +59899,7 @@
         <v>45240</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59977,7 +59977,7 @@
         <v>46230</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60055,7 +60055,7 @@
         <v>46274</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60128,7 +60128,7 @@
         <v>46275</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60206,7 +60206,7 @@
         <v>46275</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>46232</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46279</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46140</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>45301</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>46140</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>45167</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>45623</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45139</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60883,7 +60883,7 @@
         <v>46283</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45548</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46283</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>46052</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46245</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>46099</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>45132</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         <v>45139</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>44950</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>45600</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>45609</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>46289</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>45258</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>45261</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>44839</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62013,7 +62013,7 @@
         <v>45747</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>45107</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45156</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>44950</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45134</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62393,7 +62393,7 @@
         <v>45134</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62471,7 +62471,7 @@
         <v>45488</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62544,7 +62544,7 @@
         <v>45608</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62622,7 +62622,7 @@
         <v>45608</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45139</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45488</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45223</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>45068</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63002,7 +63002,7 @@
         <v>45678</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63075,7 +63075,7 @@
         <v>45628</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>45211</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63226,7 +63226,7 @@
         <v>45771</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>45771</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63382,7 +63382,7 @@
         <v>45581</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63460,7 +63460,7 @@
         <v>45068</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63538,7 +63538,7 @@
         <v>45551</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45237</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45169</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>45048</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>45156</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45674</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>45252</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64054,7 +64054,7 @@
         <v>44986</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>45544</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45776</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64273,7 +64273,7 @@
         <v>45608</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64346,7 +64346,7 @@
         <v>45617</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64424,7 +64424,7 @@
         <v>45258</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64497,7 +64497,7 @@
         <v>45544</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64570,7 +64570,7 @@
         <v>45786</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64648,7 +64648,7 @@
         <v>45455</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64721,7 +64721,7 @@
         <v>45786</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64799,7 +64799,7 @@
         <v>45478</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64877,7 +64877,7 @@
         <v>44746</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64950,7 +64950,7 @@
         <v>45790</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65023,7 +65023,7 @@
         <v>45593</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45776</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65174,7 +65174,7 @@
         <v>45323</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>45638</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45315</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45699</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65486,7 +65486,7 @@
         <v>44904</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65564,7 +65564,7 @@
         <v>46058</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>46089</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
         <v>46148</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65788,7 +65788,7 @@
         <v>46148</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>46048</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46101</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46170</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46220</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45469</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>46126</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46094</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>46185</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3382,7 +3382,7 @@
         <v>46125</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>46114</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>46132</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46125</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45274</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46038</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4703,7 +4703,7 @@
         <v>45280</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4808,7 +4808,7 @@
         <v>46053</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4917,7 +4917,7 @@
         <v>46056</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>46077</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5127,7 +5127,7 @@
         <v>45247</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>45582</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5347,7 +5347,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>46097</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>46100</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>46101</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>46125</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
         <v>46091</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>46076</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45972</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6343,7 +6343,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>45448</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>45469</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>46009</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>46104</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6892,7 +6892,7 @@
         <v>46085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7006,7 +7006,7 @@
         <v>46077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7116,7 +7116,7 @@
         <v>45022</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         <v>45754</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46282</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>46282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>46283</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44953</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45519</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44479</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44532</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44492</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44795</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44858</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44802</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44881</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44643</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44663</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>45184</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45334</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45203</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10000,7 +10000,7 @@
         <v>45527</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10078,7 +10078,7 @@
         <v>45700</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10151,7 +10151,7 @@
         <v>45330</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44893</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>44820</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44838</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45434</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>44887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>45450</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10672,7 +10672,7 @@
         <v>45443</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>45334</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10818,7 +10818,7 @@
         <v>45455</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
         <v>45366</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10969,7 +10969,7 @@
         <v>45481</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11042,7 +11042,7 @@
         <v>45490</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>45282</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11193,7 +11193,7 @@
         <v>45884</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>45478</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>46021</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>46024</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11568,7 +11568,7 @@
         <v>46027</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11641,7 +11641,7 @@
         <v>46027</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>46027</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>46027</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>46027</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11933,7 +11933,7 @@
         <v>46027</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>46029</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12079,7 +12079,7 @@
         <v>45434</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>45134</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12230,7 +12230,7 @@
         <v>45342</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12303,7 +12303,7 @@
         <v>46028</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>45621</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12449,7 +12449,7 @@
         <v>46029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12522,7 +12522,7 @@
         <v>44659</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12595,7 +12595,7 @@
         <v>45468</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12668,7 +12668,7 @@
         <v>45754</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12741,7 +12741,7 @@
         <v>45534</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12814,7 +12814,7 @@
         <v>45239</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12887,7 +12887,7 @@
         <v>45747</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45596</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13038,7 +13038,7 @@
         <v>44496</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13116,7 +13116,7 @@
         <v>46028</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13189,7 +13189,7 @@
         <v>46029</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>46029</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>46024</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>46031</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13481,7 +13481,7 @@
         <v>46034</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13554,7 +13554,7 @@
         <v>45799</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45888</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13710,7 +13710,7 @@
         <v>46033</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13783,7 +13783,7 @@
         <v>46034</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>46031</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13934,7 +13934,7 @@
         <v>46036</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14007,7 +14007,7 @@
         <v>46036</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>46035</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>45888</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>46036</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>46035</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>46036</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>46036</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>46035</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>46036</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45488</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>46038</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45889</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45800</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14966,7 +14966,7 @@
         <v>45889</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45889</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>46038</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45744</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15263,7 +15263,7 @@
         <v>46037</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15336,7 +15336,7 @@
         <v>45800</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45800</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15492,7 +15492,7 @@
         <v>45184</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>46041</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15643,7 +15643,7 @@
         <v>45891</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>46036</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>45800</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45800</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15950,7 +15950,7 @@
         <v>45800</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16028,7 +16028,7 @@
         <v>45894</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45896</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>46041</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16247,7 +16247,7 @@
         <v>46044</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>44879</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>46044</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16466,7 +16466,7 @@
         <v>45618</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>44889</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>46043</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46043</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>46038</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16831,7 +16831,7 @@
         <v>46036</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>46048</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16977,7 +16977,7 @@
         <v>46048</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17050,7 +17050,7 @@
         <v>46036</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>46044</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>46045</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17269,7 +17269,7 @@
         <v>46045</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>45903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>45903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17498,7 +17498,7 @@
         <v>45903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17571,7 +17571,7 @@
         <v>46049</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17644,7 +17644,7 @@
         <v>46050</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>46049</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17795,7 +17795,7 @@
         <v>46050</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45835</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45905</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>46052</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>46052</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>46052</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>46051</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>46056</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>46056</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
         <v>46053</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18608,7 +18608,7 @@
         <v>45777</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45280</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>46056</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>46056</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18905,7 +18905,7 @@
         <v>46056</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -18978,7 +18978,7 @@
         <v>45911</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>46056</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19129,7 +19129,7 @@
         <v>46055</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19207,7 +19207,7 @@
         <v>45911</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19280,7 +19280,7 @@
         <v>46056</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19353,7 +19353,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>46056</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
         <v>45911</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>46057</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>46062</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19733,7 +19733,7 @@
         <v>46059</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>46062</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19879,7 +19879,7 @@
         <v>45554</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>46062</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>46062</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46064</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46064</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20254,7 +20254,7 @@
         <v>46064</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>46065</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>46065</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20483,7 +20483,7 @@
         <v>45803</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20556,7 +20556,7 @@
         <v>46069</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20629,7 +20629,7 @@
         <v>46056</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20707,7 +20707,7 @@
         <v>46071</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>44950</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20853,7 +20853,7 @@
         <v>46071</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20926,7 +20926,7 @@
         <v>45925</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21004,7 +21004,7 @@
         <v>46071</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21082,7 +21082,7 @@
         <v>46071</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>46071</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21233,7 +21233,7 @@
         <v>46072</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21306,7 +21306,7 @@
         <v>46072</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>46072</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>46072</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>46071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>46071</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>46031</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>46071</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21832,7 +21832,7 @@
         <v>46076</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21910,7 +21910,7 @@
         <v>46077</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -21983,7 +21983,7 @@
         <v>46077</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22061,7 +22061,7 @@
         <v>46077</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>46073</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22212,7 +22212,7 @@
         <v>46077</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22290,7 +22290,7 @@
         <v>46077</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22368,7 +22368,7 @@
         <v>45846</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45107</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>46031</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>46077</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22675,7 +22675,7 @@
         <v>45930</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>46078</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>46079</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>44845</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>45590</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23055,7 +23055,7 @@
         <v>45617</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23133,7 +23133,7 @@
         <v>44501</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23211,7 +23211,7 @@
         <v>45554</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>46079</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23362,7 +23362,7 @@
         <v>45162</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45497</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23513,7 +23513,7 @@
         <v>44525</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>46080</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>45582</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23742,7 +23742,7 @@
         <v>45929</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45929</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>45602</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>45602</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45602</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>44816</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24200,7 +24200,7 @@
         <v>45027</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24278,7 +24278,7 @@
         <v>45608</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24356,7 +24356,7 @@
         <v>45554</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>45644</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45216</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24590,7 +24590,7 @@
         <v>44522</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>46080</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46083</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>46083</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24892,7 +24892,7 @@
         <v>46083</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24970,7 +24970,7 @@
         <v>46080</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25043,7 +25043,7 @@
         <v>45805</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25116,7 +25116,7 @@
         <v>45932</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25194,7 +25194,7 @@
         <v>46126</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25267,7 +25267,7 @@
         <v>46085</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25340,7 +25340,7 @@
         <v>46087</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25413,7 +25413,7 @@
         <v>46089</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>46091</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45937</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25642,7 +25642,7 @@
         <v>45210</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25715,7 +25715,7 @@
         <v>45937</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45937</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45937</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>46093</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>46093</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46092</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45937</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45937</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>46093</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>46094</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>46097</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26528,7 +26528,7 @@
         <v>44950</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26601,7 +26601,7 @@
         <v>46094</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>46094</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>45834</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>46092</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26893,7 +26893,7 @@
         <v>46098</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -26971,7 +26971,7 @@
         <v>46098</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27044,7 +27044,7 @@
         <v>46099</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>46098</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27195,7 +27195,7 @@
         <v>46098</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27273,7 +27273,7 @@
         <v>46098</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>46098</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>46099</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>46100</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27580,7 +27580,7 @@
         <v>46100</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45398</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>46101</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>46101</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27882,7 +27882,7 @@
         <v>45448</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>46104</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>46105</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>46104</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28194,7 +28194,7 @@
         <v>46104</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>46104</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>46104</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>46104</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>46104</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28574,7 +28574,7 @@
         <v>46099</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>45952</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28730,7 +28730,7 @@
         <v>46106</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>46106</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         <v>46099</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28959,7 +28959,7 @@
         <v>46106</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29037,7 +29037,7 @@
         <v>45954</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>46106</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>46106</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29266,7 +29266,7 @@
         <v>45953</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29339,7 +29339,7 @@
         <v>46111</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29412,7 +29412,7 @@
         <v>45954</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29490,7 +29490,7 @@
         <v>46108</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29568,7 +29568,7 @@
         <v>45953</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>46108</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29719,7 +29719,7 @@
         <v>45281</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29792,7 +29792,7 @@
         <v>46111</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29865,7 +29865,7 @@
         <v>46112</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29943,7 +29943,7 @@
         <v>46112</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30021,7 +30021,7 @@
         <v>46112</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30099,7 +30099,7 @@
         <v>45957</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30177,7 +30177,7 @@
         <v>45291</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>46114</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>46114</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30401,7 +30401,7 @@
         <v>46114</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30474,7 +30474,7 @@
         <v>46094</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30552,7 +30552,7 @@
         <v>46114</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>46119</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>46119</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>46118</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30854,7 +30854,7 @@
         <v>45959</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>46121</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>46076</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
         <v>46076</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46077</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31239,7 +31239,7 @@
         <v>46076</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31317,7 +31317,7 @@
         <v>46121</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31390,7 +31390,7 @@
         <v>46121</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31463,7 +31463,7 @@
         <v>46049</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>46076</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45966</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31687,7 +31687,7 @@
         <v>45106</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31765,7 +31765,7 @@
         <v>46125</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31843,7 +31843,7 @@
         <v>45609</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31921,7 +31921,7 @@
         <v>46106</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>46126</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>46105</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32155,7 +32155,7 @@
         <v>46126</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32228,7 +32228,7 @@
         <v>46127</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32301,7 +32301,7 @@
         <v>46127</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32374,7 +32374,7 @@
         <v>45967</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>45967</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45972</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32593,7 +32593,7 @@
         <v>45611</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45674</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45972</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32817,7 +32817,7 @@
         <v>45972</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>45973</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45973</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45973</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45973</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45973</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33255,7 +33255,7 @@
         <v>45973</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>46127</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33406,7 +33406,7 @@
         <v>46098</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>46132</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45973</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33635,7 +33635,7 @@
         <v>45817</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>46132</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45978</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33864,7 +33864,7 @@
         <v>46132</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45978</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>46132</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45978</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>46128</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45978</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34307,7 +34307,7 @@
         <v>46112</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>46112</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34463,7 +34463,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>46132</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34614,7 +34614,7 @@
         <v>46128</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34692,7 +34692,7 @@
         <v>45978</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>45978</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45978</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34911,7 +34911,7 @@
         <v>45975</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34984,7 +34984,7 @@
         <v>46132</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>46132</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45666</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46134</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>46134</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>45510</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>46134</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35510,7 +35510,7 @@
         <v>46133</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35583,7 +35583,7 @@
         <v>46133</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>46133</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35739,7 +35739,7 @@
         <v>46133</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>46136</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35885,7 +35885,7 @@
         <v>45511</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>45986</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36036,7 +36036,7 @@
         <v>45070</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36109,7 +36109,7 @@
         <v>45646</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36182,7 +36182,7 @@
         <v>45986</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36255,7 +36255,7 @@
         <v>45985</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36328,7 +36328,7 @@
         <v>45985</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36401,7 +36401,7 @@
         <v>45645</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36479,7 +36479,7 @@
         <v>45656</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36552,7 +36552,7 @@
         <v>45988</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45727</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>46136</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45817</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>46121</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36927,7 +36927,7 @@
         <v>45699</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>46119</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37078,7 +37078,7 @@
         <v>46114</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45712</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>45994</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45817</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45484</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>46140</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37531,7 +37531,7 @@
         <v>45996</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>46071</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37682,7 +37682,7 @@
         <v>45840</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37760,7 +37760,7 @@
         <v>45995</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45995</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>46048</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37994,7 +37994,7 @@
         <v>46042</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38067,7 +38067,7 @@
         <v>46064</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38140,7 +38140,7 @@
         <v>46000</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38218,7 +38218,7 @@
         <v>46140</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38296,7 +38296,7 @@
         <v>45534</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38374,7 +38374,7 @@
         <v>46137</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38452,7 +38452,7 @@
         <v>46137</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38530,7 +38530,7 @@
         <v>46140</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38608,7 +38608,7 @@
         <v>45111</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38681,7 +38681,7 @@
         <v>46139</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38759,7 +38759,7 @@
         <v>46036</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38832,7 +38832,7 @@
         <v>45819</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38910,7 +38910,7 @@
         <v>46006</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38983,7 +38983,7 @@
         <v>45821</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39056,7 +39056,7 @@
         <v>45946</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>45989</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39212,7 +39212,7 @@
         <v>45819</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>46043</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>46043</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45488</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>46063</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>46042</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>46049</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>46063</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45698</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>46009</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39962,7 +39962,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40040,7 +40040,7 @@
         <v>46138</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>46052</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>46048</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45526</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>46009</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>46098</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40493,7 +40493,7 @@
         <v>46079</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>46013</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>46014</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>46010</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40795,7 +40795,7 @@
         <v>46055</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>46013</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40951,7 +40951,7 @@
         <v>46107</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41029,7 +41029,7 @@
         <v>45817</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45803</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41185,7 +41185,7 @@
         <v>46050</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>46021</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41336,7 +41336,7 @@
         <v>46140</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41414,7 +41414,7 @@
         <v>46056</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41487,7 +41487,7 @@
         <v>46052</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45870</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41633,7 +41633,7 @@
         <v>45800</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41711,7 +41711,7 @@
         <v>45111</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41784,7 +41784,7 @@
         <v>45824</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>46052</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41940,7 +41940,7 @@
         <v>45800</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42013,7 +42013,7 @@
         <v>45821</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42091,7 +42091,7 @@
         <v>46140</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42164,7 +42164,7 @@
         <v>46140</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42242,7 +42242,7 @@
         <v>46137</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45022</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42393,7 +42393,7 @@
         <v>45925</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42471,7 +42471,7 @@
         <v>44890</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42544,7 +42544,7 @@
         <v>46034</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42622,7 +42622,7 @@
         <v>46064</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42700,7 +42700,7 @@
         <v>44663</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42778,7 +42778,7 @@
         <v>46065</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42856,7 +42856,7 @@
         <v>46052</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42929,7 +42929,7 @@
         <v>44915</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43002,7 +43002,7 @@
         <v>46029</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>46043</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43148,7 +43148,7 @@
         <v>44883</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>46034</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43299,7 +43299,7 @@
         <v>46035</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43372,7 +43372,7 @@
         <v>46091</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>44712</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>46066</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>46106</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46077</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>45111</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43820,7 +43820,7 @@
         <v>45827</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43893,7 +43893,7 @@
         <v>46063</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43971,7 +43971,7 @@
         <v>45134</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>46029</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44122,7 +44122,7 @@
         <v>45994</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>46064</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>46037</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44341,7 +44341,7 @@
         <v>46141</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44419,7 +44419,7 @@
         <v>46125</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44497,7 +44497,7 @@
         <v>46056</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>46027</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44653,7 +44653,7 @@
         <v>45827</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44731,7 +44731,7 @@
         <v>45534</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44804,7 +44804,7 @@
         <v>45827</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44882,7 +44882,7 @@
         <v>45827</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44960,7 +44960,7 @@
         <v>46071</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45038,7 +45038,7 @@
         <v>46073</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45116,7 +45116,7 @@
         <v>46142</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>46146</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>46104</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45350,7 +45350,7 @@
         <v>46122</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45428,7 +45428,7 @@
         <v>46127</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45506,7 +45506,7 @@
         <v>46125</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45584,7 +45584,7 @@
         <v>46148</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45662,7 +45662,7 @@
         <v>46148</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45740,7 +45740,7 @@
         <v>46134</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45818,7 +45818,7 @@
         <v>46147</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>46119</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45974,7 +45974,7 @@
         <v>46147</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>46148</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>46148</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46100</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46281,7 +46281,7 @@
         <v>45754</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46354,7 +46354,7 @@
         <v>46149</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>46153</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>46128</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46578,7 +46578,7 @@
         <v>46093</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46651,7 +46651,7 @@
         <v>46093</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46729,7 +46729,7 @@
         <v>46119</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>46093</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>46088</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46953,7 +46953,7 @@
         <v>46071</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47031,7 +47031,7 @@
         <v>46071</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47104,7 +47104,7 @@
         <v>45909</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45986</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46043</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47401,7 +47401,7 @@
         <v>46104</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47479,7 +47479,7 @@
         <v>46154</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47552,7 +47552,7 @@
         <v>46065</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>46066</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46049</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>46056</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>45994</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>46155</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46156</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>45838</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>45994</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>46044</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45926</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46155</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>45758</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48511,7 +48511,7 @@
         <v>46155</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48584,7 +48584,7 @@
         <v>46100</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>46160</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48730,7 +48730,7 @@
         <v>46122</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48803,7 +48803,7 @@
         <v>46161</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>46161</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48949,7 +48949,7 @@
         <v>45840</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>45840</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45716</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>46161</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49251,7 +49251,7 @@
         <v>45109</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49324,7 +49324,7 @@
         <v>46163</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>45719</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45073</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>46164</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>46164</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>46168</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45851</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49855,7 +49855,7 @@
         <v>46168</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49933,7 +49933,7 @@
         <v>46044</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50006,7 +50006,7 @@
         <v>46168</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>46169</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50157,7 +50157,7 @@
         <v>46169</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>46169</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50313,7 +50313,7 @@
         <v>46169</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50391,7 +50391,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50464,7 +50464,7 @@
         <v>46085</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>46023</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>46170</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>46170</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50766,7 +50766,7 @@
         <v>45967</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>46170</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46170</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>46170</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51068,7 +51068,7 @@
         <v>46170</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51146,7 +51146,7 @@
         <v>45156</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>46171</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51297,7 +51297,7 @@
         <v>46170</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>46175</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51453,7 +51453,7 @@
         <v>46175</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51531,7 +51531,7 @@
         <v>46174</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51604,7 +51604,7 @@
         <v>46174</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51677,7 +51677,7 @@
         <v>46174</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51750,7 +51750,7 @@
         <v>45603</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51823,7 +51823,7 @@
         <v>46177</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51901,7 +51901,7 @@
         <v>46177</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51979,7 +51979,7 @@
         <v>46181</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52052,7 +52052,7 @@
         <v>45593</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52125,7 +52125,7 @@
         <v>45041</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52203,7 +52203,7 @@
         <v>46156</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52281,7 +52281,7 @@
         <v>45611</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52359,7 +52359,7 @@
         <v>46185</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52432,7 +52432,7 @@
         <v>46185</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52505,7 +52505,7 @@
         <v>46185</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52578,7 +52578,7 @@
         <v>46185</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52651,7 +52651,7 @@
         <v>46185</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52724,7 +52724,7 @@
         <v>46189</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52802,7 +52802,7 @@
         <v>46189</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52875,7 +52875,7 @@
         <v>46189</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52948,7 +52948,7 @@
         <v>46076</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53026,7 +53026,7 @@
         <v>45615</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53099,7 +53099,7 @@
         <v>46188</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53177,7 +53177,7 @@
         <v>46189</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53250,7 +53250,7 @@
         <v>46189</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53328,7 +53328,7 @@
         <v>45981</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53406,7 +53406,7 @@
         <v>46188</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53484,7 +53484,7 @@
         <v>46055</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53562,7 +53562,7 @@
         <v>46190</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53635,7 +53635,7 @@
         <v>46190</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53708,7 +53708,7 @@
         <v>46190</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53786,7 +53786,7 @@
         <v>46190</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53859,7 +53859,7 @@
         <v>46191</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53937,7 +53937,7 @@
         <v>44970</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54010,7 +54010,7 @@
         <v>45649</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54083,7 +54083,7 @@
         <v>46195</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54161,7 +54161,7 @@
         <v>46196</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54239,7 +54239,7 @@
         <v>46196</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54317,7 +54317,7 @@
         <v>46196</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54395,7 +54395,7 @@
         <v>45072</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54468,7 +54468,7 @@
         <v>46198</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54541,7 +54541,7 @@
         <v>45719</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>45620</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54692,7 +54692,7 @@
         <v>46045</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54765,7 +54765,7 @@
         <v>46183</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54843,7 +54843,7 @@
         <v>46199</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54921,7 +54921,7 @@
         <v>46198</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54999,7 +54999,7 @@
         <v>45596</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55072,7 +55072,7 @@
         <v>45341</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55145,7 +55145,7 @@
         <v>46199</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55223,7 +55223,7 @@
         <v>45600</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55296,7 +55296,7 @@
         <v>46198</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>46203</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55447,7 +55447,7 @@
         <v>46203</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55525,7 +55525,7 @@
         <v>45586</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>46203</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>45551</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55744,7 +55744,7 @@
         <v>46205</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55817,7 +55817,7 @@
         <v>46205</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55890,7 +55890,7 @@
         <v>46204</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55968,7 +55968,7 @@
         <v>46205</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56041,7 +56041,7 @@
         <v>45617</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56119,7 +56119,7 @@
         <v>46104</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56192,7 +56192,7 @@
         <v>45181</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56265,7 +56265,7 @@
         <v>45624</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56343,7 +56343,7 @@
         <v>45180</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
         <v>45645</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56494,7 +56494,7 @@
         <v>46206</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56567,7 +56567,7 @@
         <v>46254</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>45152</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>45432</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45441</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56864,7 +56864,7 @@
         <v>46258</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45671</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45757</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57098,7 +57098,7 @@
         <v>46213</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>45705</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57244,7 +57244,7 @@
         <v>46052</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57317,7 +57317,7 @@
         <v>46260</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46216</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>44643</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57546,7 +57546,7 @@
         <v>45156</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>45243</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57697,7 +57697,7 @@
         <v>45254</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57770,7 +57770,7 @@
         <v>46218</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57848,7 +57848,7 @@
         <v>44804</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57921,7 +57921,7 @@
         <v>44725</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57994,7 +57994,7 @@
         <v>44781</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58067,7 +58067,7 @@
         <v>45204</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58140,7 +58140,7 @@
         <v>45134</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58218,7 +58218,7 @@
         <v>44700</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58296,7 +58296,7 @@
         <v>45265</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58369,7 +58369,7 @@
         <v>46220</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58447,7 +58447,7 @@
         <v>45744</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58525,7 +58525,7 @@
         <v>45982</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58603,7 +58603,7 @@
         <v>46098</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58681,7 +58681,7 @@
         <v>46223</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58759,7 +58759,7 @@
         <v>44797</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58832,7 +58832,7 @@
         <v>46071</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58910,7 +58910,7 @@
         <v>46223</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58983,7 +58983,7 @@
         <v>46223</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59056,7 +59056,7 @@
         <v>46224</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59134,7 +59134,7 @@
         <v>45772</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59207,7 +59207,7 @@
         <v>46224</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59285,7 +59285,7 @@
         <v>45237</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59358,7 +59358,7 @@
         <v>46267</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59436,7 +59436,7 @@
         <v>46268</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59514,7 +59514,7 @@
         <v>45254</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59587,7 +59587,7 @@
         <v>46268</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59665,7 +59665,7 @@
         <v>45230</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59743,7 +59743,7 @@
         <v>46269</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59821,7 +59821,7 @@
         <v>46269</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59899,7 +59899,7 @@
         <v>45240</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59977,7 +59977,7 @@
         <v>46230</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60055,7 +60055,7 @@
         <v>46274</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60128,7 +60128,7 @@
         <v>46275</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60206,7 +60206,7 @@
         <v>46275</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>46232</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60362,7 +60362,7 @@
         <v>46279</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>46140</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60513,7 +60513,7 @@
         <v>45301</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60586,7 +60586,7 @@
         <v>46140</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60659,7 +60659,7 @@
         <v>45167</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>45623</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60810,7 +60810,7 @@
         <v>45139</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60883,7 +60883,7 @@
         <v>46283</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60961,7 +60961,7 @@
         <v>45548</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61039,7 +61039,7 @@
         <v>46283</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61112,7 +61112,7 @@
         <v>46052</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46245</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>46099</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61336,7 +61336,7 @@
         <v>45132</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61414,7 +61414,7 @@
         <v>45139</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61487,7 +61487,7 @@
         <v>44950</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61560,7 +61560,7 @@
         <v>45600</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61633,7 +61633,7 @@
         <v>45609</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61711,7 +61711,7 @@
         <v>46289</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61789,7 +61789,7 @@
         <v>45258</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61862,7 +61862,7 @@
         <v>45261</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61935,7 +61935,7 @@
         <v>44839</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62013,7 +62013,7 @@
         <v>45747</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62086,7 +62086,7 @@
         <v>45107</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62164,7 +62164,7 @@
         <v>45156</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62242,7 +62242,7 @@
         <v>44950</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62315,7 +62315,7 @@
         <v>45134</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62393,7 +62393,7 @@
         <v>45134</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62471,7 +62471,7 @@
         <v>45488</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62544,7 +62544,7 @@
         <v>45608</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62622,7 +62622,7 @@
         <v>45608</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45139</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45488</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62846,7 +62846,7 @@
         <v>45223</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>45068</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63002,7 +63002,7 @@
         <v>45678</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63075,7 +63075,7 @@
         <v>45628</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>45211</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63226,7 +63226,7 @@
         <v>45771</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63304,7 +63304,7 @@
         <v>45771</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63382,7 +63382,7 @@
         <v>45581</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63460,7 +63460,7 @@
         <v>45068</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63538,7 +63538,7 @@
         <v>45551</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63611,7 +63611,7 @@
         <v>45237</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45169</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>45048</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>45156</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45674</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>45252</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64054,7 +64054,7 @@
         <v>44986</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>45544</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45776</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64273,7 +64273,7 @@
         <v>45608</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64346,7 +64346,7 @@
         <v>45617</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64424,7 +64424,7 @@
         <v>45258</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64497,7 +64497,7 @@
         <v>45544</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64570,7 +64570,7 @@
         <v>45786</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64648,7 +64648,7 @@
         <v>45455</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64721,7 +64721,7 @@
         <v>45786</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64799,7 +64799,7 @@
         <v>45478</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64877,7 +64877,7 @@
         <v>44746</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64950,7 +64950,7 @@
         <v>45790</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65023,7 +65023,7 @@
         <v>45593</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45776</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65174,7 +65174,7 @@
         <v>45323</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>45638</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65330,7 +65330,7 @@
         <v>45315</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65408,7 +65408,7 @@
         <v>45699</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65486,7 +65486,7 @@
         <v>44904</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65564,7 +65564,7 @@
         <v>46058</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>46089</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65715,7 +65715,7 @@
         <v>46148</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65788,7 +65788,7 @@
         <v>46148</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>46048</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46101</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46170</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46220</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45469</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>46126</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46094</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>46125</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>46114</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>46132</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46125</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45274</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45280</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>46009</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45022</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45754</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>46038</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>46053</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>46056</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45247</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>46077</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46097</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>46101</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>46091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46076</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45448</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45469</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>46139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>46104</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>46085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46283</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>46282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>46282</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44953</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45519</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44479</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44532</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44492</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44795</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44858</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44802</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44881</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44643</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44663</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>44889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45156</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45611</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45534</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45180</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44890</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44804</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45548</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44879</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45211</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45617</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45252</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45478</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45617</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44746</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45341</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45645</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45799</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46006</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45989</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>46009</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>46013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>46013</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>46010</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>46014</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46021</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45889</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45889</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45891</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45744</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44950</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45772</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>46027</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46027</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>46027</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>46027</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>46027</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>46024</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>46027</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>46029</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45254</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45894</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46028</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>46028</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>46029</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>46024</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>46029</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>46031</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45896</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>46031</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46034</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>46033</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>46035</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>46035</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45621</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>46035</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45903</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45903</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45903</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46037</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46036</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>46036</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>46036</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46036</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46036</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>46036</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45905</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45468</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>46041</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45593</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45835</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>46041</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46038</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>46038</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>46043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45434</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45911</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45777</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>44797</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45754</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45911</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>44659</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>46044</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>46044</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46045</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45911</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46036</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>46044</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45282</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>46045</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45434</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>46036</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>46049</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>46049</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>44986</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>46048</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45596</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>46050</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45747</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45803</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45618</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45800</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45800</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45800</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45800</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45800</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46051</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>46050</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45805</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>46051</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>46052</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>46053</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>46052</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>46052</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45611</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>46055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45132</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45925</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>46056</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>46056</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>46057</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>46056</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>46056</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45644</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45602</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45027</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45602</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45602</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>46056</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>46056</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>46056</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>46056</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45608</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45162</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44522</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45846</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45554</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45216</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45554</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>44816</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45590</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>46059</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45929</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44501</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45617</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>44845</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44525</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45582</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45107</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45930</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>46062</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45932</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>46062</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>46062</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>46062</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>46065</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44950</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>46064</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>46064</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>46065</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>46064</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45937</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45937</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46069</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45937</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>46071</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>46071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46071</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>46071</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>46071</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>46071</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>46071</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45937</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>46071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45937</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>46031</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>46072</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>46072</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>46072</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>46072</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>46073</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>46077</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45834</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45432</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46078</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>46077</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>46077</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>46077</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>46031</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>46076</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46077</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45443</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46077</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>46079</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>46080</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46080</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46080</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46079</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45953</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>46126</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>46083</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46083</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45952</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45953</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>46083</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>44887</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>46085</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45957</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45954</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45954</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>46087</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45757</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45959</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46089</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>46092</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45817</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>46093</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46094</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45817</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45966</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>46094</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45967</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45967</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>46093</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>46094</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45048</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>46093</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45488</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45581</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45041</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>46098</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45817</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>46098</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46098</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46092</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46098</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>46097</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>46098</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>46099</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45510</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45972</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45972</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45111</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45973</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45973</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45972</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>46098</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46100</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46100</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>46099</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45973</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46104</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>46104</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45975</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>46104</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>46101</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>46104</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46104</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46104</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>46106</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45978</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>46106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45978</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45978</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45978</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>46106</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>45978</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>46099</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>46105</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45819</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45978</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45978</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45819</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45223</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>46106</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>46106</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>46108</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>46108</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46111</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45985</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>46112</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>46112</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>46112</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45985</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46111</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45821</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45986</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>46114</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>46114</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45986</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>46114</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>46114</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>46094</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>46076</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45824</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45988</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46076</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46077</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46119</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46076</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>46119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>46118</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>46076</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>46121</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>46121</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>46121</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45827</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45827</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45184</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>45995</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46049</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45995</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>46125</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45994</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46126</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>46126</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>46098</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>46127</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45490</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>46105</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45827</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>46127</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46112</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45139</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46128</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45996</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>46112</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>46128</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46106</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>46127</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45705</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46000</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>46132</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>46133</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>46132</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>46133</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>46132</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>46132</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>46132</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>46133</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46132</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45181</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46132</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>46132</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45608</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45608</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44700</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>46134</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>46134</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>46114</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>46119</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>46133</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>46134</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45204</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45334</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>46043</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>46064</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45645</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>46137</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45478</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45800</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>45441</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45838</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46049</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>46106</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45254</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45946</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45840</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>44663</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>45450</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45840</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45925</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45366</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>46048</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>46055</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45109</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>46029</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45870</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45719</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45073</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>46050</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45488</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45656</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>44712</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>46137</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>46137</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45301</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45237</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>46043</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45851</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>45803</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45800</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>46052</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>46052</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44915</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45821</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45747</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>46036</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>45488</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>46021</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>46139</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>46107</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>46136</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>46136</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>46064</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>46138</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>46042</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>46065</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45712</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>46034</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>45700</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45840</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>46052</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45817</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>45342</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>46140</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>46106</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>46064</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>44970</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>46035</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>46071</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>46048</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>46140</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46140</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45111</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45111</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>46027</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>46056</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>46042</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>46063</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45754</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>46140</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>46141</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45330</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>46071</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45488</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>46098</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45526</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>46140</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>46079</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45106</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>46125</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>46091</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>46029</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>46063</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46043</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>46037</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>46073</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>46056</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>46052</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>46034</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>46077</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>46140</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46063</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>46104</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45674</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45994</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46146</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46127</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>46122</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>46125</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>46147</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>46147</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>46148</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>46148</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>46134</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>46149</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>46148</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>46148</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>46100</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45291</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>46119</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46066</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45624</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46071</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>46128</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>46153</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45551</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45986</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46043</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45926</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>46155</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>46154</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>46093</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>46119</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>46056</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45909</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46155</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>46104</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>46088</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>46044</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>46049</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>46093</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46093</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>45994</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>45994</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>46156</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>46122</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>46100</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>46161</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>46160</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>46161</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45649</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>46163</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45716</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>45600</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>46164</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46164</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46044</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>46169</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>46169</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>46169</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>46168</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45719</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>46168</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>46169</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>46168</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>46170</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         <v>46170</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>46170</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46170</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>46170</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46170</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45455</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>46170</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>46085</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45551</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>46023</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>46174</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>45967</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46174</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>46174</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>46171</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>44883</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>45586</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>46175</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>46175</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         <v>45603</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45884</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>46177</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>46177</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52495,7 +52495,7 @@
         <v>45554</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>46181</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45620</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45203</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>46185</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>46185</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>46188</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>46188</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53094,7 +53094,7 @@
         <v>46185</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>46185</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>46185</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>46190</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>45981</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>46076</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45398</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>46190</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>46190</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>45615</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>46189</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>46189</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45134</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45134</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>46189</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>46189</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46189</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>45646</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>46191</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>44839</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>46055</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>46196</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>46196</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>46196</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54906,7 +54906,7 @@
         <v>46195</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54984,7 +54984,7 @@
         <v>44496</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>46198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>46198</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55213,7 +55213,7 @@
         <v>46198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45699</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>46199</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45184</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>46199</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>46045</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>46183</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>46104</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>46204</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>46203</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>46203</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>46203</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56129,7 +56129,7 @@
         <v>46205</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56202,7 +56202,7 @@
         <v>45511</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>46206</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>44820</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>46205</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45152</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>44643</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>44893</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>46205</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45107</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45243</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45671</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45210</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>46216</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>46258</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         <v>46213</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>45593</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46260</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>46218</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>45678</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>46071</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>46220</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         <v>45156</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>46098</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57936,7 +57936,7 @@
         <v>45674</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58009,7 +58009,7 @@
         <v>45982</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>46267</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>46223</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>46223</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58311,7 +58311,7 @@
         <v>46224</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>46223</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>46224</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>46268</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>46269</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>45527</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>46269</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>46268</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>44781</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>46230</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>45261</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>46232</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59237,7 +59237,7 @@
         <v>46275</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>46274</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>46275</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59466,7 +59466,7 @@
         <v>46140</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>46279</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>46140</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>46283</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>46283</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>45758</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45534</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59987,7 +59987,7 @@
         <v>45334</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
         <v>45609</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>45022</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         <v>45139</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>46052</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60357,7 +60357,7 @@
         <v>45237</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60430,7 +60430,7 @@
         <v>45698</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>46289</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45727</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>46245</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>46099</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>45497</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>46293</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>46293</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>44838</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>46293</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46104</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>45156</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>46293</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45134</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>45134</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61575,7 +61575,7 @@
         <v>45596</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61648,7 +61648,7 @@
         <v>45240</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45609</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>45139</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>46052</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>46121</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62023,7 +62023,7 @@
         <v>46065</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>46071</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>46066</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62247,7 +62247,7 @@
         <v>45544</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62320,7 +62320,7 @@
         <v>46038</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62393,7 +62393,7 @@
         <v>46101</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62471,7 +62471,7 @@
         <v>46156</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62549,7 +62549,7 @@
         <v>46297</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62622,7 +62622,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45481</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45623</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62851,7 +62851,7 @@
         <v>46036</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>46142</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63002,7 +63002,7 @@
         <v>44725</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63075,7 +63075,7 @@
         <v>45281</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>44950</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         <v>45068</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45771</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45068</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>45534</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>45230</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45156</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45070</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>45628</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>45771</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45484</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>45280</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64054,7 +64054,7 @@
         <v>45239</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>45600</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45744</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64278,7 +64278,7 @@
         <v>45072</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64351,7 +64351,7 @@
         <v>45448</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>45666</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>45265</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64575,7 +64575,7 @@
         <v>45134</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64653,7 +64653,7 @@
         <v>44950</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         <v>45776</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64799,7 +64799,7 @@
         <v>45455</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64872,7 +64872,7 @@
         <v>45608</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64945,7 +64945,7 @@
         <v>45544</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65018,7 +65018,7 @@
         <v>45258</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>45786</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65169,7 +65169,7 @@
         <v>45786</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65247,7 +65247,7 @@
         <v>45323</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65325,7 +65325,7 @@
         <v>45638</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65403,7 +65403,7 @@
         <v>45315</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45699</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65559,7 +65559,7 @@
         <v>44904</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>46058</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65710,7 +65710,7 @@
         <v>46089</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65788,7 +65788,7 @@
         <v>46148</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>46148</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>46048</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>46293</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66085,7 +66085,7 @@
         <v>46255</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>46044</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1088,7 +1088,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1204,7 +1204,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>46099</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>45106</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46101</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>45841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46170</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46220</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>45469</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
         <v>46126</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>45812</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>46094</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>46125</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>46185</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>46153</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
         <v>46036</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>46044</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>46114</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>46132</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>46125</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>46139</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>44587</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>45274</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>45280</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>46009</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4804,7 +4804,7 @@
         <v>45022</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4918,7 +4918,7 @@
         <v>45754</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5023,7 +5023,7 @@
         <v>46038</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5132,7 +5132,7 @@
         <v>46053</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>46056</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44496</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5456,7 +5456,7 @@
         <v>45247</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45582</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5676,7 +5676,7 @@
         <v>46077</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5781,7 +5781,7 @@
         <v>46097</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
         <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>46100</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6106,7 +6106,7 @@
         <v>46101</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         <v>46125</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6334,7 +6334,7 @@
         <v>46091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>46076</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>45448</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6667,7 +6667,7 @@
         <v>46070</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45469</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>46139</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>46104</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>46085</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46077</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46283</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>46282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>46282</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         <v>44953</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>45519</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7883,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8208,7 +8208,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8359,7 +8359,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44479</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8505,7 +8505,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8578,7 +8578,7 @@
         <v>44532</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8651,7 +8651,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8802,7 +8802,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8875,7 +8875,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44492</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9026,7 +9026,7 @@
         <v>44795</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9099,7 +9099,7 @@
         <v>44858</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9177,7 +9177,7 @@
         <v>44802</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44881</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9323,7 +9323,7 @@
         <v>44705</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9396,7 +9396,7 @@
         <v>44872</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9474,7 +9474,7 @@
         <v>44532</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>44643</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9625,7 +9625,7 @@
         <v>44663</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9703,7 +9703,7 @@
         <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>44889</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
         <v>45156</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9927,7 +9927,7 @@
         <v>45611</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10005,7 +10005,7 @@
         <v>45534</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>45180</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10156,7 +10156,7 @@
         <v>44890</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44804</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10302,7 +10302,7 @@
         <v>45548</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>44879</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10453,7 +10453,7 @@
         <v>45211</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
         <v>45617</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10609,7 +10609,7 @@
         <v>45167</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10682,7 +10682,7 @@
         <v>45252</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10755,7 +10755,7 @@
         <v>45478</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10833,7 +10833,7 @@
         <v>45617</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10911,7 +10911,7 @@
         <v>44746</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10984,7 +10984,7 @@
         <v>45341</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11057,7 +11057,7 @@
         <v>45645</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11135,7 +11135,7 @@
         <v>45799</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11213,7 +11213,7 @@
         <v>46006</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45989</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>46009</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>46009</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45776</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>46013</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11671,7 +11671,7 @@
         <v>46013</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>46010</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11822,7 +11822,7 @@
         <v>46009</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>46014</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11973,7 +11973,7 @@
         <v>46021</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>45889</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>45888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12197,7 +12197,7 @@
         <v>45889</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12270,7 +12270,7 @@
         <v>45889</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12343,7 +12343,7 @@
         <v>45891</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12421,7 +12421,7 @@
         <v>45744</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44950</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45772</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>46027</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>46027</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>46027</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>46027</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>46027</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>46024</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13083,7 +13083,7 @@
         <v>46027</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13156,7 +13156,7 @@
         <v>46029</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>45254</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13302,7 +13302,7 @@
         <v>45894</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13375,7 +13375,7 @@
         <v>46028</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13448,7 +13448,7 @@
         <v>46028</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13521,7 +13521,7 @@
         <v>46029</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13594,7 +13594,7 @@
         <v>46024</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13667,7 +13667,7 @@
         <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>46029</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13813,7 +13813,7 @@
         <v>46031</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13886,7 +13886,7 @@
         <v>45896</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45790</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>46031</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>46034</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14183,7 +14183,7 @@
         <v>46034</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14256,7 +14256,7 @@
         <v>46033</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>46035</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14402,7 +14402,7 @@
         <v>46035</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45621</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14548,7 +14548,7 @@
         <v>46035</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14621,7 +14621,7 @@
         <v>45903</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14694,7 +14694,7 @@
         <v>45903</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14767,7 +14767,7 @@
         <v>45903</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>46037</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>46036</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>46036</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>46036</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>46036</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15210,7 +15210,7 @@
         <v>46036</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>46036</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45905</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>45468</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>46041</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15575,7 +15575,7 @@
         <v>45593</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15648,7 +15648,7 @@
         <v>45835</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15721,7 +15721,7 @@
         <v>46041</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>46038</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>46038</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>46043</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>46043</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>45434</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16159,7 +16159,7 @@
         <v>45911</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45777</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>44797</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>45754</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>45911</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>44659</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>46044</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>46044</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46045</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16826,7 +16826,7 @@
         <v>45911</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45911</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>46036</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17055,7 +17055,7 @@
         <v>46044</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17128,7 +17128,7 @@
         <v>45282</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17201,7 +17201,7 @@
         <v>46045</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17274,7 +17274,7 @@
         <v>45434</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17347,7 +17347,7 @@
         <v>46036</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17420,7 +17420,7 @@
         <v>46049</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17493,7 +17493,7 @@
         <v>46049</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>44986</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17639,7 +17639,7 @@
         <v>46048</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17712,7 +17712,7 @@
         <v>46048</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17785,7 +17785,7 @@
         <v>45596</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>46050</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45747</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45803</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45618</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>45800</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45800</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45800</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>45800</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18472,7 +18472,7 @@
         <v>45800</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45800</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>46051</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>46050</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45805</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>46051</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>46052</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>46053</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>46052</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>46052</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45611</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>46055</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45132</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>45925</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>46056</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>46056</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>46057</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>46056</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19836,7 +19836,7 @@
         <v>46056</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45644</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>45602</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>45027</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45602</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45602</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>46056</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20372,7 +20372,7 @@
         <v>46056</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>46056</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>46056</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>45608</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>45162</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20747,7 +20747,7 @@
         <v>44522</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>45846</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45554</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -20981,7 +20981,7 @@
         <v>45216</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45554</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21137,7 +21137,7 @@
         <v>44816</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21215,7 +21215,7 @@
         <v>45590</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>46059</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21366,7 +21366,7 @@
         <v>45929</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45929</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>44501</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45617</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>44845</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>44525</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45582</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45107</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
         <v>45930</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>46062</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45932</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22204,7 +22204,7 @@
         <v>46062</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22277,7 +22277,7 @@
         <v>46062</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>46062</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>46065</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22506,7 +22506,7 @@
         <v>44950</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>46064</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22652,7 +22652,7 @@
         <v>46064</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22725,7 +22725,7 @@
         <v>46065</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22798,7 +22798,7 @@
         <v>46064</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22876,7 +22876,7 @@
         <v>45937</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45937</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23022,7 +23022,7 @@
         <v>46069</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23095,7 +23095,7 @@
         <v>45937</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23168,7 +23168,7 @@
         <v>46071</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23246,7 +23246,7 @@
         <v>46071</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23324,7 +23324,7 @@
         <v>46071</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23397,7 +23397,7 @@
         <v>46071</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>46071</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23548,7 +23548,7 @@
         <v>46071</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>46071</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23694,7 +23694,7 @@
         <v>45937</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23767,7 +23767,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>46071</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>45937</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -23991,7 +23991,7 @@
         <v>46056</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24069,7 +24069,7 @@
         <v>46031</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24142,7 +24142,7 @@
         <v>46072</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>46072</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24288,7 +24288,7 @@
         <v>46072</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>46072</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>46073</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>46077</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45834</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24668,7 +24668,7 @@
         <v>45432</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24741,7 +24741,7 @@
         <v>46078</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24819,7 +24819,7 @@
         <v>46077</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>46077</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>46077</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>46031</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>46076</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>46077</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45443</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>46077</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25428,7 +25428,7 @@
         <v>46079</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25501,7 +25501,7 @@
         <v>46080</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25574,7 +25574,7 @@
         <v>46080</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25647,7 +25647,7 @@
         <v>45169</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25720,7 +25720,7 @@
         <v>46080</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>46079</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45953</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -25939,7 +25939,7 @@
         <v>46126</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>46083</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26085,7 +26085,7 @@
         <v>46083</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26163,7 +26163,7 @@
         <v>45952</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45953</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26314,7 +26314,7 @@
         <v>46083</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>44887</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>46085</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45957</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45954</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26694,7 +26694,7 @@
         <v>45954</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26772,7 +26772,7 @@
         <v>46087</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26845,7 +26845,7 @@
         <v>45757</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45959</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>46089</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>46092</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27152,7 +27152,7 @@
         <v>46091</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45817</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27303,7 +27303,7 @@
         <v>46093</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27376,7 +27376,7 @@
         <v>46094</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         <v>45817</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45966</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27600,7 +27600,7 @@
         <v>46094</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27673,7 +27673,7 @@
         <v>45967</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27746,7 +27746,7 @@
         <v>45967</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27819,7 +27819,7 @@
         <v>46093</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27892,7 +27892,7 @@
         <v>46094</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -27965,7 +27965,7 @@
         <v>45048</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28038,7 +28038,7 @@
         <v>46093</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28116,7 +28116,7 @@
         <v>45488</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28189,7 +28189,7 @@
         <v>45581</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28267,7 +28267,7 @@
         <v>45041</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28345,7 +28345,7 @@
         <v>46098</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28423,7 +28423,7 @@
         <v>45817</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28501,7 +28501,7 @@
         <v>46098</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28579,7 +28579,7 @@
         <v>46098</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28652,7 +28652,7 @@
         <v>46092</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28725,7 +28725,7 @@
         <v>46098</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28803,7 +28803,7 @@
         <v>46097</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28876,7 +28876,7 @@
         <v>46098</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>46099</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45510</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29100,7 +29100,7 @@
         <v>45972</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45973</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>45973</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45972</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29392,7 +29392,7 @@
         <v>45111</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45973</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29538,7 +29538,7 @@
         <v>45973</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>45973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29684,7 +29684,7 @@
         <v>45972</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>46098</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29835,7 +29835,7 @@
         <v>46100</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29908,7 +29908,7 @@
         <v>46100</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>46099</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30059,7 +30059,7 @@
         <v>45973</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30137,7 +30137,7 @@
         <v>45973</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30210,7 +30210,7 @@
         <v>46104</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>46104</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30361,7 +30361,7 @@
         <v>45975</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>46104</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>46101</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>46104</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>46104</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30741,7 +30741,7 @@
         <v>46104</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30819,7 +30819,7 @@
         <v>46106</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>45978</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -30970,7 +30970,7 @@
         <v>46106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31043,7 +31043,7 @@
         <v>45978</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31116,7 +31116,7 @@
         <v>45978</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45978</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31262,7 +31262,7 @@
         <v>46106</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>45978</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31408,7 +31408,7 @@
         <v>46099</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31486,7 +31486,7 @@
         <v>46105</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31564,7 +31564,7 @@
         <v>45819</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45978</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31715,7 +31715,7 @@
         <v>45978</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31788,7 +31788,7 @@
         <v>45819</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31866,7 +31866,7 @@
         <v>45223</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -31944,7 +31944,7 @@
         <v>46106</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32022,7 +32022,7 @@
         <v>46106</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32100,7 +32100,7 @@
         <v>46108</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32178,7 +32178,7 @@
         <v>46108</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32256,7 +32256,7 @@
         <v>46111</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45985</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>46112</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>46112</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>46112</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45985</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46111</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45821</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32860,7 +32860,7 @@
         <v>45986</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>46114</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33016,7 +33016,7 @@
         <v>46114</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45986</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33162,7 +33162,7 @@
         <v>46114</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33240,7 +33240,7 @@
         <v>46114</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33313,7 +33313,7 @@
         <v>46094</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>46076</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45824</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33547,7 +33547,7 @@
         <v>45988</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33625,7 +33625,7 @@
         <v>46076</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33703,7 +33703,7 @@
         <v>46077</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33781,7 +33781,7 @@
         <v>46119</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33854,7 +33854,7 @@
         <v>46076</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33932,7 +33932,7 @@
         <v>46119</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34010,7 +34010,7 @@
         <v>46118</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34083,7 +34083,7 @@
         <v>46076</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45827</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34239,7 +34239,7 @@
         <v>46121</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34312,7 +34312,7 @@
         <v>46121</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34385,7 +34385,7 @@
         <v>46121</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34458,7 +34458,7 @@
         <v>45827</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34531,7 +34531,7 @@
         <v>45827</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34609,7 +34609,7 @@
         <v>45184</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34687,7 +34687,7 @@
         <v>45995</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34765,7 +34765,7 @@
         <v>46049</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34838,7 +34838,7 @@
         <v>45995</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34916,7 +34916,7 @@
         <v>46125</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>45994</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>46126</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35145,7 +35145,7 @@
         <v>46126</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35223,7 +35223,7 @@
         <v>46098</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>46127</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35374,7 +35374,7 @@
         <v>45490</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35452,7 +35452,7 @@
         <v>46105</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45827</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35608,7 +35608,7 @@
         <v>46127</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46112</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35759,7 +35759,7 @@
         <v>45139</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>46128</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45996</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35983,7 +35983,7 @@
         <v>46112</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36061,7 +36061,7 @@
         <v>46128</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>46106</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>46127</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36290,7 +36290,7 @@
         <v>45705</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36363,7 +36363,7 @@
         <v>46000</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36441,7 +36441,7 @@
         <v>46132</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
         <v>46133</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36597,7 +36597,7 @@
         <v>46132</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>46133</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36753,7 +36753,7 @@
         <v>46132</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36826,7 +36826,7 @@
         <v>46132</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>46132</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>46133</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37050,7 +37050,7 @@
         <v>46132</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37128,7 +37128,7 @@
         <v>45181</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37201,7 +37201,7 @@
         <v>46132</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>46132</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45608</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37435,7 +37435,7 @@
         <v>45608</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37513,7 +37513,7 @@
         <v>44700</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37591,7 +37591,7 @@
         <v>46134</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37664,7 +37664,7 @@
         <v>46134</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37737,7 +37737,7 @@
         <v>46114</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>46119</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>46133</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>46134</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38039,7 +38039,7 @@
         <v>45204</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38112,7 +38112,7 @@
         <v>45334</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>46043</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>46064</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>45645</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38409,7 +38409,7 @@
         <v>46137</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38487,7 +38487,7 @@
         <v>45478</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38565,7 +38565,7 @@
         <v>45800</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>45441</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>45838</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46049</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>46106</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38945,7 +38945,7 @@
         <v>45254</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39018,7 +39018,7 @@
         <v>45946</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>45840</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>44663</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39247,7 +39247,7 @@
         <v>45450</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45840</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39398,7 +39398,7 @@
         <v>45925</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>45366</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39554,7 +39554,7 @@
         <v>46048</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>46055</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39710,7 +39710,7 @@
         <v>45109</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39783,7 +39783,7 @@
         <v>46029</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>45870</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39929,7 +39929,7 @@
         <v>45719</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40002,7 +40002,7 @@
         <v>45073</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40075,7 +40075,7 @@
         <v>46050</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45488</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40226,7 +40226,7 @@
         <v>45656</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40299,7 +40299,7 @@
         <v>44712</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40372,7 +40372,7 @@
         <v>46137</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40450,7 +40450,7 @@
         <v>46137</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40528,7 +40528,7 @@
         <v>45301</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45237</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>46043</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40747,7 +40747,7 @@
         <v>45851</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40825,7 +40825,7 @@
         <v>45803</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40903,7 +40903,7 @@
         <v>45800</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40976,7 +40976,7 @@
         <v>46052</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41049,7 +41049,7 @@
         <v>46052</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44915</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>45821</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45747</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>46036</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>45488</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>46021</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>46139</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>46107</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41721,7 +41721,7 @@
         <v>46136</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41794,7 +41794,7 @@
         <v>46136</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41867,7 +41867,7 @@
         <v>46064</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41945,7 +41945,7 @@
         <v>46138</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>46042</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42101,7 +42101,7 @@
         <v>46065</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42179,7 +42179,7 @@
         <v>45712</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>46034</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42330,7 +42330,7 @@
         <v>45700</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45840</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42481,7 +42481,7 @@
         <v>46052</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42559,7 +42559,7 @@
         <v>45817</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42637,7 +42637,7 @@
         <v>45342</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42710,7 +42710,7 @@
         <v>46140</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42783,7 +42783,7 @@
         <v>46106</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>46064</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>44970</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43007,7 +43007,7 @@
         <v>46035</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>46071</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43153,7 +43153,7 @@
         <v>46048</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43226,7 +43226,7 @@
         <v>46140</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>46140</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43382,7 +43382,7 @@
         <v>45111</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>45111</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43528,7 +43528,7 @@
         <v>46027</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43606,7 +43606,7 @@
         <v>46056</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>46042</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>46063</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45754</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>46140</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43981,7 +43981,7 @@
         <v>46141</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45330</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44137,7 +44137,7 @@
         <v>46071</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45488</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>46098</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44361,7 +44361,7 @@
         <v>45526</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44439,7 +44439,7 @@
         <v>46140</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44517,7 +44517,7 @@
         <v>46079</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44595,7 +44595,7 @@
         <v>45106</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44673,7 +44673,7 @@
         <v>46125</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>46091</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44824,7 +44824,7 @@
         <v>46029</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44897,7 +44897,7 @@
         <v>46063</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44975,7 +44975,7 @@
         <v>46043</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>46037</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45121,7 +45121,7 @@
         <v>46073</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45199,7 +45199,7 @@
         <v>46056</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45272,7 +45272,7 @@
         <v>46052</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>46034</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45418,7 +45418,7 @@
         <v>46077</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45496,7 +45496,7 @@
         <v>46140</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>46063</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45647,7 +45647,7 @@
         <v>46104</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>45674</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45798,7 +45798,7 @@
         <v>45994</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46146</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>46127</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>46122</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45258</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>46125</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>46147</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46334,7 +46334,7 @@
         <v>46147</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>46148</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46490,7 +46490,7 @@
         <v>46148</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46568,7 +46568,7 @@
         <v>46134</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>46149</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>46148</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46797,7 +46797,7 @@
         <v>46148</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46875,7 +46875,7 @@
         <v>46100</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46948,7 +46948,7 @@
         <v>45291</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>46119</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47099,7 +47099,7 @@
         <v>46066</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45624</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>46153</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47328,7 +47328,7 @@
         <v>46071</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47406,7 +47406,7 @@
         <v>46128</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>46153</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47557,7 +47557,7 @@
         <v>45551</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47630,7 +47630,7 @@
         <v>45986</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47708,7 +47708,7 @@
         <v>46043</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47781,7 +47781,7 @@
         <v>45926</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>46155</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47927,7 +47927,7 @@
         <v>46154</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48000,7 +48000,7 @@
         <v>46155</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48073,7 +48073,7 @@
         <v>46093</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48146,7 +48146,7 @@
         <v>46119</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48219,7 +48219,7 @@
         <v>46056</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>45909</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48365,7 +48365,7 @@
         <v>46155</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48438,7 +48438,7 @@
         <v>46104</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48516,7 +48516,7 @@
         <v>46088</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48594,7 +48594,7 @@
         <v>46044</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48667,7 +48667,7 @@
         <v>46049</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48740,7 +48740,7 @@
         <v>46093</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>46093</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48891,7 +48891,7 @@
         <v>45994</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>45994</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>46156</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49110,7 +49110,7 @@
         <v>46122</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49183,7 +49183,7 @@
         <v>46100</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49256,7 +49256,7 @@
         <v>46161</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49329,7 +49329,7 @@
         <v>46160</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49402,7 +49402,7 @@
         <v>46161</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49475,7 +49475,7 @@
         <v>45649</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>46163</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45716</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>45600</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>46164</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46164</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>46044</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>46169</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>46169</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50147,7 +50147,7 @@
         <v>46169</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50225,7 +50225,7 @@
         <v>46168</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50303,7 +50303,7 @@
         <v>45719</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50381,7 +50381,7 @@
         <v>46169</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50459,7 +50459,7 @@
         <v>46168</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50537,7 +50537,7 @@
         <v>46169</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>46168</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50688,7 +50688,7 @@
         <v>46170</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50761,7 +50761,7 @@
         <v>46170</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>46170</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>46170</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50995,7 +50995,7 @@
         <v>46170</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51073,7 +51073,7 @@
         <v>46170</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51151,7 +51151,7 @@
         <v>45455</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>46170</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51302,7 +51302,7 @@
         <v>46085</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45551</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51448,7 +51448,7 @@
         <v>46023</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>46174</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51594,7 +51594,7 @@
         <v>45967</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51667,7 +51667,7 @@
         <v>46174</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51740,7 +51740,7 @@
         <v>46174</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51813,7 +51813,7 @@
         <v>46171</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51886,7 +51886,7 @@
         <v>44883</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51964,7 +51964,7 @@
         <v>45586</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52037,7 +52037,7 @@
         <v>46175</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52115,7 +52115,7 @@
         <v>46175</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52193,7 +52193,7 @@
         <v>45603</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52266,7 +52266,7 @@
         <v>45884</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52339,7 +52339,7 @@
         <v>46177</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52417,7 +52417,7 @@
         <v>46177</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52495,7 +52495,7 @@
         <v>45554</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52573,7 +52573,7 @@
         <v>46181</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52646,7 +52646,7 @@
         <v>45620</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52719,7 +52719,7 @@
         <v>45203</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52792,7 +52792,7 @@
         <v>46185</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52865,7 +52865,7 @@
         <v>46185</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>46188</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53016,7 +53016,7 @@
         <v>46188</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53094,7 +53094,7 @@
         <v>46185</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53167,7 +53167,7 @@
         <v>46185</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53240,7 +53240,7 @@
         <v>46185</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53313,7 +53313,7 @@
         <v>46190</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>45981</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53464,7 +53464,7 @@
         <v>46076</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>45398</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53615,7 +53615,7 @@
         <v>46190</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>46190</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>45615</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>46189</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53907,7 +53907,7 @@
         <v>46189</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53980,7 +53980,7 @@
         <v>45134</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45134</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>46189</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>46189</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54287,7 +54287,7 @@
         <v>46189</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54365,7 +54365,7 @@
         <v>45646</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54438,7 +54438,7 @@
         <v>46191</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>44839</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>46055</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54672,7 +54672,7 @@
         <v>46196</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54750,7 +54750,7 @@
         <v>46196</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54828,7 +54828,7 @@
         <v>46196</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54906,7 +54906,7 @@
         <v>46195</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54984,7 +54984,7 @@
         <v>44496</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55062,7 +55062,7 @@
         <v>46198</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55135,7 +55135,7 @@
         <v>46198</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55213,7 +55213,7 @@
         <v>46198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>45699</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55364,7 +55364,7 @@
         <v>46199</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55442,7 +55442,7 @@
         <v>45184</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55520,7 +55520,7 @@
         <v>46199</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55598,7 +55598,7 @@
         <v>46045</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>46183</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>46104</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55822,7 +55822,7 @@
         <v>46204</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55900,7 +55900,7 @@
         <v>46203</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55978,7 +55978,7 @@
         <v>46203</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>46203</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56129,7 +56129,7 @@
         <v>46205</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56202,7 +56202,7 @@
         <v>45511</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56275,7 +56275,7 @@
         <v>46206</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56348,7 +56348,7 @@
         <v>44820</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56426,7 +56426,7 @@
         <v>46205</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56499,7 +56499,7 @@
         <v>45152</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56572,7 +56572,7 @@
         <v>44643</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56645,7 +56645,7 @@
         <v>44893</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56718,7 +56718,7 @@
         <v>46205</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56791,7 +56791,7 @@
         <v>45107</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56869,7 +56869,7 @@
         <v>45243</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56942,7 +56942,7 @@
         <v>45671</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57020,7 +57020,7 @@
         <v>45210</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57093,7 +57093,7 @@
         <v>46216</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57171,7 +57171,7 @@
         <v>46258</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57249,7 +57249,7 @@
         <v>46213</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57322,7 +57322,7 @@
         <v>45593</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57395,7 +57395,7 @@
         <v>46260</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57473,7 +57473,7 @@
         <v>46218</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57551,7 +57551,7 @@
         <v>45678</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57624,7 +57624,7 @@
         <v>46071</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57702,7 +57702,7 @@
         <v>46220</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57780,7 +57780,7 @@
         <v>45156</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57858,7 +57858,7 @@
         <v>46098</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57936,7 +57936,7 @@
         <v>45674</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58009,7 +58009,7 @@
         <v>45982</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58087,7 +58087,7 @@
         <v>46267</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58165,7 +58165,7 @@
         <v>46223</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>46223</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58311,7 +58311,7 @@
         <v>46224</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58389,7 +58389,7 @@
         <v>46223</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58467,7 +58467,7 @@
         <v>46224</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58545,7 +58545,7 @@
         <v>46268</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58623,7 +58623,7 @@
         <v>46269</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58701,7 +58701,7 @@
         <v>45527</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58779,7 +58779,7 @@
         <v>46269</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58857,7 +58857,7 @@
         <v>46268</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58935,7 +58935,7 @@
         <v>44781</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59008,7 +59008,7 @@
         <v>46230</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59086,7 +59086,7 @@
         <v>45261</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59159,7 +59159,7 @@
         <v>46232</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59237,7 +59237,7 @@
         <v>46275</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59315,7 +59315,7 @@
         <v>46274</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59388,7 +59388,7 @@
         <v>46275</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59466,7 +59466,7 @@
         <v>46140</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59539,7 +59539,7 @@
         <v>46279</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59617,7 +59617,7 @@
         <v>46140</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59690,7 +59690,7 @@
         <v>46283</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59763,7 +59763,7 @@
         <v>46283</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59841,7 +59841,7 @@
         <v>45758</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59914,7 +59914,7 @@
         <v>45534</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59987,7 +59987,7 @@
         <v>45334</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60060,7 +60060,7 @@
         <v>45609</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60138,7 +60138,7 @@
         <v>45022</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60211,7 +60211,7 @@
         <v>45139</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60284,7 +60284,7 @@
         <v>46052</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60357,7 +60357,7 @@
         <v>45237</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60430,7 +60430,7 @@
         <v>45698</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60503,7 +60503,7 @@
         <v>46289</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60581,7 +60581,7 @@
         <v>45727</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60654,7 +60654,7 @@
         <v>46245</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60732,7 +60732,7 @@
         <v>46099</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60805,7 +60805,7 @@
         <v>45497</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60878,7 +60878,7 @@
         <v>46293</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60956,7 +60956,7 @@
         <v>46293</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61034,7 +61034,7 @@
         <v>44838</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61107,7 +61107,7 @@
         <v>46293</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61185,7 +61185,7 @@
         <v>46104</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61263,7 +61263,7 @@
         <v>45156</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61341,7 +61341,7 @@
         <v>46293</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61419,7 +61419,7 @@
         <v>45134</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61497,7 +61497,7 @@
         <v>45134</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61575,7 +61575,7 @@
         <v>45596</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61648,7 +61648,7 @@
         <v>45240</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61726,7 +61726,7 @@
         <v>45609</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61804,7 +61804,7 @@
         <v>45139</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61877,7 +61877,7 @@
         <v>46052</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61950,7 +61950,7 @@
         <v>46121</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62023,7 +62023,7 @@
         <v>46065</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62101,7 +62101,7 @@
         <v>46071</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62174,7 +62174,7 @@
         <v>46066</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62247,7 +62247,7 @@
         <v>45544</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62320,7 +62320,7 @@
         <v>46038</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62393,7 +62393,7 @@
         <v>46101</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62471,7 +62471,7 @@
         <v>46156</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62549,7 +62549,7 @@
         <v>46297</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62622,7 +62622,7 @@
         <v>46254</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62700,7 +62700,7 @@
         <v>45481</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62773,7 +62773,7 @@
         <v>45623</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62851,7 +62851,7 @@
         <v>46036</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62924,7 +62924,7 @@
         <v>46142</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -63002,7 +63002,7 @@
         <v>44725</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63075,7 +63075,7 @@
         <v>45281</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63148,7 +63148,7 @@
         <v>44950</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63221,7 +63221,7 @@
         <v>45068</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63299,7 +63299,7 @@
         <v>45771</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63377,7 +63377,7 @@
         <v>45068</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63455,7 +63455,7 @@
         <v>45534</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63528,7 +63528,7 @@
         <v>45230</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45156</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63684,7 +63684,7 @@
         <v>45070</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63757,7 +63757,7 @@
         <v>45628</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63830,7 +63830,7 @@
         <v>45771</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63908,7 +63908,7 @@
         <v>45484</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63981,7 +63981,7 @@
         <v>45280</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64054,7 +64054,7 @@
         <v>45239</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64127,7 +64127,7 @@
         <v>45600</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64200,7 +64200,7 @@
         <v>45744</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64278,7 +64278,7 @@
         <v>45072</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64351,7 +64351,7 @@
         <v>45448</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64429,7 +64429,7 @@
         <v>45666</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64502,7 +64502,7 @@
         <v>45265</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64575,7 +64575,7 @@
         <v>45134</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64653,7 +64653,7 @@
         <v>44950</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64726,7 +64726,7 @@
         <v>45776</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64799,7 +64799,7 @@
         <v>45455</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64872,7 +64872,7 @@
         <v>45608</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64945,7 +64945,7 @@
         <v>45544</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65018,7 +65018,7 @@
         <v>45258</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65091,7 +65091,7 @@
         <v>45786</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65169,7 +65169,7 @@
         <v>45786</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65247,7 +65247,7 @@
         <v>45323</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65325,7 +65325,7 @@
         <v>45638</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65403,7 +65403,7 @@
         <v>45315</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65481,7 +65481,7 @@
         <v>45699</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65559,7 +65559,7 @@
         <v>44904</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65637,7 +65637,7 @@
         <v>46058</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65710,7 +65710,7 @@
         <v>46089</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65788,7 +65788,7 @@
         <v>46148</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65861,7 +65861,7 @@
         <v>46148</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65934,7 +65934,7 @@
         <v>46048</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66007,7 +66007,7 @@
         <v>46293</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -66085,7 +66085,7 @@
         <v>46255</v>
       </c>
       <c r="E839" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>45106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45841</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46101</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46170</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45469</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>46126</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>46094</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>46185</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46125</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46153</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46114</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>46132</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46036</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>46044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>46125</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45280</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45519</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45582</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44496</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46097</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>46100</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>46101</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45022</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>46125</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>46091</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>46076</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44953</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>46009</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45448</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45469</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>46038</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>46104</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>46085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>46077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>46053</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>46056</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>46077</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>46282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46282</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>46283</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>46302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44479</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44532</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44492</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44532</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44802</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44881</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44663</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>44872</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44795</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44858</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44838</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45488</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>44893</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45754</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44820</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45608</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45434</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45139</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45488</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>45203</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45758</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45223</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45068</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45184</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45334</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45211</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45450</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45443</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45771</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45771</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45068</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45551</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45527</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>45334</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45700</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45455</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45237</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45366</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45481</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45490</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45478</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45169</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45884</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45048</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45156</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45134</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45342</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45156</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45674</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45252</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45534</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45239</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44986</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44496</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45889</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45889</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45889</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45744</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45891</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45896</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45488</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45903</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45903</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45184</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45835</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45905</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>44879</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45618</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45593</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45776</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45777</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45041</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45911</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45911</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45911</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>45611</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45608</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45617</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>45258</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45554</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45544</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45786</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45455</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45786</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45478</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44746</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>45790</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45925</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44970</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45593</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45649</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44950</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45776</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45846</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45107</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44845</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>45590</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45617</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44501</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45282</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45554</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44525</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45582</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45497</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45072</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45929</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45929</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45602</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45602</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44816</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45027</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45608</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45554</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45644</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45216</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44522</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45620</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45434</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45596</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45341</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45621</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44659</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>45468</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>45754</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45600</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45932</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45747</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45596</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45210</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45800</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45800</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45800</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45800</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45800</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45800</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44950</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45617</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45937</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45803</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45181</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45624</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45937</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45180</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45937</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45805</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45937</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45398</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45448</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45937</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45645</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45834</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45152</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45281</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45432</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45441</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45817</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45817</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45291</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45819</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45819</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45671</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45824</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45757</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45821</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45705</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45106</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45609</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>45952</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45827</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45827</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45827</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44643</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45156</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45611</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45674</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45954</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45953</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45954</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45953</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45957</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45959</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45243</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45254</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45838</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>44804</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>44725</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45666</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45840</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44781</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45966</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45840</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45510</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45511</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45204</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45967</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45967</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45070</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45646</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45134</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45645</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45972</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45109</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45972</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44700</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45972</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45719</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45073</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45265</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45727</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45973</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45973</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45973</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45744</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45699</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45973</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45973</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>45851</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45484</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44797</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45978</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>45978</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45978</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45772</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45534</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45237</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45978</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45254</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45978</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45978</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>45978</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>45230</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45975</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45698</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45719</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45586</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45551</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>46094</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45022</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>46098</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>44890</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>46098</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>46099</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>46098</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>46098</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>46098</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>46098</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>46099</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>44883</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>46100</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>46100</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45986</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45301</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>46101</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>46104</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>46105</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>46104</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>46104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44712</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45985</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45985</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>46104</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45134</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>46106</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>46106</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>46106</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>46106</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45534</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>46111</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>46108</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>45988</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>45167</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>46108</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45623</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46111</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46112</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>46112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>46112</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45139</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>46114</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>46114</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46114</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>46094</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>46114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>46119</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>46119</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>46118</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45994</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>46076</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46076</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>46077</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>46076</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>46121</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>46121</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45548</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>46049</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>46076</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>45996</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45995</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45995</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>46106</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>46126</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>46105</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46000</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>46126</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>46127</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46127</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>46098</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>46132</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>46132</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>46132</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>46128</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>46112</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>46112</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>46132</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>46132</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>46128</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>46132</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>46132</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>46134</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>46134</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46134</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>46133</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>46133</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>46133</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>46006</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>46133</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>46136</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45989</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45132</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45139</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45656</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>44950</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>45600</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45609</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46009</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>46136</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>46009</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>46119</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46114</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>45712</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>46013</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>46014</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>46010</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>46013</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>46140</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>46071</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45840</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>46009</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>46021</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46048</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46024</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45258</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>46042</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>46064</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>46027</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46140</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>46027</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>46027</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>46027</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>46027</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>46027</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>46137</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>46137</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>46029</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>46028</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45261</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>46029</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45111</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46139</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>46028</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>46029</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>46029</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>46024</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>46036</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46031</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45821</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>46034</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46033</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45946</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>46034</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>46043</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>46043</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>46031</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45488</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>46063</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>46036</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46036</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46035</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>46042</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>46036</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>46035</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>46036</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>46036</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>46049</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>46063</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>46035</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46036</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>44839</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46106</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>46138</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>46052</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>46048</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45526</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>46038</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>46038</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>46037</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>46041</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>46098</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45747</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>46055</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>46107</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45803</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>46041</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45107</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>46044</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>46050</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45156</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46021</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>46140</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>46044</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44950</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>46056</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>46052</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45870</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45800</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>46043</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>46043</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>46052</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45800</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>46140</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>46036</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>46140</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45134</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>46137</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45134</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>46048</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45925</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>46034</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>46064</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>44663</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46048</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>46065</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>46052</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>46036</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44915</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>46029</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>46043</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>46044</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>46045</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>46045</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>46049</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>46050</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>46034</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>46035</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>46091</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46049</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>46106</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>46077</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45111</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>46050</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>46063</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>46029</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>46051</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45994</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>46064</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>46052</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>46052</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>46052</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>46037</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>46051</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>46056</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>46056</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>46053</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>46056</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>46056</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>46056</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>46056</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>46055</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>46141</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>46056</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>46056</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>46057</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>46125</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>46056</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>46062</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>46027</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>46059</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>46062</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>46071</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>46073</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>46062</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>46062</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>46146</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>46064</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>46104</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>46064</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>46064</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>46122</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>46127</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>46125</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>46148</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>46065</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>46148</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>46134</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>46065</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>46147</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>46119</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>46147</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>46148</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>46148</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>46056</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>46149</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>46071</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>46071</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>46071</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>46153</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>46071</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>46071</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>46072</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>46072</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>46072</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>46072</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>46071</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50606,7 +50606,7 @@
         <v>46071</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>46031</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>46071</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>46076</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>46128</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>46077</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>46077</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>46077</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>46093</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>46093</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>46119</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>46073</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>46077</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46093</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>46077</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51741,7 +51741,7 @@
         <v>46088</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>46071</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>46031</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45909</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>45986</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>46077</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52199,7 +52199,7 @@
         <v>46078</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>46079</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>46079</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>46080</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>46153</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52569,7 +52569,7 @@
         <v>46043</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>46104</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>46154</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>46066</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>46080</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>46083</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>46083</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>46083</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>46080</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>46049</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>46056</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45994</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>46155</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>46156</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>45994</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>46044</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45926</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>46085</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>46155</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>46155</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>46087</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>46089</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54200,7 +54200,7 @@
         <v>46100</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54273,7 +54273,7 @@
         <v>46091</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>46160</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>46122</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>46093</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>46161</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>46093</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>46092</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>46161</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>46093</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>46094</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55013,7 +55013,7 @@
         <v>46097</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55086,7 +55086,7 @@
         <v>46094</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55159,7 +55159,7 @@
         <v>45716</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55232,7 +55232,7 @@
         <v>46163</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>46164</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>46164</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>46168</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>46168</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55617,7 +55617,7 @@
         <v>46044</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55690,7 +55690,7 @@
         <v>46168</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>46169</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>46169</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>46169</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>46169</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56075,7 +56075,7 @@
         <v>46169</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56148,7 +56148,7 @@
         <v>46085</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>46023</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56294,7 +56294,7 @@
         <v>46170</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56372,7 +56372,7 @@
         <v>46170</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>45967</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>46170</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>46170</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>46170</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>46170</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>46171</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>46170</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>46175</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>46175</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>46174</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>46174</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>46174</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>45603</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>46177</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>46177</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>46181</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>46185</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>46185</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>46185</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>46185</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>46185</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>46189</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>46189</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>46189</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>46076</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45615</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58398,7 +58398,7 @@
         <v>46189</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>46189</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45981</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>46188</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58705,7 +58705,7 @@
         <v>46055</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58783,7 +58783,7 @@
         <v>46190</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>46190</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>46190</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>46191</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59080,7 +59080,7 @@
         <v>46195</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59158,7 +59158,7 @@
         <v>46196</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59236,7 +59236,7 @@
         <v>46196</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>46196</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>46198</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59465,7 +59465,7 @@
         <v>46183</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59543,7 +59543,7 @@
         <v>46199</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59621,7 +59621,7 @@
         <v>46198</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59699,7 +59699,7 @@
         <v>46199</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>46198</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>46203</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59928,7 +59928,7 @@
         <v>46203</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>46203</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60079,7 +60079,7 @@
         <v>46205</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>46205</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60225,7 +60225,7 @@
         <v>46204</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>46205</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>46104</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60449,7 +60449,7 @@
         <v>46206</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>46216</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60600,7 +60600,7 @@
         <v>46218</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45982</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60756,7 +60756,7 @@
         <v>46098</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60834,7 +60834,7 @@
         <v>46071</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>46223</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>46223</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61058,7 +61058,7 @@
         <v>46267</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61136,7 +61136,7 @@
         <v>46268</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61214,7 +61214,7 @@
         <v>46268</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61292,7 +61292,7 @@
         <v>46269</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61370,7 +61370,7 @@
         <v>46269</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
         <v>46230</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>46274</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
         <v>46275</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61677,7 +61677,7 @@
         <v>46275</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61755,7 +61755,7 @@
         <v>46279</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>46140</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>46140</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
         <v>46283</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>46283</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>46052</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62203,7 +62203,7 @@
         <v>46245</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62281,7 +62281,7 @@
         <v>46099</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>46289</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46293</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>46065</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62588,7 +62588,7 @@
         <v>46066</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62661,7 +62661,7 @@
         <v>46293</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62739,7 +62739,7 @@
         <v>46293</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62817,7 +62817,7 @@
         <v>46104</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62895,7 +62895,7 @@
         <v>46071</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62968,7 +62968,7 @@
         <v>46052</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>46293</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>46142</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45986</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63270,7 +63270,7 @@
         <v>46121</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63343,7 +63343,7 @@
         <v>46297</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63416,7 +63416,7 @@
         <v>46156</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63494,7 +63494,7 @@
         <v>46300</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63567,7 +63567,7 @@
         <v>46254</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63645,7 +63645,7 @@
         <v>46092</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63718,7 +63718,7 @@
         <v>46079</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>46038</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63869,7 +63869,7 @@
         <v>46100</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63942,7 +63942,7 @@
         <v>46101</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64020,7 +64020,7 @@
         <v>46036</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64093,7 +64093,7 @@
         <v>46188</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64171,7 +64171,7 @@
         <v>46126</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64244,7 +64244,7 @@
         <v>46121</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64317,7 +64317,7 @@
         <v>46213</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64390,7 +64390,7 @@
         <v>46260</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64468,7 +64468,7 @@
         <v>46045</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64541,7 +64541,7 @@
         <v>46224</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64619,7 +64619,7 @@
         <v>46223</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>46224</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64775,7 +64775,7 @@
         <v>46258</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64853,7 +64853,7 @@
         <v>46220</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64931,7 +64931,7 @@
         <v>46232</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65009,7 +65009,7 @@
         <v>45323</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65087,7 +65087,7 @@
         <v>45638</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65165,7 +65165,7 @@
         <v>45315</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>45699</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65321,7 +65321,7 @@
         <v>44904</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65399,7 +65399,7 @@
         <v>46058</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65472,7 +65472,7 @@
         <v>46089</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65550,7 +65550,7 @@
         <v>46148</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65623,7 +65623,7 @@
         <v>46148</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65696,7 +65696,7 @@
         <v>46048</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46293</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65847,7 +65847,7 @@
         <v>46300</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65920,7 +65920,7 @@
         <v>46255</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>45106</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46132</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>45841</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46101</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>46077</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46099</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2598,7 +2598,7 @@
         <v>46170</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45469</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>46126</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>45812</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>46094</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3162,7 +3162,7 @@
         <v>46185</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>46125</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46153</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46114</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>46132</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46036</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3816,7 +3816,7 @@
         <v>46044</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>46125</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45280</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45519</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4691,7 +4691,7 @@
         <v>45247</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4801,7 +4801,7 @@
         <v>45582</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4911,7 +4911,7 @@
         <v>44496</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>45972</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45754</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5236,7 +5236,7 @@
         <v>46097</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>46100</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5451,7 +5451,7 @@
         <v>46101</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5565,7 +5565,7 @@
         <v>45022</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>46125</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         <v>46091</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>46076</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44953</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>46009</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>46070</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6341,7 +6341,7 @@
         <v>46139</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>45448</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45469</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6671,7 +6671,7 @@
         <v>46038</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>46104</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6894,7 +6894,7 @@
         <v>46085</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>46077</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>46053</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>46056</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7332,7 +7332,7 @@
         <v>46077</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>46282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         <v>46282</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>46283</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>46302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44479</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44529</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44532</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>44817</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44795</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44509</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8871,7 +8871,7 @@
         <v>44858</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44492</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44532</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44643</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44802</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44881</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44663</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44705</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
         <v>44872</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44795</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>44858</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>44480</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
         <v>45330</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44838</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45488</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -9996,7 +9996,7 @@
         <v>44893</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
         <v>45754</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10142,7 +10142,7 @@
         <v>44820</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45608</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>45608</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10376,7 +10376,7 @@
         <v>45434</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10449,7 +10449,7 @@
         <v>44887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         <v>45139</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10595,7 +10595,7 @@
         <v>45488</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>45203</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45758</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>45223</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10892,7 +10892,7 @@
         <v>45068</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>45184</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45678</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>45628</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45334</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45211</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45450</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45443</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>45771</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45771</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>45581</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>45068</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45551</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45527</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11954,7 +11954,7 @@
         <v>45334</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12027,7 +12027,7 @@
         <v>45700</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12100,7 +12100,7 @@
         <v>45455</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>45237</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45366</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12324,7 +12324,7 @@
         <v>45481</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>45490</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45478</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>45169</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>45884</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>45048</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45799</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45156</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45134</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>45342</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45156</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45888</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45674</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13308,7 +13308,7 @@
         <v>45252</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45534</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45239</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44986</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45544</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>44496</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45889</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45889</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>45889</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45744</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45891</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14126,7 +14126,7 @@
         <v>45894</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45896</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45488</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
         <v>45903</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45903</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>45903</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14569,7 +14569,7 @@
         <v>45184</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>45835</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45905</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>44879</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>45618</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>44889</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>45593</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45776</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>45777</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45041</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45911</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45911</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45911</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45911</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>45611</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>45280</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>45608</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45617</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15918,7 +15918,7 @@
         <v>45258</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>45554</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45544</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16142,7 +16142,7 @@
         <v>45786</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>45455</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45786</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16371,7 +16371,7 @@
         <v>45478</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16449,7 +16449,7 @@
         <v>44746</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>45790</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16595,7 +16595,7 @@
         <v>45925</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
         <v>44970</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16746,7 +16746,7 @@
         <v>45593</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16819,7 +16819,7 @@
         <v>45649</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44950</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>45776</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>45846</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17121,7 +17121,7 @@
         <v>45107</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17199,7 +17199,7 @@
         <v>45930</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44845</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>45590</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45617</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>44501</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>45282</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45554</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45162</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44525</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45582</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>45497</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45072</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>45929</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45929</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45602</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45602</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45602</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18495,7 +18495,7 @@
         <v>44816</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>45027</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45608</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45554</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45644</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>45216</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44522</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19041,7 +19041,7 @@
         <v>45620</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45434</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45596</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19260,7 +19260,7 @@
         <v>45341</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19333,7 +19333,7 @@
         <v>45621</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>44659</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19479,7 +19479,7 @@
         <v>45468</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>45754</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45600</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
         <v>45932</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>45747</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19854,7 +19854,7 @@
         <v>45596</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19927,7 +19927,7 @@
         <v>45210</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>45800</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>45800</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45800</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20234,7 +20234,7 @@
         <v>45800</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20312,7 +20312,7 @@
         <v>45800</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
         <v>45800</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20468,7 +20468,7 @@
         <v>44950</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20541,7 +20541,7 @@
         <v>45617</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>45937</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>45803</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20770,7 +20770,7 @@
         <v>45181</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20843,7 +20843,7 @@
         <v>45624</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20921,7 +20921,7 @@
         <v>45937</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20994,7 +20994,7 @@
         <v>45180</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45937</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>45805</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21213,7 +21213,7 @@
         <v>45937</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21286,7 +21286,7 @@
         <v>45398</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21359,7 +21359,7 @@
         <v>45448</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21437,7 +21437,7 @@
         <v>45937</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21510,7 +21510,7 @@
         <v>45937</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21583,7 +21583,7 @@
         <v>45645</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21661,7 +21661,7 @@
         <v>45834</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45152</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>45281</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21880,7 +21880,7 @@
         <v>45432</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45441</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22026,7 +22026,7 @@
         <v>45817</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
         <v>45817</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22182,7 +22182,7 @@
         <v>45291</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22255,7 +22255,7 @@
         <v>45817</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22328,7 +22328,7 @@
         <v>45819</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22406,7 +22406,7 @@
         <v>45819</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22484,7 +22484,7 @@
         <v>45671</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>45824</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45757</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22718,7 +22718,7 @@
         <v>45821</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22796,7 +22796,7 @@
         <v>45705</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22869,7 +22869,7 @@
         <v>45106</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22947,7 +22947,7 @@
         <v>45609</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>45952</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23103,7 +23103,7 @@
         <v>45827</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23176,7 +23176,7 @@
         <v>45827</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23254,7 +23254,7 @@
         <v>45827</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>45827</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44643</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45156</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>45611</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23639,7 +23639,7 @@
         <v>45674</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23712,7 +23712,7 @@
         <v>45954</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>45953</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23863,7 +23863,7 @@
         <v>45954</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23941,7 +23941,7 @@
         <v>45953</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24014,7 +24014,7 @@
         <v>45957</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45959</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45243</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45254</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24316,7 +24316,7 @@
         <v>45838</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24389,7 +24389,7 @@
         <v>44804</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24462,7 +24462,7 @@
         <v>44725</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24535,7 +24535,7 @@
         <v>45666</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24608,7 +24608,7 @@
         <v>45840</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>44781</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45966</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24832,7 +24832,7 @@
         <v>45840</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45510</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24978,7 +24978,7 @@
         <v>45511</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>45204</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25124,7 +25124,7 @@
         <v>45967</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25197,7 +25197,7 @@
         <v>45967</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45070</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25343,7 +25343,7 @@
         <v>45646</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25416,7 +25416,7 @@
         <v>45134</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45645</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25572,7 +25572,7 @@
         <v>45972</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>45109</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25718,7 +25718,7 @@
         <v>45972</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44700</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>45972</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25942,7 +25942,7 @@
         <v>45719</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26015,7 +26015,7 @@
         <v>45073</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>45265</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26161,7 +26161,7 @@
         <v>45727</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>45973</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26307,7 +26307,7 @@
         <v>45973</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26380,7 +26380,7 @@
         <v>45973</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45744</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45699</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26609,7 +26609,7 @@
         <v>45973</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45973</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>45973</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45973</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26906,7 +26906,7 @@
         <v>45851</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -26984,7 +26984,7 @@
         <v>45484</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27057,7 +27057,7 @@
         <v>44797</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45978</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27203,7 +27203,7 @@
         <v>45978</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>45978</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>45772</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27422,7 +27422,7 @@
         <v>45534</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45237</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45978</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45254</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27719,7 +27719,7 @@
         <v>45978</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27792,7 +27792,7 @@
         <v>45978</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27865,7 +27865,7 @@
         <v>45978</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27938,7 +27938,7 @@
         <v>45230</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28016,7 +28016,7 @@
         <v>45975</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28089,7 +28089,7 @@
         <v>45240</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28167,7 +28167,7 @@
         <v>45698</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28240,7 +28240,7 @@
         <v>45719</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>45111</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28391,7 +28391,7 @@
         <v>45586</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28464,7 +28464,7 @@
         <v>45551</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28537,7 +28537,7 @@
         <v>46094</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45022</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>46098</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28761,7 +28761,7 @@
         <v>44890</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28834,7 +28834,7 @@
         <v>46098</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28907,7 +28907,7 @@
         <v>46099</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         <v>46098</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29058,7 +29058,7 @@
         <v>46098</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>46098</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29214,7 +29214,7 @@
         <v>46098</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>46099</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29370,7 +29370,7 @@
         <v>44883</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29448,7 +29448,7 @@
         <v>46100</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>46100</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45986</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29672,7 +29672,7 @@
         <v>45301</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29745,7 +29745,7 @@
         <v>46101</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29823,7 +29823,7 @@
         <v>46104</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>46105</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29979,7 +29979,7 @@
         <v>46104</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30057,7 +30057,7 @@
         <v>46104</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30130,7 +30130,7 @@
         <v>46104</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30208,7 +30208,7 @@
         <v>44712</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45985</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30354,7 +30354,7 @@
         <v>45985</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30427,7 +30427,7 @@
         <v>46104</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30505,7 +30505,7 @@
         <v>45134</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30583,7 +30583,7 @@
         <v>46104</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30656,7 +30656,7 @@
         <v>46106</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30734,7 +30734,7 @@
         <v>46106</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30807,7 +30807,7 @@
         <v>46106</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30885,7 +30885,7 @@
         <v>46106</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30963,7 +30963,7 @@
         <v>45534</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31036,7 +31036,7 @@
         <v>46106</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31109,7 +31109,7 @@
         <v>46111</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31182,7 +31182,7 @@
         <v>46108</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31260,7 +31260,7 @@
         <v>45988</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>45167</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>46108</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31489,7 +31489,7 @@
         <v>45623</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31567,7 +31567,7 @@
         <v>46111</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31640,7 +31640,7 @@
         <v>46112</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31718,7 +31718,7 @@
         <v>46112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31796,7 +31796,7 @@
         <v>46112</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31874,7 +31874,7 @@
         <v>45139</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31947,7 +31947,7 @@
         <v>46114</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>46114</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32098,7 +32098,7 @@
         <v>46114</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32171,7 +32171,7 @@
         <v>46094</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>46114</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32327,7 +32327,7 @@
         <v>46119</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>46119</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>46118</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32551,7 +32551,7 @@
         <v>45994</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>46076</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>46076</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>46077</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>46076</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>46121</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>46121</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45548</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>46049</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33238,7 +33238,7 @@
         <v>46076</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33316,7 +33316,7 @@
         <v>45996</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33394,7 +33394,7 @@
         <v>45995</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45995</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>46125</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33628,7 +33628,7 @@
         <v>46106</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33706,7 +33706,7 @@
         <v>46126</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>46105</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33862,7 +33862,7 @@
         <v>46000</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33940,7 +33940,7 @@
         <v>46126</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>46127</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34086,7 +34086,7 @@
         <v>46127</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34159,7 +34159,7 @@
         <v>46127</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34232,7 +34232,7 @@
         <v>46098</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34310,7 +34310,7 @@
         <v>46132</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>46132</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34466,7 +34466,7 @@
         <v>46132</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34539,7 +34539,7 @@
         <v>46132</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>46128</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34690,7 +34690,7 @@
         <v>46112</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>46112</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34846,7 +34846,7 @@
         <v>46132</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34924,7 +34924,7 @@
         <v>46132</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>46128</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35075,7 +35075,7 @@
         <v>46132</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>46132</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>46134</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>46134</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>46134</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>46133</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>46133</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35606,7 +35606,7 @@
         <v>46133</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35684,7 +35684,7 @@
         <v>46006</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35757,7 +35757,7 @@
         <v>46133</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35830,7 +35830,7 @@
         <v>46136</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>45989</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>45132</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36059,7 +36059,7 @@
         <v>45139</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36132,7 +36132,7 @@
         <v>45656</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>44950</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36278,7 +36278,7 @@
         <v>45600</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36351,7 +36351,7 @@
         <v>45609</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46009</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>46136</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36580,7 +36580,7 @@
         <v>46009</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>46119</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46114</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36804,7 +36804,7 @@
         <v>45712</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36877,7 +36877,7 @@
         <v>46013</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>46014</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37028,7 +37028,7 @@
         <v>46010</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37101,7 +37101,7 @@
         <v>46013</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37179,7 +37179,7 @@
         <v>46140</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>46071</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37330,7 +37330,7 @@
         <v>45840</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37408,7 +37408,7 @@
         <v>46009</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37486,7 +37486,7 @@
         <v>46021</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37559,7 +37559,7 @@
         <v>46048</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46024</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37710,7 +37710,7 @@
         <v>45258</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37783,7 +37783,7 @@
         <v>46042</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37856,7 +37856,7 @@
         <v>46064</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37929,7 +37929,7 @@
         <v>46027</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38002,7 +38002,7 @@
         <v>46140</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>46027</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38153,7 +38153,7 @@
         <v>46027</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38226,7 +38226,7 @@
         <v>46027</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38299,7 +38299,7 @@
         <v>46027</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38372,7 +38372,7 @@
         <v>46027</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>46137</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38523,7 +38523,7 @@
         <v>46137</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38601,7 +38601,7 @@
         <v>46029</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38674,7 +38674,7 @@
         <v>46028</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>45261</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>46029</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45111</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38966,7 +38966,7 @@
         <v>46139</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>46028</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>46029</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39190,7 +39190,7 @@
         <v>46029</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>46024</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39336,7 +39336,7 @@
         <v>46036</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39409,7 +39409,7 @@
         <v>46031</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39482,7 +39482,7 @@
         <v>45821</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>46034</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>46033</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39701,7 +39701,7 @@
         <v>45946</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39779,7 +39779,7 @@
         <v>46034</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>46043</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39930,7 +39930,7 @@
         <v>46043</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>46031</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40076,7 +40076,7 @@
         <v>45488</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40149,7 +40149,7 @@
         <v>46063</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40222,7 +40222,7 @@
         <v>46036</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40295,7 +40295,7 @@
         <v>46036</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40368,7 +40368,7 @@
         <v>46035</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40441,7 +40441,7 @@
         <v>46042</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40519,7 +40519,7 @@
         <v>46036</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40592,7 +40592,7 @@
         <v>46035</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>46036</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40738,7 +40738,7 @@
         <v>46036</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40811,7 +40811,7 @@
         <v>46049</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40889,7 +40889,7 @@
         <v>46063</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40962,7 +40962,7 @@
         <v>46035</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46036</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>44839</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>46106</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41264,7 +41264,7 @@
         <v>46138</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41342,7 +41342,7 @@
         <v>46052</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41420,7 +41420,7 @@
         <v>46048</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41493,7 +41493,7 @@
         <v>45526</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41571,7 +41571,7 @@
         <v>46038</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41644,7 +41644,7 @@
         <v>46038</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>46037</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41790,7 +41790,7 @@
         <v>46041</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41863,7 +41863,7 @@
         <v>46098</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41936,7 +41936,7 @@
         <v>45747</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>46055</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>46107</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>45803</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42243,7 +42243,7 @@
         <v>46041</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42316,7 +42316,7 @@
         <v>45107</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42394,7 +42394,7 @@
         <v>46044</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42467,7 +42467,7 @@
         <v>46050</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>45156</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42623,7 +42623,7 @@
         <v>46021</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>46140</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42774,7 +42774,7 @@
         <v>46044</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>44950</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42920,7 +42920,7 @@
         <v>46056</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>46052</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45870</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45800</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43217,7 +43217,7 @@
         <v>46043</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>46043</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>46052</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43441,7 +43441,7 @@
         <v>45800</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>46140</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43587,7 +43587,7 @@
         <v>46036</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>46140</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43738,7 +43738,7 @@
         <v>45134</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>46137</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43894,7 +43894,7 @@
         <v>45134</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>46048</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>45925</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>46034</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>46064</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>44663</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44357,7 +44357,7 @@
         <v>46048</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44430,7 +44430,7 @@
         <v>46065</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44508,7 +44508,7 @@
         <v>46052</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>46036</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>44915</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>46029</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44800,7 +44800,7 @@
         <v>46043</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>46044</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44946,7 +44946,7 @@
         <v>46045</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45019,7 +45019,7 @@
         <v>46045</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45097,7 +45097,7 @@
         <v>46049</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45170,7 +45170,7 @@
         <v>46050</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45248,7 +45248,7 @@
         <v>46034</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>46035</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>46091</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45467,7 +45467,7 @@
         <v>46049</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45540,7 +45540,7 @@
         <v>46106</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45618,7 +45618,7 @@
         <v>46077</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45696,7 +45696,7 @@
         <v>45111</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>46050</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>46063</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>46029</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>46051</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45994</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46149,7 +46149,7 @@
         <v>46064</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>46052</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>46052</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46368,7 +46368,7 @@
         <v>46052</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46441,7 +46441,7 @@
         <v>46037</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46514,7 +46514,7 @@
         <v>46051</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46587,7 +46587,7 @@
         <v>46056</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46660,7 +46660,7 @@
         <v>46056</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46733,7 +46733,7 @@
         <v>46053</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46806,7 +46806,7 @@
         <v>46056</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46879,7 +46879,7 @@
         <v>46056</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46952,7 +46952,7 @@
         <v>46056</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47025,7 +47025,7 @@
         <v>46056</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>46055</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47176,7 +47176,7 @@
         <v>46141</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47254,7 +47254,7 @@
         <v>46056</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47327,7 +47327,7 @@
         <v>46056</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47405,7 +47405,7 @@
         <v>46057</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>46125</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47561,7 +47561,7 @@
         <v>46056</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>46062</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>46027</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47790,7 +47790,7 @@
         <v>46059</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47863,7 +47863,7 @@
         <v>46062</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47936,7 +47936,7 @@
         <v>46071</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48014,7 +48014,7 @@
         <v>46073</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48092,7 +48092,7 @@
         <v>46062</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>46062</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>46146</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48321,7 +48321,7 @@
         <v>46064</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48394,7 +48394,7 @@
         <v>46104</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>46064</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48545,7 +48545,7 @@
         <v>46064</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48623,7 +48623,7 @@
         <v>46122</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48701,7 +48701,7 @@
         <v>46127</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48779,7 +48779,7 @@
         <v>46125</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48857,7 +48857,7 @@
         <v>46148</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48935,7 +48935,7 @@
         <v>46065</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49013,7 +49013,7 @@
         <v>46148</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49091,7 +49091,7 @@
         <v>46134</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>46065</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>46147</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>46119</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>46147</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49476,7 +49476,7 @@
         <v>46148</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49554,7 +49554,7 @@
         <v>46148</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49632,7 +49632,7 @@
         <v>46056</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49710,7 +49710,7 @@
         <v>46149</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49783,7 +49783,7 @@
         <v>46071</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>46071</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49929,7 +49929,7 @@
         <v>46071</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50007,7 +50007,7 @@
         <v>46153</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50080,7 +50080,7 @@
         <v>46071</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50158,7 +50158,7 @@
         <v>46071</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50231,7 +50231,7 @@
         <v>46072</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>46072</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>46072</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50455,7 +50455,7 @@
         <v>46072</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50533,7 +50533,7 @@
         <v>46071</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50606,7 +50606,7 @@
         <v>46071</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50679,7 +50679,7 @@
         <v>46031</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50752,7 +50752,7 @@
         <v>46071</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50830,7 +50830,7 @@
         <v>46076</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50908,7 +50908,7 @@
         <v>46128</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50986,7 +50986,7 @@
         <v>46077</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>46077</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51137,7 +51137,7 @@
         <v>46077</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51215,7 +51215,7 @@
         <v>46093</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51288,7 +51288,7 @@
         <v>46093</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>46119</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51439,7 +51439,7 @@
         <v>46073</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51512,7 +51512,7 @@
         <v>46077</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51590,7 +51590,7 @@
         <v>46093</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51663,7 +51663,7 @@
         <v>46077</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51741,7 +51741,7 @@
         <v>46088</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51819,7 +51819,7 @@
         <v>46071</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51897,7 +51897,7 @@
         <v>46031</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51970,7 +51970,7 @@
         <v>45909</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52043,7 +52043,7 @@
         <v>45986</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52121,7 +52121,7 @@
         <v>46077</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52199,7 +52199,7 @@
         <v>46078</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52277,7 +52277,7 @@
         <v>46079</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52350,7 +52350,7 @@
         <v>46079</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52423,7 +52423,7 @@
         <v>46080</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>46153</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52569,7 +52569,7 @@
         <v>46043</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52642,7 +52642,7 @@
         <v>46104</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52720,7 +52720,7 @@
         <v>46154</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52793,7 +52793,7 @@
         <v>46066</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
         <v>46080</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52944,7 +52944,7 @@
         <v>46083</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53022,7 +53022,7 @@
         <v>46083</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53095,7 +53095,7 @@
         <v>46083</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53173,7 +53173,7 @@
         <v>46080</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>46049</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>46056</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>45994</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>46155</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53538,7 +53538,7 @@
         <v>46156</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53611,7 +53611,7 @@
         <v>45994</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>46044</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45926</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>46085</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53903,7 +53903,7 @@
         <v>46155</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53976,7 +53976,7 @@
         <v>46155</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54049,7 +54049,7 @@
         <v>46087</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>46089</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54200,7 +54200,7 @@
         <v>46100</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54273,7 +54273,7 @@
         <v>46091</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54346,7 +54346,7 @@
         <v>46160</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54419,7 +54419,7 @@
         <v>46122</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54492,7 +54492,7 @@
         <v>46093</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54565,7 +54565,7 @@
         <v>46161</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>46093</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54716,7 +54716,7 @@
         <v>46092</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>46161</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54862,7 +54862,7 @@
         <v>46093</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54935,7 +54935,7 @@
         <v>46094</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55013,7 +55013,7 @@
         <v>46097</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55086,7 +55086,7 @@
         <v>46094</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55159,7 +55159,7 @@
         <v>45716</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55232,7 +55232,7 @@
         <v>46163</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55310,7 +55310,7 @@
         <v>46164</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55388,7 +55388,7 @@
         <v>46164</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55461,7 +55461,7 @@
         <v>46168</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55539,7 +55539,7 @@
         <v>46168</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55617,7 +55617,7 @@
         <v>46044</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55690,7 +55690,7 @@
         <v>46168</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55768,7 +55768,7 @@
         <v>46169</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55841,7 +55841,7 @@
         <v>46169</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55919,7 +55919,7 @@
         <v>46169</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>46169</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56075,7 +56075,7 @@
         <v>46169</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56148,7 +56148,7 @@
         <v>46085</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56221,7 +56221,7 @@
         <v>46023</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56294,7 +56294,7 @@
         <v>46170</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56372,7 +56372,7 @@
         <v>46170</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>45967</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>46170</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>46170</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56674,7 +56674,7 @@
         <v>46170</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>46170</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>46171</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>46170</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>46175</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57059,7 +57059,7 @@
         <v>46175</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>46174</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>46174</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57283,7 +57283,7 @@
         <v>46174</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57356,7 +57356,7 @@
         <v>45603</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>46177</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>46177</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>46181</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57658,7 +57658,7 @@
         <v>46185</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57731,7 +57731,7 @@
         <v>46185</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>46185</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57877,7 +57877,7 @@
         <v>46185</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57950,7 +57950,7 @@
         <v>46185</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58023,7 +58023,7 @@
         <v>46189</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58101,7 +58101,7 @@
         <v>46189</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58174,7 +58174,7 @@
         <v>46189</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58247,7 +58247,7 @@
         <v>46076</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58325,7 +58325,7 @@
         <v>45615</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58398,7 +58398,7 @@
         <v>46189</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58471,7 +58471,7 @@
         <v>46189</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58549,7 +58549,7 @@
         <v>45981</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58627,7 +58627,7 @@
         <v>46188</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58705,7 +58705,7 @@
         <v>46055</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58783,7 +58783,7 @@
         <v>46190</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>46190</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>46190</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>46191</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59080,7 +59080,7 @@
         <v>46195</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59158,7 +59158,7 @@
         <v>46196</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59236,7 +59236,7 @@
         <v>46196</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59314,7 +59314,7 @@
         <v>46196</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59392,7 +59392,7 @@
         <v>46198</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59465,7 +59465,7 @@
         <v>46183</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59543,7 +59543,7 @@
         <v>46199</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59621,7 +59621,7 @@
         <v>46198</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59699,7 +59699,7 @@
         <v>46199</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>46198</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>46203</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59928,7 +59928,7 @@
         <v>46203</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60006,7 +60006,7 @@
         <v>46203</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60079,7 +60079,7 @@
         <v>46205</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60152,7 +60152,7 @@
         <v>46205</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60225,7 +60225,7 @@
         <v>46204</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60303,7 +60303,7 @@
         <v>46205</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>46104</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60449,7 +60449,7 @@
         <v>46206</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60522,7 +60522,7 @@
         <v>46216</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60600,7 +60600,7 @@
         <v>46218</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60678,7 +60678,7 @@
         <v>45982</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60756,7 +60756,7 @@
         <v>46098</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60834,7 +60834,7 @@
         <v>46071</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60912,7 +60912,7 @@
         <v>46223</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60985,7 +60985,7 @@
         <v>46223</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61058,7 +61058,7 @@
         <v>46267</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61136,7 +61136,7 @@
         <v>46268</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61214,7 +61214,7 @@
         <v>46268</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61292,7 +61292,7 @@
         <v>46269</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61370,7 +61370,7 @@
         <v>46269</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
         <v>46230</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61526,7 +61526,7 @@
         <v>46274</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61599,7 +61599,7 @@
         <v>46275</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61677,7 +61677,7 @@
         <v>46275</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61755,7 +61755,7 @@
         <v>46279</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61833,7 +61833,7 @@
         <v>46140</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>46140</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
         <v>46283</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>46283</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>46052</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62203,7 +62203,7 @@
         <v>46245</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62281,7 +62281,7 @@
         <v>46099</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>46289</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62432,7 +62432,7 @@
         <v>46293</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62510,7 +62510,7 @@
         <v>46065</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62588,7 +62588,7 @@
         <v>46066</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62661,7 +62661,7 @@
         <v>46293</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62739,7 +62739,7 @@
         <v>46293</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62817,7 +62817,7 @@
         <v>46104</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62895,7 +62895,7 @@
         <v>46071</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62968,7 +62968,7 @@
         <v>46052</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63041,7 +63041,7 @@
         <v>46293</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63119,7 +63119,7 @@
         <v>46142</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63197,7 +63197,7 @@
         <v>45986</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63270,7 +63270,7 @@
         <v>46121</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63343,7 +63343,7 @@
         <v>46297</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63416,7 +63416,7 @@
         <v>46156</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63494,7 +63494,7 @@
         <v>46300</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63567,7 +63567,7 @@
         <v>46254</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63645,7 +63645,7 @@
         <v>46092</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63718,7 +63718,7 @@
         <v>46079</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63796,7 +63796,7 @@
         <v>46038</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63869,7 +63869,7 @@
         <v>46100</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63942,7 +63942,7 @@
         <v>46101</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64020,7 +64020,7 @@
         <v>46036</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64093,7 +64093,7 @@
         <v>46188</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64171,7 +64171,7 @@
         <v>46126</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64244,7 +64244,7 @@
         <v>46121</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64317,7 +64317,7 @@
         <v>46213</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64390,7 +64390,7 @@
         <v>46260</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64468,7 +64468,7 @@
         <v>46045</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64541,7 +64541,7 @@
         <v>46224</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64619,7 +64619,7 @@
         <v>46223</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64697,7 +64697,7 @@
         <v>46224</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64775,7 +64775,7 @@
         <v>46258</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64853,7 +64853,7 @@
         <v>46220</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64931,7 +64931,7 @@
         <v>46232</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65009,7 +65009,7 @@
         <v>45323</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65087,7 +65087,7 @@
         <v>45638</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65165,7 +65165,7 @@
         <v>45315</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>45699</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65321,7 +65321,7 @@
         <v>44904</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65399,7 +65399,7 @@
         <v>46058</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65472,7 +65472,7 @@
         <v>46089</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65550,7 +65550,7 @@
         <v>46148</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65623,7 +65623,7 @@
         <v>46148</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65696,7 +65696,7 @@
         <v>46048</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65769,7 +65769,7 @@
         <v>46293</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65847,7 +65847,7 @@
         <v>46300</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65920,7 +65920,7 @@
         <v>46255</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45106</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>46132</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46101</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45841</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46170</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46094</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45469</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>46125</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>46185</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46126</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46153</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46125</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>46125</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46036</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>46044</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>46114</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46132</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45280</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45022</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45754</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45448</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45469</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>46139</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>46104</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46085</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>46077</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>44496</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>45247</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>46009</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>46038</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46053</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>46056</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>46077</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>46097</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>46100</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>46101</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46125</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>46091</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>46283</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>46282</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>46282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44953</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45519</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>46302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44529</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44532</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44795</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44492</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44795</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44802</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44705</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44643</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44663</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44889</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45534</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45180</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44804</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45611</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45156</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>44890</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45548</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44879</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45211</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>45252</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45341</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45617</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45645</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45254</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>44950</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>45772</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44797</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44986</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45618</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45132</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45611</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45432</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45443</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44887</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45757</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45488</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45041</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45048</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45510</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45111</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45223</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>46029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45870</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45799</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46050</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>45656</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>46137</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>46137</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>46043</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45800</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>46052</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46052</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44915</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45821</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>46036</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>46021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45889</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45490</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>46139</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45888</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>46107</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45891</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45139</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45744</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>46136</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>46136</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45884</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45894</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>46064</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>46138</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>46042</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>46065</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45896</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45181</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>45712</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45608</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45608</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44700</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45840</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>46052</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>46140</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>46106</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>46064</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>46035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>46071</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>46048</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>46140</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>46140</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45111</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>46027</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>46056</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>46063</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>46071</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45488</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>46098</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>46140</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>46125</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>46091</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45903</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46029</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45204</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>46063</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>46043</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46037</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>46073</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45905</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45835</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>46056</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>46052</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>46034</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>46077</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45645</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>46140</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45777</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46063</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45478</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45441</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45911</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45254</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45911</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46104</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45994</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45450</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46146</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45366</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>46127</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>46122</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46125</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45488</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44712</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>46147</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>46147</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45301</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>46148</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45925</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45237</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>46148</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>46134</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46149</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45602</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46148</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>46148</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45027</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45602</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45602</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45608</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45162</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44522</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45747</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45846</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>45554</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>45216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45554</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>44816</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45590</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45929</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45929</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>44501</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45617</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44845</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44525</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45582</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>46119</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>46066</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45930</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>46153</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45932</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>46071</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>46128</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46153</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45488</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45937</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45937</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45937</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45937</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45834</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45700</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45342</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44970</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45986</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>46043</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>45926</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>46155</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>45953</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>46154</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45952</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46155</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45754</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45953</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>46093</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>46119</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>46056</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45330</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>46155</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>46104</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>46088</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45957</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>46044</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>46049</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45954</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45954</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>46093</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>46093</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45994</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45994</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>46156</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>46122</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45959</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>46100</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>46161</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>46160</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>45966</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45967</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>45967</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>46161</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>45674</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>45972</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>45973</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>45972</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45973</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45973</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45972</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45973</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45973</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>46163</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45975</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45716</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45978</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45291</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45978</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45624</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>45551</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>45985</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>45986</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>46164</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>46164</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45988</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45649</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>46044</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>46169</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45995</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>46169</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>46169</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>46168</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45995</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>45994</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>46169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>45996</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>46168</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45600</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46169</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>46000</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>46168</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>46170</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46170</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>46170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46170</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>46170</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46170</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46170</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>46085</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46006</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45989</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45455</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46009</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46009</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>46023</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>46174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45967</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46174</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>46013</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>46013</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>44883</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46010</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>46009</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>46014</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46171</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>46021</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45554</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>46027</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>46027</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>46027</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>46027</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>46027</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>46024</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>46027</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>46029</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46028</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46028</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>46029</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>46024</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>46029</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46029</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45620</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45203</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>46031</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>46031</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46034</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46034</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>46033</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46035</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>46035</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>46175</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46175</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>46035</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>46037</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>46036</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>46036</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>46036</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>46036</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45603</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46036</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>46036</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>46041</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46041</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>46038</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>46038</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>46043</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>46043</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>46177</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>46177</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>46044</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>46044</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>46045</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>46036</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46044</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45398</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>46045</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45134</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45134</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>46036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>46049</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45646</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>46049</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>46048</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46048</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>46050</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>44839</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>46051</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46050</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>46051</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>46052</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>46181</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46053</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>46052</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>46052</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46055</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>46056</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>46056</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>46057</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>46056</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>46056</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>46056</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46056</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>46056</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>46056</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44496</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>46059</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>46062</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>46062</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>46062</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>46062</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>46065</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>46064</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45699</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>46064</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>46065</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>46064</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45184</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>46185</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>46185</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>46071</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>46071</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46071</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46071</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>46071</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>46071</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>46071</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>46071</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>46056</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>46188</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46031</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>46072</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>46072</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>46072</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46072</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>46073</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46077</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46078</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>46077</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>46077</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>46077</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46031</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46076</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46077</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>46077</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46185</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>46185</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>46185</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>46079</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>46080</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>46080</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>46080</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>46079</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>46190</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45511</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>44820</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>46083</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45152</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>46083</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>44643</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>46083</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>44893</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>46085</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45107</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45981</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>46087</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45243</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46076</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46190</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45615</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>46089</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45671</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>46092</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>46189</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>46189</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>46091</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46189</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>46189</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>46189</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>46191</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>45210</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         <v>46093</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>46094</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>46094</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>46093</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>46094</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46093</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>46055</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>46098</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>46098</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46098</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>46196</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>46098</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>46097</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>46098</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>46099</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>46196</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>46196</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>46098</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>46100</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>46100</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>46099</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>46104</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45593</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>46104</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>46195</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>46104</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>46101</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46245,7 +46245,7 @@
         <v>46104</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>46104</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>46104</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>46106</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>46106</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>46106</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45678</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>46105</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>46106</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45156</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>46106</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>46108</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>46108</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>46198</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>46111</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>46112</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>46112</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>46198</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>46112</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45674</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>46111</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>46114</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>46114</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>46114</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>46114</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>46076</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>46199</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>46076</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46077</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46119</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>46076</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>46119</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>46118</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>46076</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>46121</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>46121</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         <v>46049</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>46125</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45527</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>46199</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>46126</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>46126</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>46098</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>46127</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>46105</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>46127</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>46112</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>46128</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>46112</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>46128</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>46106</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>46127</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>44781</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>46183</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>46104</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>46204</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50576,7 +50576,7 @@
         <v>46132</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46133</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46132</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>46133</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>46132</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>46132</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45261</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>46132</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>46133</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>46132</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>46132</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>46132</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>46203</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>46134</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>46203</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>46134</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>46114</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>46119</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>46133</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>46134</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>46203</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>46043</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>46205</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>46064</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>46137</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45800</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>46049</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>46106</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45946</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>46206</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>46205</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>44663</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45925</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>46048</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>46055</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>46205</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45758</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>45534</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45334</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53528,7 +53528,7 @@
         <v>45609</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>46216</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>45022</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45139</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>46218</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>46071</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>46098</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54064,7 +54064,7 @@
         <v>45237</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54137,7 +54137,7 @@
         <v>45982</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45698</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>46223</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45727</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>46223</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>46230</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54585,7 +54585,7 @@
         <v>45497</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54658,7 +54658,7 @@
         <v>44838</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>46275</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>46274</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54882,7 +54882,7 @@
         <v>45156</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45134</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>46275</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55116,7 +55116,7 @@
         <v>46140</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55189,7 +55189,7 @@
         <v>45134</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55267,7 +55267,7 @@
         <v>45596</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>46279</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55418,7 +55418,7 @@
         <v>46140</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>45240</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>45609</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55647,7 +55647,7 @@
         <v>45139</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45544</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55793,7 +55793,7 @@
         <v>46283</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55866,7 +55866,7 @@
         <v>46283</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55944,7 +55944,7 @@
         <v>45481</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>45623</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>44725</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45281</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>44950</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45068</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>46052</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56465,7 +56465,7 @@
         <v>45771</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45068</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>45534</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56694,7 +56694,7 @@
         <v>46289</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>45230</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>45156</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>46245</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57006,7 +57006,7 @@
         <v>45070</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57079,7 +57079,7 @@
         <v>46099</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>45628</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57225,7 +57225,7 @@
         <v>45771</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>46293</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         <v>45484</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>45280</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>46293</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>45239</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>46293</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>46104</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57834,7 +57834,7 @@
         <v>46293</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57912,7 +57912,7 @@
         <v>45600</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45744</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45072</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58136,7 +58136,7 @@
         <v>46052</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58209,7 +58209,7 @@
         <v>46065</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58287,7 +58287,7 @@
         <v>46071</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45448</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>46066</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45666</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>46038</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45265</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45134</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>46101</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58886,7 +58886,7 @@
         <v>46297</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>46254</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59037,7 +59037,7 @@
         <v>46036</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>46142</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59188,7 +59188,7 @@
         <v>46121</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59261,7 +59261,7 @@
         <v>46156</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>44950</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59412,7 +59412,7 @@
         <v>46092</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59485,7 +59485,7 @@
         <v>46100</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59558,7 +59558,7 @@
         <v>45776</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59631,7 +59631,7 @@
         <v>45986</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         <v>46126</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>46300</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>45455</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59923,7 +59923,7 @@
         <v>45608</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45544</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60069,7 +60069,7 @@
         <v>45258</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>46079</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60220,7 +60220,7 @@
         <v>45786</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60298,7 +60298,7 @@
         <v>45786</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>46224</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60454,7 +60454,7 @@
         <v>46220</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60532,7 +60532,7 @@
         <v>46258</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>46260</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45478</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60766,7 +60766,7 @@
         <v>45617</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>44746</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60917,7 +60917,7 @@
         <v>46232</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60995,7 +60995,7 @@
         <v>46188</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61073,7 +61073,7 @@
         <v>46213</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61146,7 +61146,7 @@
         <v>46223</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>46045</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45776</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>46121</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
         <v>45790</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>45621</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>45468</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61667,7 +61667,7 @@
         <v>45593</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61740,7 +61740,7 @@
         <v>45754</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61813,7 +61813,7 @@
         <v>44659</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>45282</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45434</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>45596</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62105,7 +62105,7 @@
         <v>45747</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45803</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62256,7 +62256,7 @@
         <v>45800</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62334,7 +62334,7 @@
         <v>45800</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62412,7 +62412,7 @@
         <v>45800</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45800</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62568,7 +62568,7 @@
         <v>45800</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62646,7 +62646,7 @@
         <v>45800</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62724,7 +62724,7 @@
         <v>45805</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62797,7 +62797,7 @@
         <v>46268</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>46269</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62953,7 +62953,7 @@
         <v>45817</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>45817</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>45817</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>46267</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>45819</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63338,7 +63338,7 @@
         <v>45819</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63416,7 +63416,7 @@
         <v>46311</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63494,7 +63494,7 @@
         <v>45821</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63572,7 +63572,7 @@
         <v>45824</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63650,7 +63650,7 @@
         <v>46094</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63728,7 +63728,7 @@
         <v>46269</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>46224</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>45827</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>45827</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>45827</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>46268</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>45827</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64269,7 +64269,7 @@
         <v>45838</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
         <v>45840</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45840</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64493,7 +64493,7 @@
         <v>45109</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64566,7 +64566,7 @@
         <v>45719</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64639,7 +64639,7 @@
         <v>45073</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64712,7 +64712,7 @@
         <v>45851</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>45719</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64868,7 +64868,7 @@
         <v>45551</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
         <v>45323</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65019,7 +65019,7 @@
         <v>45638</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45315</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65175,7 +65175,7 @@
         <v>45699</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65253,7 +65253,7 @@
         <v>44904</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65331,7 +65331,7 @@
         <v>46058</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65404,7 +65404,7 @@
         <v>46089</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65482,7 +65482,7 @@
         <v>46148</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65555,7 +65555,7 @@
         <v>46148</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65628,7 +65628,7 @@
         <v>46048</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65701,7 +65701,7 @@
         <v>46293</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65779,7 +65779,7 @@
         <v>46300</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65852,7 +65852,7 @@
         <v>46255</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65930,7 +65930,7 @@
         <v>46307</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>46099</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1093,7 +1093,7 @@
         <v>45545</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1209,7 +1209,7 @@
         <v>45106</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>46044</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>46132</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>46101</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>45841</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46132</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46220</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46170</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46094</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>45469</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2939,7 +2939,7 @@
         <v>46125</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>46185</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>46126</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3270,7 +3270,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46153</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46125</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>46125</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3710,7 +3710,7 @@
         <v>46139</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>46036</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3927,7 +3927,7 @@
         <v>46044</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>46114</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46132</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45280</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45022</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>45754</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4805,7 +4805,7 @@
         <v>45448</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>46070</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45469</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5135,7 +5135,7 @@
         <v>46139</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5245,7 +5245,7 @@
         <v>46104</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5359,7 +5359,7 @@
         <v>46085</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>46077</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>44496</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>45247</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         <v>45582</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5913,7 +5913,7 @@
         <v>45972</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6023,7 +6023,7 @@
         <v>46009</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>46038</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>46053</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>46056</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6451,7 +6451,7 @@
         <v>46077</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>46097</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>46100</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6771,7 +6771,7 @@
         <v>46101</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6885,7 +6885,7 @@
         <v>46125</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6999,7 +6999,7 @@
         <v>46091</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         <v>46076</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7222,7 +7222,7 @@
         <v>46283</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>46282</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>46282</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>44953</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45519</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         <v>46302</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44529</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44532</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44795</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44492</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44795</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         <v>44858</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44802</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44881</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44705</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         <v>44872</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9397,7 +9397,7 @@
         <v>44532</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44643</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9548,7 +9548,7 @@
         <v>44663</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>44889</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9699,7 +9699,7 @@
         <v>45534</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>45180</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44804</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9923,7 +9923,7 @@
         <v>45611</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45156</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>44890</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10152,7 +10152,7 @@
         <v>45548</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10230,7 +10230,7 @@
         <v>44879</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10303,7 +10303,7 @@
         <v>45211</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>45252</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10454,7 +10454,7 @@
         <v>45167</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10527,7 +10527,7 @@
         <v>45341</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10600,7 +10600,7 @@
         <v>45617</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45645</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>45254</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>44950</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>45772</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10975,7 +10975,7 @@
         <v>44797</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
         <v>45434</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11121,7 +11121,7 @@
         <v>44986</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45618</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45132</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45611</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45432</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>45443</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>45169</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44887</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>45757</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>45488</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45581</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45041</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45048</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45510</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45111</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45223</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>45586</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>44950</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>46029</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45870</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45799</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12689,7 +12689,7 @@
         <v>46050</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
         <v>45656</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>46137</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12918,7 +12918,7 @@
         <v>46137</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>46043</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>45803</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45800</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>46052</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46052</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13371,7 +13371,7 @@
         <v>44915</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45821</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>46036</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45184</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13668,7 +13668,7 @@
         <v>46021</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13741,7 +13741,7 @@
         <v>45889</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>45490</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>46139</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45888</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14048,7 +14048,7 @@
         <v>45889</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>45889</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>46107</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45891</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14350,7 +14350,7 @@
         <v>45139</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45744</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14501,7 +14501,7 @@
         <v>45705</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14574,7 +14574,7 @@
         <v>46136</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>46136</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14720,7 +14720,7 @@
         <v>45884</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14793,7 +14793,7 @@
         <v>45894</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>46064</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14944,7 +14944,7 @@
         <v>46138</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15022,7 +15022,7 @@
         <v>46042</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>46065</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15178,7 +15178,7 @@
         <v>45896</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45181</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15324,7 +15324,7 @@
         <v>45712</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15397,7 +15397,7 @@
         <v>45608</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>45608</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>44700</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>46034</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45840</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15787,7 +15787,7 @@
         <v>46052</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15865,7 +15865,7 @@
         <v>46140</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15938,7 +15938,7 @@
         <v>46106</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16016,7 +16016,7 @@
         <v>46064</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>46035</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>46071</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>46048</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16308,7 +16308,7 @@
         <v>46140</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>46140</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>45111</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16537,7 +16537,7 @@
         <v>45111</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16610,7 +16610,7 @@
         <v>46027</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16688,7 +16688,7 @@
         <v>46056</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16766,7 +16766,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16839,7 +16839,7 @@
         <v>46063</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>46141</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>46071</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>45488</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17141,7 +17141,7 @@
         <v>46098</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17214,7 +17214,7 @@
         <v>45526</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17292,7 +17292,7 @@
         <v>46140</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>46125</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>46091</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>45903</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>45903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>45903</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>46029</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>45204</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>46063</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>46043</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>46037</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>46073</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>45905</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18266,7 +18266,7 @@
         <v>45835</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45334</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>46056</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>46052</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>46034</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>46077</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45645</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>46140</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18865,7 +18865,7 @@
         <v>45911</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45777</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>46063</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45478</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45441</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45911</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45254</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45911</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45911</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
         <v>46104</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45994</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45450</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19766,7 +19766,7 @@
         <v>46146</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19844,7 +19844,7 @@
         <v>45366</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>46127</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20000,7 +20000,7 @@
         <v>46122</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20078,7 +20078,7 @@
         <v>46125</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45488</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>44712</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
         <v>46147</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20380,7 +20380,7 @@
         <v>46147</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20458,7 +20458,7 @@
         <v>45301</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20531,7 +20531,7 @@
         <v>46148</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45925</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>45237</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20760,7 +20760,7 @@
         <v>46148</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20838,7 +20838,7 @@
         <v>46134</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20916,7 +20916,7 @@
         <v>46149</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45644</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21067,7 +21067,7 @@
         <v>45602</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>46148</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21223,7 +21223,7 @@
         <v>46148</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21301,7 +21301,7 @@
         <v>45027</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21379,7 +21379,7 @@
         <v>45602</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>45602</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21535,7 +21535,7 @@
         <v>45608</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21613,7 +21613,7 @@
         <v>45162</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21691,7 +21691,7 @@
         <v>44522</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21769,7 +21769,7 @@
         <v>45747</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21842,7 +21842,7 @@
         <v>45846</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21920,7 +21920,7 @@
         <v>45554</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -21998,7 +21998,7 @@
         <v>45216</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22076,7 +22076,7 @@
         <v>45554</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>44816</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22232,7 +22232,7 @@
         <v>45590</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45929</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22383,7 +22383,7 @@
         <v>45929</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22456,7 +22456,7 @@
         <v>44501</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22534,7 +22534,7 @@
         <v>45617</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22612,7 +22612,7 @@
         <v>44845</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>44525</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22768,7 +22768,7 @@
         <v>45582</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
         <v>45107</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22924,7 +22924,7 @@
         <v>46119</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23002,7 +23002,7 @@
         <v>46066</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23080,7 +23080,7 @@
         <v>45930</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>46153</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23226,7 +23226,7 @@
         <v>45932</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23304,7 +23304,7 @@
         <v>46071</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23382,7 +23382,7 @@
         <v>46128</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>46153</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23533,7 +23533,7 @@
         <v>45488</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23606,7 +23606,7 @@
         <v>45937</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23679,7 +23679,7 @@
         <v>45937</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23752,7 +23752,7 @@
         <v>45937</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23825,7 +23825,7 @@
         <v>45937</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23898,7 +23898,7 @@
         <v>45937</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23976,7 +23976,7 @@
         <v>45937</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24049,7 +24049,7 @@
         <v>45834</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45700</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45342</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24268,7 +24268,7 @@
         <v>44970</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24341,7 +24341,7 @@
         <v>45986</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>46043</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24492,7 +24492,7 @@
         <v>45926</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24565,7 +24565,7 @@
         <v>46155</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24638,7 +24638,7 @@
         <v>45953</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24711,7 +24711,7 @@
         <v>46154</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24784,7 +24784,7 @@
         <v>45952</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24862,7 +24862,7 @@
         <v>46155</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24935,7 +24935,7 @@
         <v>45754</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25008,7 +25008,7 @@
         <v>45953</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25081,7 +25081,7 @@
         <v>46093</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>46119</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>46056</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25300,7 +25300,7 @@
         <v>45909</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25373,7 +25373,7 @@
         <v>45330</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25451,7 +25451,7 @@
         <v>46155</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25524,7 +25524,7 @@
         <v>46104</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25602,7 +25602,7 @@
         <v>46088</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25680,7 +25680,7 @@
         <v>45957</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25758,7 +25758,7 @@
         <v>46044</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>46049</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25904,7 +25904,7 @@
         <v>45954</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45954</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>46093</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>46093</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>45994</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26284,7 +26284,7 @@
         <v>45994</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26357,7 +26357,7 @@
         <v>46156</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26430,7 +26430,7 @@
         <v>46122</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45959</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26581,7 +26581,7 @@
         <v>46100</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26654,7 +26654,7 @@
         <v>46161</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45106</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26805,7 +26805,7 @@
         <v>46160</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>45966</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45967</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27024,7 +27024,7 @@
         <v>45967</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27097,7 +27097,7 @@
         <v>46161</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27170,7 +27170,7 @@
         <v>45674</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27243,7 +27243,7 @@
         <v>45972</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>45973</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27389,7 +27389,7 @@
         <v>45973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         <v>45972</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45973</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45973</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27681,7 +27681,7 @@
         <v>45973</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27754,7 +27754,7 @@
         <v>45972</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         <v>45258</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27900,7 +27900,7 @@
         <v>45973</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -27978,7 +27978,7 @@
         <v>45973</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28051,7 +28051,7 @@
         <v>46163</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45975</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45716</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28275,7 +28275,7 @@
         <v>45978</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>45978</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45978</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45978</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28567,7 +28567,7 @@
         <v>45978</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28640,7 +28640,7 @@
         <v>45291</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28713,7 +28713,7 @@
         <v>45978</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28786,7 +28786,7 @@
         <v>45978</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45624</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28937,7 +28937,7 @@
         <v>45551</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29010,7 +29010,7 @@
         <v>45985</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29083,7 +29083,7 @@
         <v>45985</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         <v>45986</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>46164</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29307,7 +29307,7 @@
         <v>46164</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29385,7 +29385,7 @@
         <v>45988</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29463,7 +29463,7 @@
         <v>45649</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>46044</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29609,7 +29609,7 @@
         <v>46169</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29682,7 +29682,7 @@
         <v>45995</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>46169</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29838,7 +29838,7 @@
         <v>46169</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29916,7 +29916,7 @@
         <v>46168</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -29994,7 +29994,7 @@
         <v>45995</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30072,7 +30072,7 @@
         <v>45994</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30150,7 +30150,7 @@
         <v>46169</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30228,7 +30228,7 @@
         <v>45996</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>46168</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30384,7 +30384,7 @@
         <v>45600</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>46169</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30530,7 +30530,7 @@
         <v>46000</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>46168</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30686,7 +30686,7 @@
         <v>46170</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30759,7 +30759,7 @@
         <v>46170</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30837,7 +30837,7 @@
         <v>46170</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>46170</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>46170</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31071,7 +31071,7 @@
         <v>46170</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31149,7 +31149,7 @@
         <v>46170</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31227,7 +31227,7 @@
         <v>46085</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31300,7 +31300,7 @@
         <v>46006</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31373,7 +31373,7 @@
         <v>45989</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31451,7 +31451,7 @@
         <v>45455</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31524,7 +31524,7 @@
         <v>46009</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31602,7 +31602,7 @@
         <v>46009</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>46023</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31748,7 +31748,7 @@
         <v>46174</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31821,7 +31821,7 @@
         <v>45967</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31894,7 +31894,7 @@
         <v>46174</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>46013</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32045,7 +32045,7 @@
         <v>46013</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32123,7 +32123,7 @@
         <v>44883</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>46010</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32274,7 +32274,7 @@
         <v>46174</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32347,7 +32347,7 @@
         <v>46009</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>46014</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32498,7 +32498,7 @@
         <v>46171</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32571,7 +32571,7 @@
         <v>46021</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32644,7 +32644,7 @@
         <v>45554</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>46027</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32795,7 +32795,7 @@
         <v>46027</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32868,7 +32868,7 @@
         <v>46027</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32941,7 +32941,7 @@
         <v>46027</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33014,7 +33014,7 @@
         <v>46027</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>46024</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33160,7 +33160,7 @@
         <v>46027</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>46029</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33306,7 +33306,7 @@
         <v>46028</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33379,7 +33379,7 @@
         <v>46028</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33452,7 +33452,7 @@
         <v>46029</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33525,7 +33525,7 @@
         <v>46024</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>46029</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33671,7 +33671,7 @@
         <v>46029</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33744,7 +33744,7 @@
         <v>45620</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33817,7 +33817,7 @@
         <v>45203</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>46031</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33963,7 +33963,7 @@
         <v>46031</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34036,7 +34036,7 @@
         <v>46034</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34114,7 +34114,7 @@
         <v>46034</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34187,7 +34187,7 @@
         <v>46033</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>46035</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34333,7 +34333,7 @@
         <v>46035</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34406,7 +34406,7 @@
         <v>46175</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>46175</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34562,7 +34562,7 @@
         <v>46035</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34635,7 +34635,7 @@
         <v>46037</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>46036</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>46036</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34854,7 +34854,7 @@
         <v>46036</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34927,7 +34927,7 @@
         <v>46036</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35000,7 +35000,7 @@
         <v>45603</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46036</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>46036</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>46041</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35292,7 +35292,7 @@
         <v>46041</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35365,7 +35365,7 @@
         <v>46038</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35438,7 +35438,7 @@
         <v>46038</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35511,7 +35511,7 @@
         <v>46043</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35584,7 +35584,7 @@
         <v>46043</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35657,7 +35657,7 @@
         <v>46177</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35735,7 +35735,7 @@
         <v>46177</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>46044</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35886,7 +35886,7 @@
         <v>46044</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>46045</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>46036</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>46044</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36183,7 +36183,7 @@
         <v>45398</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>46045</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36329,7 +36329,7 @@
         <v>45134</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45134</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36485,7 +36485,7 @@
         <v>46036</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>46049</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36631,7 +36631,7 @@
         <v>45646</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36704,7 +36704,7 @@
         <v>46049</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36777,7 +36777,7 @@
         <v>46048</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36850,7 +36850,7 @@
         <v>46048</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36923,7 +36923,7 @@
         <v>46050</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>44839</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37079,7 +37079,7 @@
         <v>46051</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37157,7 +37157,7 @@
         <v>46050</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37235,7 +37235,7 @@
         <v>46051</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37308,7 +37308,7 @@
         <v>46052</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37381,7 +37381,7 @@
         <v>46181</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37454,7 +37454,7 @@
         <v>46053</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37527,7 +37527,7 @@
         <v>46052</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37600,7 +37600,7 @@
         <v>46052</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37673,7 +37673,7 @@
         <v>46055</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37751,7 +37751,7 @@
         <v>46056</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37829,7 +37829,7 @@
         <v>46056</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37902,7 +37902,7 @@
         <v>46057</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -37980,7 +37980,7 @@
         <v>46056</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>46056</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38126,7 +38126,7 @@
         <v>46056</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
         <v>46056</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>46056</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38345,7 +38345,7 @@
         <v>46056</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44496</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38496,7 +38496,7 @@
         <v>46059</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38569,7 +38569,7 @@
         <v>46062</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38642,7 +38642,7 @@
         <v>46062</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38715,7 +38715,7 @@
         <v>46062</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38788,7 +38788,7 @@
         <v>46062</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38866,7 +38866,7 @@
         <v>46065</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -38944,7 +38944,7 @@
         <v>46064</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39017,7 +39017,7 @@
         <v>45699</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39095,7 +39095,7 @@
         <v>46064</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39168,7 +39168,7 @@
         <v>46065</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39241,7 +39241,7 @@
         <v>46064</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39319,7 +39319,7 @@
         <v>45184</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>46185</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39470,7 +39470,7 @@
         <v>46185</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39543,7 +39543,7 @@
         <v>46071</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39621,7 +39621,7 @@
         <v>46071</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39699,7 +39699,7 @@
         <v>46071</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39772,7 +39772,7 @@
         <v>46071</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>46071</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39923,7 +39923,7 @@
         <v>46071</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -39996,7 +39996,7 @@
         <v>46071</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>46071</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>46056</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40220,7 +40220,7 @@
         <v>46188</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>46031</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>46072</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40444,7 +40444,7 @@
         <v>46072</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40517,7 +40517,7 @@
         <v>46072</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40595,7 +40595,7 @@
         <v>46072</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>46073</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46077</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         <v>46078</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40902,7 +40902,7 @@
         <v>46077</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -40980,7 +40980,7 @@
         <v>46077</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>46077</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41136,7 +41136,7 @@
         <v>46031</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41209,7 +41209,7 @@
         <v>46076</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41287,7 +41287,7 @@
         <v>46077</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>46077</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41438,7 +41438,7 @@
         <v>46185</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41511,7 +41511,7 @@
         <v>46185</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41584,7 +41584,7 @@
         <v>46185</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41657,7 +41657,7 @@
         <v>46079</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41730,7 +41730,7 @@
         <v>46080</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>46080</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41876,7 +41876,7 @@
         <v>46080</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41949,7 +41949,7 @@
         <v>46079</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>46190</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42095,7 +42095,7 @@
         <v>45511</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42168,7 +42168,7 @@
         <v>44820</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42246,7 +42246,7 @@
         <v>46083</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45152</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42392,7 +42392,7 @@
         <v>46083</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42470,7 +42470,7 @@
         <v>44643</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42543,7 +42543,7 @@
         <v>46083</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42621,7 +42621,7 @@
         <v>44893</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>46085</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42767,7 +42767,7 @@
         <v>45107</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42845,7 +42845,7 @@
         <v>45981</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42923,7 +42923,7 @@
         <v>46087</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45243</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43069,7 +43069,7 @@
         <v>46076</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43147,7 +43147,7 @@
         <v>46190</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43220,7 +43220,7 @@
         <v>46190</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45615</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>46089</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45671</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>46092</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43595,7 +43595,7 @@
         <v>46189</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43668,7 +43668,7 @@
         <v>46189</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43741,7 +43741,7 @@
         <v>46091</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43814,7 +43814,7 @@
         <v>46189</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43892,7 +43892,7 @@
         <v>46189</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>46189</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44043,7 +44043,7 @@
         <v>46191</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44121,7 +44121,7 @@
         <v>45210</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44194,7 +44194,7 @@
         <v>46093</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44267,7 +44267,7 @@
         <v>46094</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44345,7 +44345,7 @@
         <v>46094</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44418,7 +44418,7 @@
         <v>46093</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>46094</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44564,7 +44564,7 @@
         <v>46093</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44642,7 +44642,7 @@
         <v>46055</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44720,7 +44720,7 @@
         <v>46098</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>46098</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>46098</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -44949,7 +44949,7 @@
         <v>46196</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45027,7 +45027,7 @@
         <v>46098</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>46097</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45178,7 +45178,7 @@
         <v>46098</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>46099</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45329,7 +45329,7 @@
         <v>46196</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45407,7 +45407,7 @@
         <v>46196</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45485,7 +45485,7 @@
         <v>46098</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45563,7 +45563,7 @@
         <v>46100</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45636,7 +45636,7 @@
         <v>46100</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45709,7 +45709,7 @@
         <v>46099</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45787,7 +45787,7 @@
         <v>46104</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45865,7 +45865,7 @@
         <v>45593</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -45938,7 +45938,7 @@
         <v>46104</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46011,7 +46011,7 @@
         <v>46195</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>46104</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46167,7 +46167,7 @@
         <v>46101</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46245,7 +46245,7 @@
         <v>46104</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>46104</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>46104</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46474,7 +46474,7 @@
         <v>46106</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46552,7 +46552,7 @@
         <v>46106</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46625,7 +46625,7 @@
         <v>46106</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46698,7 +46698,7 @@
         <v>45678</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46771,7 +46771,7 @@
         <v>46105</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46849,7 +46849,7 @@
         <v>46106</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45156</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47005,7 +47005,7 @@
         <v>46106</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>46108</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47161,7 +47161,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>46108</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>46198</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47390,7 +47390,7 @@
         <v>46111</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47463,7 +47463,7 @@
         <v>46112</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>46112</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47619,7 +47619,7 @@
         <v>46198</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47692,7 +47692,7 @@
         <v>46112</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47770,7 +47770,7 @@
         <v>45674</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47843,7 +47843,7 @@
         <v>46111</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -47916,7 +47916,7 @@
         <v>46114</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -47994,7 +47994,7 @@
         <v>46114</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>46114</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>46114</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48218,7 +48218,7 @@
         <v>46076</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48296,7 +48296,7 @@
         <v>46199</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48374,7 +48374,7 @@
         <v>46076</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48452,7 +48452,7 @@
         <v>46077</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48530,7 +48530,7 @@
         <v>46119</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48603,7 +48603,7 @@
         <v>46076</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48681,7 +48681,7 @@
         <v>46119</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48759,7 +48759,7 @@
         <v>46118</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48832,7 +48832,7 @@
         <v>46076</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48910,7 +48910,7 @@
         <v>46121</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -48983,7 +48983,7 @@
         <v>46121</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49056,7 +49056,7 @@
         <v>46049</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49129,7 +49129,7 @@
         <v>46125</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49207,7 +49207,7 @@
         <v>45527</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>46199</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49363,7 +49363,7 @@
         <v>46126</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49436,7 +49436,7 @@
         <v>46126</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49514,7 +49514,7 @@
         <v>46098</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49592,7 +49592,7 @@
         <v>46127</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>46105</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49743,7 +49743,7 @@
         <v>46127</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49816,7 +49816,7 @@
         <v>46112</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49894,7 +49894,7 @@
         <v>46128</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -49967,7 +49967,7 @@
         <v>46112</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50045,7 +50045,7 @@
         <v>46128</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>46106</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50201,7 +50201,7 @@
         <v>46127</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50274,7 +50274,7 @@
         <v>44781</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50347,7 +50347,7 @@
         <v>46183</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>46104</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50498,7 +50498,7 @@
         <v>46204</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50576,7 +50576,7 @@
         <v>46132</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50654,7 +50654,7 @@
         <v>46133</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50732,7 +50732,7 @@
         <v>46132</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50810,7 +50810,7 @@
         <v>46133</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50888,7 +50888,7 @@
         <v>46132</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -50961,7 +50961,7 @@
         <v>46132</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51039,7 +51039,7 @@
         <v>45261</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>46132</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>46133</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>46132</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>46132</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>46132</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>46203</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51570,7 +51570,7 @@
         <v>46134</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51643,7 +51643,7 @@
         <v>46203</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51721,7 +51721,7 @@
         <v>46134</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>46114</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>46119</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>46133</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>46134</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>46203</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>46043</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>46205</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52315,7 +52315,7 @@
         <v>46064</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52388,7 +52388,7 @@
         <v>46137</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45800</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52544,7 +52544,7 @@
         <v>46049</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>46106</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>45946</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>46206</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52851,7 +52851,7 @@
         <v>46205</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52924,7 +52924,7 @@
         <v>44663</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53002,7 +53002,7 @@
         <v>45925</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53080,7 +53080,7 @@
         <v>46048</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53158,7 +53158,7 @@
         <v>46055</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53236,7 +53236,7 @@
         <v>46205</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53309,7 +53309,7 @@
         <v>45758</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53382,7 +53382,7 @@
         <v>45534</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53455,7 +53455,7 @@
         <v>45334</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53528,7 +53528,7 @@
         <v>45609</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53606,7 +53606,7 @@
         <v>46216</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53684,7 +53684,7 @@
         <v>45022</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53757,7 +53757,7 @@
         <v>45139</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53830,7 +53830,7 @@
         <v>46218</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53908,7 +53908,7 @@
         <v>46071</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -53986,7 +53986,7 @@
         <v>46098</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54064,7 +54064,7 @@
         <v>45237</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54137,7 +54137,7 @@
         <v>45982</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54215,7 +54215,7 @@
         <v>45698</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54288,7 +54288,7 @@
         <v>46223</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54361,7 +54361,7 @@
         <v>45727</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54434,7 +54434,7 @@
         <v>46223</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54507,7 +54507,7 @@
         <v>46230</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54585,7 +54585,7 @@
         <v>45497</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54658,7 +54658,7 @@
         <v>44838</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54731,7 +54731,7 @@
         <v>46275</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54809,7 +54809,7 @@
         <v>46274</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54882,7 +54882,7 @@
         <v>45156</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -54960,7 +54960,7 @@
         <v>45134</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55038,7 +55038,7 @@
         <v>46275</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55116,7 +55116,7 @@
         <v>46140</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55189,7 +55189,7 @@
         <v>45134</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55267,7 +55267,7 @@
         <v>45596</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55340,7 +55340,7 @@
         <v>46279</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55418,7 +55418,7 @@
         <v>46140</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55491,7 +55491,7 @@
         <v>45240</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55569,7 +55569,7 @@
         <v>45609</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55647,7 +55647,7 @@
         <v>45139</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55720,7 +55720,7 @@
         <v>45544</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55793,7 +55793,7 @@
         <v>46283</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55866,7 +55866,7 @@
         <v>46283</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -55944,7 +55944,7 @@
         <v>45481</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56017,7 +56017,7 @@
         <v>45623</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56095,7 +56095,7 @@
         <v>44725</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56168,7 +56168,7 @@
         <v>45281</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56241,7 +56241,7 @@
         <v>44950</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56314,7 +56314,7 @@
         <v>45068</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56392,7 +56392,7 @@
         <v>46052</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56465,7 +56465,7 @@
         <v>45771</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56543,7 +56543,7 @@
         <v>45068</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56621,7 +56621,7 @@
         <v>45534</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56694,7 +56694,7 @@
         <v>46289</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>45230</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56850,7 +56850,7 @@
         <v>45156</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -56928,7 +56928,7 @@
         <v>46245</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57006,7 +57006,7 @@
         <v>45070</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57079,7 +57079,7 @@
         <v>46099</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57152,7 +57152,7 @@
         <v>45628</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57225,7 +57225,7 @@
         <v>45771</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57303,7 +57303,7 @@
         <v>46293</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57381,7 +57381,7 @@
         <v>45484</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57454,7 +57454,7 @@
         <v>45280</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57527,7 +57527,7 @@
         <v>46293</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>45239</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>46293</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57756,7 +57756,7 @@
         <v>46104</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57834,7 +57834,7 @@
         <v>46293</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -57912,7 +57912,7 @@
         <v>45600</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45744</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45072</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58136,7 +58136,7 @@
         <v>46052</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58209,7 +58209,7 @@
         <v>46065</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58287,7 +58287,7 @@
         <v>46071</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45448</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>46066</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58511,7 +58511,7 @@
         <v>45666</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58584,7 +58584,7 @@
         <v>46038</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58657,7 +58657,7 @@
         <v>45265</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58730,7 +58730,7 @@
         <v>45134</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58808,7 +58808,7 @@
         <v>46101</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58886,7 +58886,7 @@
         <v>46297</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -58959,7 +58959,7 @@
         <v>46254</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59037,7 +59037,7 @@
         <v>46036</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59110,7 +59110,7 @@
         <v>46142</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59188,7 +59188,7 @@
         <v>46121</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59261,7 +59261,7 @@
         <v>46156</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59339,7 +59339,7 @@
         <v>44950</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59412,7 +59412,7 @@
         <v>46092</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59485,7 +59485,7 @@
         <v>46100</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59558,7 +59558,7 @@
         <v>45776</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59631,7 +59631,7 @@
         <v>45986</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59704,7 +59704,7 @@
         <v>46126</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59777,7 +59777,7 @@
         <v>46300</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59850,7 +59850,7 @@
         <v>45455</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -59923,7 +59923,7 @@
         <v>45608</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -59996,7 +59996,7 @@
         <v>45544</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60069,7 +60069,7 @@
         <v>45258</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60142,7 +60142,7 @@
         <v>46079</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60220,7 +60220,7 @@
         <v>45786</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60298,7 +60298,7 @@
         <v>45786</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60376,7 +60376,7 @@
         <v>46224</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60454,7 +60454,7 @@
         <v>46220</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60532,7 +60532,7 @@
         <v>46258</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60610,7 +60610,7 @@
         <v>46260</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60688,7 +60688,7 @@
         <v>45478</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60766,7 +60766,7 @@
         <v>45617</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>44746</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60917,7 +60917,7 @@
         <v>46232</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -60995,7 +60995,7 @@
         <v>46188</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61073,7 +61073,7 @@
         <v>46213</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61146,7 +61146,7 @@
         <v>46223</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61224,7 +61224,7 @@
         <v>46045</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61297,7 +61297,7 @@
         <v>45776</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61375,7 +61375,7 @@
         <v>46121</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61448,7 +61448,7 @@
         <v>45790</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61521,7 +61521,7 @@
         <v>45621</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61594,7 +61594,7 @@
         <v>45468</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61667,7 +61667,7 @@
         <v>45593</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61740,7 +61740,7 @@
         <v>45754</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61813,7 +61813,7 @@
         <v>44659</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61886,7 +61886,7 @@
         <v>45282</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -61959,7 +61959,7 @@
         <v>45434</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62032,7 +62032,7 @@
         <v>45596</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62105,7 +62105,7 @@
         <v>45747</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62183,7 +62183,7 @@
         <v>45803</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62256,7 +62256,7 @@
         <v>45800</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62334,7 +62334,7 @@
         <v>45800</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62412,7 +62412,7 @@
         <v>45800</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62490,7 +62490,7 @@
         <v>45800</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62568,7 +62568,7 @@
         <v>45800</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62646,7 +62646,7 @@
         <v>45800</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62724,7 +62724,7 @@
         <v>45805</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62797,7 +62797,7 @@
         <v>46268</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62875,7 +62875,7 @@
         <v>46269</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62953,7 +62953,7 @@
         <v>45817</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63031,7 +63031,7 @@
         <v>45817</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63104,7 +63104,7 @@
         <v>45817</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63182,7 +63182,7 @@
         <v>46267</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63260,7 +63260,7 @@
         <v>45819</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63338,7 +63338,7 @@
         <v>45819</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63416,7 +63416,7 @@
         <v>46311</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63494,7 +63494,7 @@
         <v>45821</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63572,7 +63572,7 @@
         <v>45824</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63650,7 +63650,7 @@
         <v>46094</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63728,7 +63728,7 @@
         <v>46269</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63806,7 +63806,7 @@
         <v>46224</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>45827</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>45827</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64035,7 +64035,7 @@
         <v>45827</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>46268</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>45827</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64269,7 +64269,7 @@
         <v>45838</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64342,7 +64342,7 @@
         <v>45840</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64415,7 +64415,7 @@
         <v>45840</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64493,7 +64493,7 @@
         <v>45109</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64566,7 +64566,7 @@
         <v>45719</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64639,7 +64639,7 @@
         <v>45073</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64712,7 +64712,7 @@
         <v>45851</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64790,7 +64790,7 @@
         <v>45719</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64868,7 +64868,7 @@
         <v>45551</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64941,7 +64941,7 @@
         <v>45323</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65019,7 +65019,7 @@
         <v>45638</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65097,7 +65097,7 @@
         <v>45315</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65175,7 +65175,7 @@
         <v>45699</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65253,7 +65253,7 @@
         <v>44904</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65331,7 +65331,7 @@
         <v>46058</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65404,7 +65404,7 @@
         <v>46089</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65482,7 +65482,7 @@
         <v>46148</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65555,7 +65555,7 @@
         <v>46148</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65628,7 +65628,7 @@
         <v>46048</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65701,7 +65701,7 @@
         <v>46293</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65779,7 +65779,7 @@
         <v>46300</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65852,7 +65852,7 @@
         <v>46255</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65930,7 +65930,7 @@
         <v>46307</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>45545</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>45106</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46044</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>45841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46101</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46132</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46170</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45469</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>46185</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>46125</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>46153</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>46126</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>46114</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>46132</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>46125</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44953</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>45247</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44496</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>46009</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45519</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>46282</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>46282</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>46038</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>46053</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>46056</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>46077</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>46097</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>46100</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>46101</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>46302</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>46125</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>46091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>46076</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45280</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>46139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45448</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45469</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>46104</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>46085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46077</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45022</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44529</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44532</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44795</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44858</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44802</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44705</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>44643</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44663</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45888</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45132</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45203</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45184</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45889</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45889</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45744</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>45139</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45884</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>45891</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>44950</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45334</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45894</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45896</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>45527</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45700</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45903</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45903</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45330</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45835</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45258</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45905</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>46160</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>46161</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45777</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45911</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45911</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45911</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45261</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45716</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>46163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>46164</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>46164</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>46168</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44839</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45747</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46168</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44893</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45925</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45107</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46168</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45156</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>46169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44950</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46169</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>46169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45846</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>45107</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45930</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>44845</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45590</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45617</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>46085</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>46023</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>44501</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>46170</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>46170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45554</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45967</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>46170</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>44525</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>44820</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45602</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>45602</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45602</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>44816</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45608</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45554</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45644</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45216</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>44522</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>46170</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>46170</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45932</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>45134</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45134</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46171</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>46170</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>46175</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45434</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>45937</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44887</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45937</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45937</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45937</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46174</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>46174</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45834</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>46174</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45603</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>46177</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45488</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>46177</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45443</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45608</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45608</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45139</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45334</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45488</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>46181</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45952</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45223</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45954</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45068</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45953</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45954</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45953</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45678</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45628</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46185</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>46185</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45211</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45957</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46185</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>46185</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45771</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45771</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45581</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45959</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45068</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>46185</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>46189</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45455</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>46189</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>46189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45551</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>46076</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45615</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>46189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46189</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45981</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>46188</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>46055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>46190</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>46190</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>46190</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>46191</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45237</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45967</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45967</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45972</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46195</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45972</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45972</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45973</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45973</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45973</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45169</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>46196</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45973</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45973</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45973</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>46196</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>46196</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45973</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46198</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46183</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>46199</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>46198</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45978</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45978</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45048</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>46199</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45978</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45978</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45975</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>46198</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45366</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45156</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>46203</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>46203</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>46203</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45481</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45674</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46205</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>46205</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>46204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45252</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>46205</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44986</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45490</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45986</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>46104</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45544</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45985</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45985</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45478</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45988</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>46206</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45994</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>45996</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45995</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>46216</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45995</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>46218</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>46000</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45776</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45982</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>46098</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46071</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46006</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45989</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>46230</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45608</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>46009</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45617</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46279</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>46009</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>46140</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45258</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>46013</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>46014</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46010</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>46013</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45544</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45786</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>46140</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45455</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45786</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>46009</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45478</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44746</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>46021</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>46024</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>46027</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>46027</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>46027</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46027</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>46027</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46027</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>46029</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45790</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45593</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46028</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46029</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46028</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>46029</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>46029</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46024</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>46031</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>46034</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>46283</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>46033</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45776</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>46034</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>46031</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>46036</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30097,7 +30097,7 @@
         <v>46036</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>46035</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>46036</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46035</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>46036</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>46036</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45282</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>46035</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>46036</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>46283</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>46038</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>46038</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46037</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>46041</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45434</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45621</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>46052</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>46041</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44659</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>46044</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45468</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>46245</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45754</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>46044</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45747</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>46043</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>46043</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45596</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>46036</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>46048</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>46099</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>46048</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>46036</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45800</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45800</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>46044</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>46045</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>45800</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>46045</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45800</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45800</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45800</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46049</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46050</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>46049</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>46050</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46051</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>46052</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>46052</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>46052</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45134</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>45803</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46051</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45342</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46056</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>46056</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>46053</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>46056</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>46056</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>46056</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45805</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>46056</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>46055</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46056</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>46056</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>46289</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>46057</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46062</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>46059</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>46293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>46062</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>46062</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>46065</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>46066</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>46062</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>46293</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>46064</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>46064</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>46293</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>46104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>46064</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>46071</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>46065</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>46065</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>46052</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>46293</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45817</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45817</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>46056</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>46071</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45819</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>46071</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45819</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>46071</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>46071</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>46071</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46072</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>46072</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>46072</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>46072</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>46071</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46071</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46031</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46071</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>46076</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>46077</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>46077</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>46077</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>46073</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>45824</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46077</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45821</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46077</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>46031</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>46077</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>46078</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>46079</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>46079</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45827</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>46080</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>45827</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>46080</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>46083</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45827</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45827</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46083</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>46083</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>46080</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>46142</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45986</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>46121</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>46085</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>46297</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>45534</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>46087</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>46156</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>46300</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>46254</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>46089</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>46092</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45838</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>46091</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>46079</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>46093</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>46093</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46092</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45840</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>45840</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45239</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>46093</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>46094</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>46097</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>46038</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46094</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46094</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>46098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>46098</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>46100</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>46099</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>46101</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>46098</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>46098</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>46098</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>44496</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45109</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>46098</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>46099</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>46100</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>46100</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>46036</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>46101</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>46104</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45719</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45073</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>46105</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>46104</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>46188</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>46126</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>46104</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46104</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>46104</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>46104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>46106</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>46106</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>46121</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>46106</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>45851</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>46106</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>46106</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>46111</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>46213</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>46108</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>46108</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>46111</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>46112</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>46112</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46112</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>46114</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>45488</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>46114</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46114</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46114</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>46119</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>46119</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>46118</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>46076</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>46076</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
         <v>46077</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>46076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>46121</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>46121</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>46049</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>46045</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>46076</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45184</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>46125</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>46106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>46126</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>46105</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>46126</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>46127</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>46127</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>46127</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>46098</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>46132</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>46132</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>46132</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>46132</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>46128</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>46112</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>46112</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45719</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47616,7 +47616,7 @@
         <v>46132</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>46132</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>46128</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>46132</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46132</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>45586</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>46134</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45551</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>44879</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45618</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>46134</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44889</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>46134</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>46133</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>46133</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>46133</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>46133</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>46136</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>45656</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49038,7 +49038,7 @@
         <v>45280</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>46136</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>46119</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
         <v>46114</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45712</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>46140</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>46071</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45840</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>46267</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>45554</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>46048</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>46042</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>46269</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>46064</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50095,7 +50095,7 @@
         <v>46094</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>46140</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>46223</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>46223</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>46137</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>46137</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>46269</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>46224</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50709,7 +50709,7 @@
         <v>46268</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>46268</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45111</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>46139</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51016,7 +51016,7 @@
         <v>46036</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>45821</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45946</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>46311</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>46043</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>46043</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45488</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>46063</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>44950</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>46042</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>46049</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>46063</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>46106</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>46138</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>46052</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>46048</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>45526</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>46098</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>46055</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52448,7 +52448,7 @@
         <v>46107</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>45803</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>46050</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>46021</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>46140</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>46056</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>46052</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52979,7 +52979,7 @@
         <v>45870</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
         <v>45800</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>46052</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         <v>45800</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53281,7 +53281,7 @@
         <v>46140</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>46140</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>46137</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>45497</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>46315</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45925</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>46034</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>46064</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53890,7 +53890,7 @@
         <v>44663</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53968,7 +53968,7 @@
         <v>46065</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54046,7 +54046,7 @@
         <v>46316</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>46052</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>44915</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>46029</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>46043</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>46220</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>46258</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>46275</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46034</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>46035</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>46091</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>46232</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46106</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>46077</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>45111</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>46260</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>46063</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>46029</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45994</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>46064</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>46275</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>46037</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>46141</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>46317</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>46125</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>46056</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>46027</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45210</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>46071</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>46073</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56311,7 +56311,7 @@
         <v>46223</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>46146</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>46104</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>46122</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>46224</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>46127</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>46125</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>44950</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46148</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>46148</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>46134</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>46147</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57242,7 +57242,7 @@
         <v>46119</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57320,7 +57320,7 @@
         <v>46147</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>46148</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57476,7 +57476,7 @@
         <v>46148</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57554,7 +57554,7 @@
         <v>45398</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>46149</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45448</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>46153</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>46128</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57929,7 +57929,7 @@
         <v>46093</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>46093</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>46119</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>46093</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>46088</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58304,7 +58304,7 @@
         <v>46071</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45909</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58455,7 +58455,7 @@
         <v>45986</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58533,7 +58533,7 @@
         <v>46153</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58606,7 +58606,7 @@
         <v>46043</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58679,7 +58679,7 @@
         <v>46104</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>46154</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58830,7 +58830,7 @@
         <v>46066</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>46049</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>46056</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45994</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
         <v>46155</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>46156</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>45281</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>45994</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>46044</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45926</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>46155</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>46155</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45291</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59784,7 +59784,7 @@
         <v>46100</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59857,7 +59857,7 @@
         <v>45106</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59935,7 +59935,7 @@
         <v>45609</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>45611</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45674</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>45666</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>45510</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>45511</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45070</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60456,7 +60456,7 @@
         <v>45646</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45645</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45727</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45699</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45484</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45534</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60909,7 +60909,7 @@
         <v>45698</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60982,7 +60982,7 @@
         <v>45111</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45022</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>44890</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61201,7 +61201,7 @@
         <v>44883</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>44712</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>45134</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61430,7 +61430,7 @@
         <v>45534</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>45754</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61576,7 +61576,7 @@
         <v>45758</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61649,7 +61649,7 @@
         <v>45156</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61727,7 +61727,7 @@
         <v>45593</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61800,7 +61800,7 @@
         <v>45041</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61878,7 +61878,7 @@
         <v>45611</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61956,7 +61956,7 @@
         <v>44970</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62029,7 +62029,7 @@
         <v>45649</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>45072</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>45620</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45596</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>45341</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62394,7 +62394,7 @@
         <v>45600</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62467,7 +62467,7 @@
         <v>45617</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62545,7 +62545,7 @@
         <v>45181</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>45624</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62696,7 +62696,7 @@
         <v>45180</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62769,7 +62769,7 @@
         <v>45645</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62847,7 +62847,7 @@
         <v>45152</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62920,7 +62920,7 @@
         <v>45432</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62993,7 +62993,7 @@
         <v>45441</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63066,7 +63066,7 @@
         <v>45671</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63144,7 +63144,7 @@
         <v>45757</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63222,7 +63222,7 @@
         <v>45705</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63295,7 +63295,7 @@
         <v>44643</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45156</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63446,7 +63446,7 @@
         <v>45243</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>45254</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>44804</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>44725</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>44781</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63811,7 +63811,7 @@
         <v>45204</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>45134</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>44700</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
         <v>45265</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>45744</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>44797</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45772</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64337,7 +64337,7 @@
         <v>45237</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>45254</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64483,7 +64483,7 @@
         <v>45230</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64561,7 +64561,7 @@
         <v>45240</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64639,7 +64639,7 @@
         <v>45301</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64712,7 +64712,7 @@
         <v>45167</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64785,7 +64785,7 @@
         <v>45623</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45139</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64936,7 +64936,7 @@
         <v>45548</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65014,7 +65014,7 @@
         <v>45323</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>45638</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65170,7 +65170,7 @@
         <v>45315</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65248,7 +65248,7 @@
         <v>45699</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65326,7 +65326,7 @@
         <v>44904</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65404,7 +65404,7 @@
         <v>46058</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65477,7 +65477,7 @@
         <v>46089</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65555,7 +65555,7 @@
         <v>46148</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65628,7 +65628,7 @@
         <v>46148</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65701,7 +65701,7 @@
         <v>46048</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65774,7 +65774,7 @@
         <v>46293</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65852,7 +65852,7 @@
         <v>46300</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>46255</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>46307</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>

--- a/Översikt OCKELBO.xlsx
+++ b/Översikt OCKELBO.xlsx
@@ -601,7 +601,7 @@
         <v>44614</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>46077</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>46073</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>45545</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1089,7 +1089,7 @@
         <v>45106</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
         <v>46044</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         <v>46132</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>46099</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>45054</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>45387</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1796,7 +1796,7 @@
         <v>46077</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>45841</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>46101</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2143,7 +2143,7 @@
         <v>46220</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>46132</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
         <v>44995</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>46170</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2602,7 +2602,7 @@
         <v>46099</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>45469</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>46185</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>46125</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3046,7 +3046,7 @@
         <v>46153</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>46126</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3265,7 +3265,7 @@
         <v>45812</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>46094</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>46036</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>46044</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3704,7 +3704,7 @@
         <v>46114</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3815,7 +3815,7 @@
         <v>46132</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3926,7 +3926,7 @@
         <v>46125</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>46125</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
         <v>46139</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4259,7 +4259,7 @@
         <v>44587</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44953</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
         <v>45247</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4701,7 +4701,7 @@
         <v>45582</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4811,7 +4811,7 @@
         <v>44496</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>45972</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
         <v>46009</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45519</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>46282</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5355,7 +5355,7 @@
         <v>46282</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5469,7 +5469,7 @@
         <v>46283</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>46038</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>46053</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>46056</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>46077</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>46097</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6112,7 +6112,7 @@
         <v>46100</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6217,7 +6217,7 @@
         <v>46101</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6331,7 +6331,7 @@
         <v>46302</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6440,7 +6440,7 @@
         <v>46125</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>46091</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         <v>46076</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         <v>45280</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6882,7 +6882,7 @@
         <v>46070</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6992,7 +6992,7 @@
         <v>46139</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7102,7 +7102,7 @@
         <v>45448</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7212,7 +7212,7 @@
         <v>45469</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>46104</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>46085</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>46077</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45022</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>45754</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         <v>45051</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7989,7 +7989,7 @@
         <v>45982</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8099,7 +8099,7 @@
         <v>46019</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44795</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>44858</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>44795</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>44529</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>44532</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44817</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>44795</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44509</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>44858</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44795</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44858</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>44802</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
         <v>44881</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9173,7 +9173,7 @@
         <v>44705</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         <v>44872</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44532</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>44643</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>44663</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45799</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>45888</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>45132</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9787,7 +9787,7 @@
         <v>45203</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>45184</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>45889</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10011,7 +10011,7 @@
         <v>45889</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>45889</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45744</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10235,7 +10235,7 @@
         <v>45139</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>45884</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10381,7 +10381,7 @@
         <v>45891</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10459,7 +10459,7 @@
         <v>44950</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>45334</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10605,7 +10605,7 @@
         <v>45894</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>45896</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10751,7 +10751,7 @@
         <v>45600</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>45609</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10902,7 +10902,7 @@
         <v>45527</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>45700</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11053,7 +11053,7 @@
         <v>45903</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         <v>45903</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11204,7 +11204,7 @@
         <v>45903</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11277,7 +11277,7 @@
         <v>45330</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11355,7 +11355,7 @@
         <v>45835</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11428,7 +11428,7 @@
         <v>45258</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45905</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>46160</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>46122</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>46161</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11793,7 +11793,7 @@
         <v>46161</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         <v>45777</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -11944,7 +11944,7 @@
         <v>45911</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45911</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>45911</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12168,7 +12168,7 @@
         <v>45261</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>45716</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45911</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>46163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>46164</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>46164</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44838</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>46168</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44839</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45747</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>46168</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>46044</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44893</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13147,7 +13147,7 @@
         <v>45925</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45107</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>46168</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13381,7 +13381,7 @@
         <v>45156</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>46169</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13532,7 +13532,7 @@
         <v>44950</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46169</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13683,7 +13683,7 @@
         <v>46169</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13761,7 +13761,7 @@
         <v>46169</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13839,7 +13839,7 @@
         <v>46169</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13912,7 +13912,7 @@
         <v>45846</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>45107</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45930</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>44845</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45590</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14297,7 +14297,7 @@
         <v>45617</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>46085</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>46023</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>44501</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>46170</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14677,7 +14677,7 @@
         <v>46170</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14755,7 +14755,7 @@
         <v>45554</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14833,7 +14833,7 @@
         <v>45967</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14906,7 +14906,7 @@
         <v>46170</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -14984,7 +14984,7 @@
         <v>45162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15062,7 +15062,7 @@
         <v>46170</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15135,7 +15135,7 @@
         <v>44525</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15213,7 +15213,7 @@
         <v>45582</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15291,7 +15291,7 @@
         <v>44820</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15369,7 +15369,7 @@
         <v>45929</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45929</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45602</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>45602</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45602</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15749,7 +15749,7 @@
         <v>44816</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>45027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>45608</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>45554</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16061,7 +16061,7 @@
         <v>45644</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16139,7 +16139,7 @@
         <v>45216</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16217,7 +16217,7 @@
         <v>44522</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16295,7 +16295,7 @@
         <v>46170</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>46170</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16451,7 +16451,7 @@
         <v>45932</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>45134</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>45134</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>46171</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16758,7 +16758,7 @@
         <v>46170</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>46175</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16914,7 +16914,7 @@
         <v>46175</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16992,7 +16992,7 @@
         <v>45434</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17065,7 +17065,7 @@
         <v>45937</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>44887</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45937</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>45937</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>45937</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17435,7 +17435,7 @@
         <v>45937</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17508,7 +17508,7 @@
         <v>45937</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>46174</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17654,7 +17654,7 @@
         <v>46174</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17727,7 +17727,7 @@
         <v>45834</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17800,7 +17800,7 @@
         <v>46174</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17873,7 +17873,7 @@
         <v>45603</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>46177</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18024,7 +18024,7 @@
         <v>45488</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18097,7 +18097,7 @@
         <v>46177</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18175,7 +18175,7 @@
         <v>45450</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18248,7 +18248,7 @@
         <v>45443</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18321,7 +18321,7 @@
         <v>45608</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18399,7 +18399,7 @@
         <v>45608</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18477,7 +18477,7 @@
         <v>45139</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45334</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>45488</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>46181</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45952</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45223</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45954</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>45068</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>45953</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45954</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45953</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19305,7 +19305,7 @@
         <v>45678</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45628</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>46185</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>46185</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45211</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>45957</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>46185</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19826,7 +19826,7 @@
         <v>46185</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19899,7 +19899,7 @@
         <v>45771</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19977,7 +19977,7 @@
         <v>45771</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>45581</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>45959</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45068</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>46185</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20362,7 +20362,7 @@
         <v>46189</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20440,7 +20440,7 @@
         <v>45455</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>46189</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>46189</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>45551</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20732,7 +20732,7 @@
         <v>46076</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20810,7 +20810,7 @@
         <v>45615</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20883,7 +20883,7 @@
         <v>46189</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20956,7 +20956,7 @@
         <v>46189</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45981</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21112,7 +21112,7 @@
         <v>46188</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21190,7 +21190,7 @@
         <v>45966</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21263,7 +21263,7 @@
         <v>46055</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>46190</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>46190</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         <v>46190</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>46191</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21638,7 +21638,7 @@
         <v>45237</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>45967</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21784,7 +21784,7 @@
         <v>45967</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21857,7 +21857,7 @@
         <v>45972</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -21930,7 +21930,7 @@
         <v>46195</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45972</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>45972</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45973</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45973</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>45973</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45169</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>46196</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45973</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -22597,7 +22597,7 @@
         <v>45973</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -22670,7 +22670,7 @@
         <v>45973</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>46196</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>46196</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -22904,7 +22904,7 @@
         <v>45973</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -22977,7 +22977,7 @@
         <v>46198</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23050,7 +23050,7 @@
         <v>46183</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>46199</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23206,7 +23206,7 @@
         <v>45978</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -23279,7 +23279,7 @@
         <v>46198</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>45978</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -23430,7 +23430,7 @@
         <v>45978</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -23503,7 +23503,7 @@
         <v>45978</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45048</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -23649,7 +23649,7 @@
         <v>46199</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -23727,7 +23727,7 @@
         <v>45978</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -23800,7 +23800,7 @@
         <v>45978</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45978</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45975</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24019,7 +24019,7 @@
         <v>46198</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24092,7 +24092,7 @@
         <v>45366</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24170,7 +24170,7 @@
         <v>45156</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -24248,7 +24248,7 @@
         <v>46203</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>46203</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -24404,7 +24404,7 @@
         <v>46203</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -24477,7 +24477,7 @@
         <v>45481</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -24550,7 +24550,7 @@
         <v>45674</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -24623,7 +24623,7 @@
         <v>46205</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -24696,7 +24696,7 @@
         <v>46205</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -24769,7 +24769,7 @@
         <v>46204</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -24847,7 +24847,7 @@
         <v>45252</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -24920,7 +24920,7 @@
         <v>46205</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -24993,7 +24993,7 @@
         <v>44986</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25066,7 +25066,7 @@
         <v>45490</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>45986</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25222,7 +25222,7 @@
         <v>46104</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -25295,7 +25295,7 @@
         <v>45544</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -25368,7 +25368,7 @@
         <v>45985</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>45985</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -25514,7 +25514,7 @@
         <v>45478</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -25592,7 +25592,7 @@
         <v>45988</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -25670,7 +25670,7 @@
         <v>46206</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>45994</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -25821,7 +25821,7 @@
         <v>45996</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -25899,7 +25899,7 @@
         <v>45995</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -25977,7 +25977,7 @@
         <v>46216</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45995</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>46218</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26211,7 +26211,7 @@
         <v>46000</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -26289,7 +26289,7 @@
         <v>45776</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45982</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -26440,7 +26440,7 @@
         <v>46098</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -26518,7 +26518,7 @@
         <v>46071</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         <v>46006</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -26669,7 +26669,7 @@
         <v>45989</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -26747,7 +26747,7 @@
         <v>46230</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>45608</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -26898,7 +26898,7 @@
         <v>46009</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         <v>45617</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27054,7 +27054,7 @@
         <v>46279</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>46009</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>46140</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45258</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>46013</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -27429,7 +27429,7 @@
         <v>46014</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -27502,7 +27502,7 @@
         <v>46010</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -27575,7 +27575,7 @@
         <v>46013</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45544</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -27726,7 +27726,7 @@
         <v>45786</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -27804,7 +27804,7 @@
         <v>46140</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         <v>45455</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -27950,7 +27950,7 @@
         <v>45786</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>46009</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28106,7 +28106,7 @@
         <v>45478</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>44746</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28257,7 +28257,7 @@
         <v>46021</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -28330,7 +28330,7 @@
         <v>46024</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -28403,7 +28403,7 @@
         <v>46027</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>46027</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -28549,7 +28549,7 @@
         <v>46027</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -28622,7 +28622,7 @@
         <v>46027</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -28695,7 +28695,7 @@
         <v>46027</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -28768,7 +28768,7 @@
         <v>46027</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -28841,7 +28841,7 @@
         <v>46029</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -28914,7 +28914,7 @@
         <v>45790</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45593</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29060,7 +29060,7 @@
         <v>46028</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>46029</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         <v>46028</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29279,7 +29279,7 @@
         <v>46029</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         <v>46029</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -29425,7 +29425,7 @@
         <v>46024</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -29498,7 +29498,7 @@
         <v>46031</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>46034</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -29644,7 +29644,7 @@
         <v>46283</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -29722,7 +29722,7 @@
         <v>46033</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -29795,7 +29795,7 @@
         <v>45776</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -29873,7 +29873,7 @@
         <v>46034</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -29951,7 +29951,7 @@
         <v>46031</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30024,7 +30024,7 @@
         <v>46036</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30097,7 +30097,7 @@
         <v>46036</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>46035</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>46036</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -30316,7 +30316,7 @@
         <v>46035</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>46036</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -30462,7 +30462,7 @@
         <v>46036</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -30535,7 +30535,7 @@
         <v>45282</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -30608,7 +30608,7 @@
         <v>46035</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -30681,7 +30681,7 @@
         <v>46036</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -30754,7 +30754,7 @@
         <v>46283</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -30827,7 +30827,7 @@
         <v>46038</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -30900,7 +30900,7 @@
         <v>46038</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -30973,7 +30973,7 @@
         <v>46037</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>46041</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31119,7 +31119,7 @@
         <v>45434</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45621</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>46052</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -31338,7 +31338,7 @@
         <v>46041</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -31411,7 +31411,7 @@
         <v>44659</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -31484,7 +31484,7 @@
         <v>46044</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45468</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -31630,7 +31630,7 @@
         <v>46245</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -31708,7 +31708,7 @@
         <v>45754</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>46044</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>45747</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>46043</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32005,7 +32005,7 @@
         <v>46043</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45596</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32151,7 +32151,7 @@
         <v>46036</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
         <v>46048</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>46099</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>46048</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>46036</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>45800</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45800</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -32672,7 +32672,7 @@
         <v>46044</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>46045</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -32818,7 +32818,7 @@
         <v>45800</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>46045</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45800</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45800</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>45800</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46049</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33281,7 +33281,7 @@
         <v>46050</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>46049</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -33432,7 +33432,7 @@
         <v>46050</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -33510,7 +33510,7 @@
         <v>46051</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -33588,7 +33588,7 @@
         <v>46052</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>46052</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>46052</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -33807,7 +33807,7 @@
         <v>45134</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -33885,7 +33885,7 @@
         <v>45803</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -33958,7 +33958,7 @@
         <v>46051</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45342</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>46056</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>46056</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34250,7 +34250,7 @@
         <v>46053</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34323,7 +34323,7 @@
         <v>46056</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -34396,7 +34396,7 @@
         <v>46056</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -34469,7 +34469,7 @@
         <v>46056</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -34542,7 +34542,7 @@
         <v>45805</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -34615,7 +34615,7 @@
         <v>46056</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -34688,7 +34688,7 @@
         <v>46055</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -34766,7 +34766,7 @@
         <v>46056</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>46056</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>46289</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -34995,7 +34995,7 @@
         <v>46057</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35073,7 +35073,7 @@
         <v>46062</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35146,7 +35146,7 @@
         <v>46059</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35219,7 +35219,7 @@
         <v>46293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35297,7 +35297,7 @@
         <v>46062</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -35370,7 +35370,7 @@
         <v>46062</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -35448,7 +35448,7 @@
         <v>46065</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -35526,7 +35526,7 @@
         <v>46066</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>46062</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>46293</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>46064</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -35823,7 +35823,7 @@
         <v>46064</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -35896,7 +35896,7 @@
         <v>46293</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -35974,7 +35974,7 @@
         <v>46104</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36052,7 +36052,7 @@
         <v>46064</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>46071</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36203,7 +36203,7 @@
         <v>46065</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36281,7 +36281,7 @@
         <v>45817</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>46065</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -36432,7 +36432,7 @@
         <v>46052</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -36505,7 +36505,7 @@
         <v>46293</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -36583,7 +36583,7 @@
         <v>45817</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -36661,7 +36661,7 @@
         <v>45817</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>46056</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>46071</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45819</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>46071</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>45819</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>46071</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>46071</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>46071</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46072</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>46072</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -37489,7 +37489,7 @@
         <v>46072</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>46072</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>46071</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>46071</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -37791,7 +37791,7 @@
         <v>46031</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -37864,7 +37864,7 @@
         <v>46071</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>46076</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38020,7 +38020,7 @@
         <v>46077</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38093,7 +38093,7 @@
         <v>46077</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38171,7 +38171,7 @@
         <v>46077</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>46073</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38322,7 +38322,7 @@
         <v>45824</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>46077</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -38478,7 +38478,7 @@
         <v>45821</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>46077</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>46031</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>46077</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -38785,7 +38785,7 @@
         <v>46078</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>46079</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>46079</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39009,7 +39009,7 @@
         <v>45827</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>46080</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39155,7 +39155,7 @@
         <v>45827</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39233,7 +39233,7 @@
         <v>46080</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39306,7 +39306,7 @@
         <v>46083</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45827</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39462,7 +39462,7 @@
         <v>45827</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -39540,7 +39540,7 @@
         <v>46083</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -39613,7 +39613,7 @@
         <v>46083</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>46080</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -39764,7 +39764,7 @@
         <v>46142</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -39842,7 +39842,7 @@
         <v>45986</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -39915,7 +39915,7 @@
         <v>46121</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -39988,7 +39988,7 @@
         <v>46085</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40061,7 +40061,7 @@
         <v>46297</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40134,7 +40134,7 @@
         <v>45534</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>46087</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40280,7 +40280,7 @@
         <v>46156</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40358,7 +40358,7 @@
         <v>46300</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40431,7 +40431,7 @@
         <v>46254</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -40509,7 +40509,7 @@
         <v>46089</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>46092</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -40660,7 +40660,7 @@
         <v>45838</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -40733,7 +40733,7 @@
         <v>46091</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -40806,7 +40806,7 @@
         <v>46079</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -40884,7 +40884,7 @@
         <v>46093</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -40957,7 +40957,7 @@
         <v>46093</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>46092</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41108,7 +41108,7 @@
         <v>45840</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41186,7 +41186,7 @@
         <v>45840</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41259,7 +41259,7 @@
         <v>45239</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41332,7 +41332,7 @@
         <v>46093</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41405,7 +41405,7 @@
         <v>46094</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>46097</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>46038</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -41629,7 +41629,7 @@
         <v>46094</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -41702,7 +41702,7 @@
         <v>46094</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
         <v>46098</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -41853,7 +41853,7 @@
         <v>46098</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -41926,7 +41926,7 @@
         <v>46100</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -41999,7 +41999,7 @@
         <v>46099</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42077,7 +42077,7 @@
         <v>46101</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42155,7 +42155,7 @@
         <v>46098</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42228,7 +42228,7 @@
         <v>46098</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42306,7 +42306,7 @@
         <v>46098</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>44496</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42462,7 +42462,7 @@
         <v>45109</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>46098</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -42613,7 +42613,7 @@
         <v>46099</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -42691,7 +42691,7 @@
         <v>46100</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -42764,7 +42764,7 @@
         <v>46100</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -42837,7 +42837,7 @@
         <v>46036</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -42910,7 +42910,7 @@
         <v>46101</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>46104</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43066,7 +43066,7 @@
         <v>45719</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43139,7 +43139,7 @@
         <v>45073</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43212,7 +43212,7 @@
         <v>46105</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43290,7 +43290,7 @@
         <v>46104</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43368,7 +43368,7 @@
         <v>46188</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43446,7 +43446,7 @@
         <v>46126</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>46104</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -43592,7 +43592,7 @@
         <v>46104</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>46104</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -43748,7 +43748,7 @@
         <v>46104</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -43821,7 +43821,7 @@
         <v>46106</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -43899,7 +43899,7 @@
         <v>46106</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -43972,7 +43972,7 @@
         <v>46121</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>46106</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44123,7 +44123,7 @@
         <v>45851</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44201,7 +44201,7 @@
         <v>46106</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44279,7 +44279,7 @@
         <v>46106</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>46111</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44425,7 +44425,7 @@
         <v>46213</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44498,7 +44498,7 @@
         <v>46108</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44576,7 +44576,7 @@
         <v>46108</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>46111</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -44727,7 +44727,7 @@
         <v>46112</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -44805,7 +44805,7 @@
         <v>46112</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -44883,7 +44883,7 @@
         <v>46112</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>46114</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45039,7 +45039,7 @@
         <v>45488</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>46114</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46114</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45258,7 +45258,7 @@
         <v>46114</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45336,7 +45336,7 @@
         <v>46119</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45409,7 +45409,7 @@
         <v>46119</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45487,7 +45487,7 @@
         <v>46118</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45560,7 +45560,7 @@
         <v>46076</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -45638,7 +45638,7 @@
         <v>46076</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
         <v>46077</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -45794,7 +45794,7 @@
         <v>46076</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -45872,7 +45872,7 @@
         <v>46121</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>46121</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>46049</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46091,7 +46091,7 @@
         <v>46045</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46164,7 +46164,7 @@
         <v>46076</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46242,7 +46242,7 @@
         <v>45184</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46320,7 +46320,7 @@
         <v>46125</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>46106</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46476,7 +46476,7 @@
         <v>46126</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46554,7 +46554,7 @@
         <v>46105</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46632,7 +46632,7 @@
         <v>46126</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -46705,7 +46705,7 @@
         <v>46127</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>46127</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>46127</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>46098</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>46132</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>46132</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47158,7 +47158,7 @@
         <v>46132</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47231,7 +47231,7 @@
         <v>46132</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47309,7 +47309,7 @@
         <v>46128</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47382,7 +47382,7 @@
         <v>46112</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>46112</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>45719</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47616,7 +47616,7 @@
         <v>46132</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -47694,7 +47694,7 @@
         <v>46132</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -47767,7 +47767,7 @@
         <v>46128</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>46132</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>46132</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48001,7 +48001,7 @@
         <v>45586</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48074,7 +48074,7 @@
         <v>46134</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48147,7 +48147,7 @@
         <v>45551</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>44879</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48293,7 +48293,7 @@
         <v>45618</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48366,7 +48366,7 @@
         <v>46134</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48439,7 +48439,7 @@
         <v>44889</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48512,7 +48512,7 @@
         <v>46134</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>46133</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -48663,7 +48663,7 @@
         <v>46133</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -48741,7 +48741,7 @@
         <v>46133</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>46133</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -48892,7 +48892,7 @@
         <v>46136</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -48965,7 +48965,7 @@
         <v>45656</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49038,7 +49038,7 @@
         <v>45280</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49111,7 +49111,7 @@
         <v>46136</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49184,7 +49184,7 @@
         <v>46119</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49257,7 +49257,7 @@
         <v>46114</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49335,7 +49335,7 @@
         <v>45712</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>46140</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49486,7 +49486,7 @@
         <v>46071</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49559,7 +49559,7 @@
         <v>45840</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49637,7 +49637,7 @@
         <v>46267</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -49715,7 +49715,7 @@
         <v>45554</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>46048</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>46042</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -49944,7 +49944,7 @@
         <v>46269</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50022,7 +50022,7 @@
         <v>46064</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50095,7 +50095,7 @@
         <v>46094</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>46140</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50251,7 +50251,7 @@
         <v>46223</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50324,7 +50324,7 @@
         <v>46223</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50397,7 +50397,7 @@
         <v>46137</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>46137</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50553,7 +50553,7 @@
         <v>46269</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50631,7 +50631,7 @@
         <v>46224</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -50709,7 +50709,7 @@
         <v>46268</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -50787,7 +50787,7 @@
         <v>46268</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -50865,7 +50865,7 @@
         <v>45111</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -50938,7 +50938,7 @@
         <v>46139</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51016,7 +51016,7 @@
         <v>46036</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51089,7 +51089,7 @@
         <v>45821</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51162,7 +51162,7 @@
         <v>45946</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51240,7 +51240,7 @@
         <v>46311</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51318,7 +51318,7 @@
         <v>46043</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51391,7 +51391,7 @@
         <v>46043</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51464,7 +51464,7 @@
         <v>45488</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51537,7 +51537,7 @@
         <v>46063</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51610,7 +51610,7 @@
         <v>44950</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51683,7 +51683,7 @@
         <v>46042</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -51761,7 +51761,7 @@
         <v>46049</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -51839,7 +51839,7 @@
         <v>46063</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -51912,7 +51912,7 @@
         <v>46106</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>46138</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52068,7 +52068,7 @@
         <v>46052</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52146,7 +52146,7 @@
         <v>46048</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52219,7 +52219,7 @@
         <v>45526</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52297,7 +52297,7 @@
         <v>46098</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52370,7 +52370,7 @@
         <v>46055</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52448,7 +52448,7 @@
         <v>46107</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52526,7 +52526,7 @@
         <v>45803</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52604,7 +52604,7 @@
         <v>46050</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52682,7 +52682,7 @@
         <v>46021</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -52755,7 +52755,7 @@
         <v>46140</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -52833,7 +52833,7 @@
         <v>46056</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -52906,7 +52906,7 @@
         <v>46052</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -52979,7 +52979,7 @@
         <v>45870</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53052,7 +53052,7 @@
         <v>45800</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53130,7 +53130,7 @@
         <v>46052</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53208,7 +53208,7 @@
         <v>45800</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53281,7 +53281,7 @@
         <v>46140</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53354,7 +53354,7 @@
         <v>46140</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53432,7 +53432,7 @@
         <v>46137</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53510,7 +53510,7 @@
         <v>45497</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53583,7 +53583,7 @@
         <v>46315</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53656,7 +53656,7 @@
         <v>45925</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -53734,7 +53734,7 @@
         <v>46034</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -53812,7 +53812,7 @@
         <v>46064</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -53890,7 +53890,7 @@
         <v>44663</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -53968,7 +53968,7 @@
         <v>46065</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54046,7 +54046,7 @@
         <v>46316</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54119,7 +54119,7 @@
         <v>46052</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54192,7 +54192,7 @@
         <v>44915</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54265,7 +54265,7 @@
         <v>46029</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54338,7 +54338,7 @@
         <v>46043</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54411,7 +54411,7 @@
         <v>46220</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54489,7 +54489,7 @@
         <v>46258</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54567,7 +54567,7 @@
         <v>46275</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>46034</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54718,7 +54718,7 @@
         <v>46035</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -54791,7 +54791,7 @@
         <v>46091</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -54864,7 +54864,7 @@
         <v>46232</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -54942,7 +54942,7 @@
         <v>46106</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55020,7 +55020,7 @@
         <v>46077</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55098,7 +55098,7 @@
         <v>45111</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55171,7 +55171,7 @@
         <v>46260</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55249,7 +55249,7 @@
         <v>46063</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55327,7 +55327,7 @@
         <v>46029</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45994</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>46064</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>46275</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>46037</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>46141</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55775,7 +55775,7 @@
         <v>46317</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -55848,7 +55848,7 @@
         <v>46125</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -55926,7 +55926,7 @@
         <v>46056</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56004,7 +56004,7 @@
         <v>46027</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56082,7 +56082,7 @@
         <v>45210</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>46071</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56233,7 +56233,7 @@
         <v>46073</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56311,7 +56311,7 @@
         <v>46223</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>46146</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>46104</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>46122</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56623,7 +56623,7 @@
         <v>46224</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56701,7 +56701,7 @@
         <v>46127</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>46125</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -56857,7 +56857,7 @@
         <v>44950</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>46148</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>46148</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>46134</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>46147</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57242,7 +57242,7 @@
         <v>46119</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57320,7 +57320,7 @@
         <v>46147</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57398,7 +57398,7 @@
         <v>46148</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57476,7 +57476,7 @@
         <v>46148</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57554,7 +57554,7 @@
         <v>45398</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>46149</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57700,7 +57700,7 @@
         <v>45448</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>46153</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -57851,7 +57851,7 @@
         <v>46128</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -57929,7 +57929,7 @@
         <v>46093</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58002,7 +58002,7 @@
         <v>46093</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58080,7 +58080,7 @@
         <v>46119</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58153,7 +58153,7 @@
         <v>46093</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>46088</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58304,7 +58304,7 @@
         <v>46071</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58382,7 +58382,7 @@
         <v>45909</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58455,7 +58455,7 @@
         <v>45986</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58533,7 +58533,7 @@
         <v>46153</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58606,7 +58606,7 @@
         <v>46043</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58679,7 +58679,7 @@
         <v>46104</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>46154</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58830,7 +58830,7 @@
         <v>46066</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -58908,7 +58908,7 @@
         <v>46049</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -58981,7 +58981,7 @@
         <v>46056</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59054,7 +59054,7 @@
         <v>45994</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59127,7 +59127,7 @@
         <v>46155</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59200,7 +59200,7 @@
         <v>46156</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59273,7 +59273,7 @@
         <v>45281</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59346,7 +59346,7 @@
         <v>45994</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>46044</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45926</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>46155</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59638,7 +59638,7 @@
         <v>46155</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59711,7 +59711,7 @@
         <v>45291</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59784,7 +59784,7 @@
         <v>46100</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -59857,7 +59857,7 @@
         <v>45106</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -59935,7 +59935,7 @@
         <v>45609</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60013,7 +60013,7 @@
         <v>45611</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60091,7 +60091,7 @@
         <v>45674</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60164,7 +60164,7 @@
         <v>45666</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60237,7 +60237,7 @@
         <v>45510</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60310,7 +60310,7 @@
         <v>45511</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60383,7 +60383,7 @@
         <v>45070</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60456,7 +60456,7 @@
         <v>45646</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45645</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45727</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60680,7 +60680,7 @@
         <v>45699</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45484</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>45534</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -60909,7 +60909,7 @@
         <v>45698</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -60982,7 +60982,7 @@
         <v>45111</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61055,7 +61055,7 @@
         <v>45022</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61128,7 +61128,7 @@
         <v>44890</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61201,7 +61201,7 @@
         <v>44883</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61279,7 +61279,7 @@
         <v>44712</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>45134</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61430,7 +61430,7 @@
         <v>45534</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>45754</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61576,7 +61576,7 @@
         <v>45758</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61649,7 +61649,7 @@
         <v>45156</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61727,7 +61727,7 @@
         <v>45593</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61800,7 +61800,7 @@
         <v>45041</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -61878,7 +61878,7 @@
         <v>45611</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -61956,7 +61956,7 @@
         <v>44970</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62029,7 +62029,7 @@
         <v>45649</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62102,7 +62102,7 @@
         <v>45072</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>45620</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>45596</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>45341</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62394,7 +62394,7 @@
         <v>45600</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
@@ -62467,7 +62467,7 @@
         <v>45617</v>
       </c>
       <c r="E791" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -62545,7 +62545,7 @@
         <v>45181</v>
       </c>
       <c r="E792" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -62618,7 +62618,7 @@
         <v>45624</v>
       </c>
       <c r="E793" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -62696,7 +62696,7 @@
         <v>45180</v>
       </c>
       <c r="E794" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -62769,7 +62769,7 @@
         <v>45645</v>
       </c>
       <c r="E795" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
@@ -62847,7 +62847,7 @@
         <v>45152</v>
       </c>
       <c r="E796" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -62920,7 +62920,7 @@
         <v>45432</v>
       </c>
       <c r="E797" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -62993,7 +62993,7 @@
         <v>45441</v>
       </c>
       <c r="E798" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -63066,7 +63066,7 @@
         <v>45671</v>
       </c>
       <c r="E799" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -63144,7 +63144,7 @@
         <v>45757</v>
       </c>
       <c r="E800" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -63222,7 +63222,7 @@
         <v>45705</v>
       </c>
       <c r="E801" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -63295,7 +63295,7 @@
         <v>44643</v>
       </c>
       <c r="E802" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45156</v>
       </c>
       <c r="E803" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -63446,7 +63446,7 @@
         <v>45243</v>
       </c>
       <c r="E804" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
@@ -63519,7 +63519,7 @@
         <v>45254</v>
       </c>
       <c r="E805" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -63592,7 +63592,7 @@
         <v>44804</v>
       </c>
       <c r="E806" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -63665,7 +63665,7 @@
         <v>44725</v>
       </c>
       <c r="E807" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
@@ -63738,7 +63738,7 @@
         <v>44781</v>
       </c>
       <c r="E808" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F808" t="inlineStr">
         <is>
@@ -63811,7 +63811,7 @@
         <v>45204</v>
       </c>
       <c r="E809" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
@@ -63884,7 +63884,7 @@
         <v>45134</v>
       </c>
       <c r="E810" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -63962,7 +63962,7 @@
         <v>44700</v>
       </c>
       <c r="E811" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -64040,7 +64040,7 @@
         <v>45265</v>
       </c>
       <c r="E812" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
@@ -64113,7 +64113,7 @@
         <v>45744</v>
       </c>
       <c r="E813" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -64191,7 +64191,7 @@
         <v>44797</v>
       </c>
       <c r="E814" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -64264,7 +64264,7 @@
         <v>45772</v>
       </c>
       <c r="E815" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
@@ -64337,7 +64337,7 @@
         <v>45237</v>
       </c>
       <c r="E816" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -64410,7 +64410,7 @@
         <v>45254</v>
       </c>
       <c r="E817" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -64483,7 +64483,7 @@
         <v>45230</v>
       </c>
       <c r="E818" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -64561,7 +64561,7 @@
         <v>45240</v>
       </c>
       <c r="E819" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -64639,7 +64639,7 @@
         <v>45301</v>
       </c>
       <c r="E820" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -64712,7 +64712,7 @@
         <v>45167</v>
       </c>
       <c r="E821" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -64785,7 +64785,7 @@
         <v>45623</v>
       </c>
       <c r="E822" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45139</v>
       </c>
       <c r="E823" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
@@ -64936,7 +64936,7 @@
         <v>45548</v>
       </c>
       <c r="E824" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -65014,7 +65014,7 @@
         <v>45323</v>
       </c>
       <c r="E825" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F825" t="inlineStr">
         <is>
@@ -65092,7 +65092,7 @@
         <v>45638</v>
       </c>
       <c r="E826" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -65170,7 +65170,7 @@
         <v>45315</v>
       </c>
       <c r="E827" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
@@ -65248,7 +65248,7 @@
         <v>45699</v>
       </c>
       <c r="E828" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -65326,7 +65326,7 @@
         <v>44904</v>
       </c>
       <c r="E829" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -65404,7 +65404,7 @@
         <v>46058</v>
       </c>
       <c r="E830" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -65477,7 +65477,7 @@
         <v>46089</v>
       </c>
       <c r="E831" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -65555,7 +65555,7 @@
         <v>46148</v>
       </c>
       <c r="E832" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -65628,7 +65628,7 @@
         <v>46148</v>
       </c>
       <c r="E833" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -65701,7 +65701,7 @@
         <v>46048</v>
       </c>
       <c r="E834" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -65774,7 +65774,7 @@
         <v>46293</v>
       </c>
       <c r="E835" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -65852,7 +65852,7 @@
         <v>46300</v>
       </c>
       <c r="E836" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F836" t="inlineStr">
         <is>
@@ -65925,7 +65925,7 @@
         <v>46255</v>
       </c>
       <c r="E837" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -66003,7 +66003,7 @@
         <v>46307</v>
       </c>
       <c r="E838" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
